--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV_Mel\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FE0B48-6453-4D43-9524-09C1EAF652C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332C59DA-D947-4EFA-AF1E-73C3535C9F0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$581</definedName>
-    <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$520</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$583</definedName>
+    <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$522</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="1037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2514" uniqueCount="1042">
   <si>
     <t>1С</t>
   </si>
@@ -3150,6 +3150,21 @@
   </si>
   <si>
     <t>Снеки «Чебупицца со вкусом Том ям» Фикс.вес 0,23 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>Жареные вареники с картофелем и беконом ТМ Стародворье 0,2 кг  ПОКОМ</t>
+  </si>
+  <si>
+    <t>Хрустипай манго чили ТМ Горячая штучка 0,18кг с начинкой ПОКОМ</t>
+  </si>
+  <si>
+    <t>SU004070</t>
+  </si>
+  <si>
+    <t>P005200</t>
+  </si>
+  <si>
+    <t>Изделия хлебобулочные «Хрустипай манго чили» Фикс.вес 0,18 ТМ «Горячая штучка»</t>
   </si>
 </sst>
 </file>
@@ -6405,7 +6420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H581"/>
+  <dimension ref="A1:H583"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88" style="11" customWidth="1"/>
@@ -18283,7 +18298,7 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>997</v>
+        <v>1037</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>1010</v>
@@ -18304,175 +18319,169 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D515" s="4">
-        <v>4301135873</v>
+        <v>4301135834</v>
       </c>
       <c r="E515" s="3">
-        <v>4640242182087</v>
+        <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="D516" s="4">
-        <v>4301135850</v>
+        <v>4301135873</v>
       </c>
       <c r="E516" s="3">
-        <v>4620207491492</v>
+        <v>4640242182087</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="D517" s="4">
-        <v>4301190117</v>
+        <v>4301135850</v>
       </c>
       <c r="E517" s="3">
-        <v>4620207491386</v>
+        <v>4620207491492</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="D518" s="4">
-        <v>4301190115</v>
+        <v>4301190117</v>
       </c>
       <c r="E518" s="3">
-        <v>4620207491362</v>
+        <v>4620207491386</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D519" s="4">
+        <v>4301190115</v>
+      </c>
+      <c r="E519" s="3">
+        <v>4620207491362</v>
+      </c>
+      <c r="F519" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G519" s="1"/>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A520" s="10" t="s">
         <v>1033</v>
       </c>
-      <c r="B519" s="3" t="s">
+      <c r="B520" s="3" t="s">
         <v>1034</v>
       </c>
-      <c r="C519" s="3" t="s">
+      <c r="C520" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="D519" s="4">
+      <c r="D520" s="4">
         <v>4301135865</v>
       </c>
-      <c r="E519" s="3">
+      <c r="E520" s="3">
         <v>4620207491485</v>
       </c>
-      <c r="F519" s="5" t="s">
+      <c r="F520" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="G519" s="1"/>
-    </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A520" s="17" t="s">
-        <v>788</v>
-      </c>
-      <c r="B520" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="C520" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="D520" s="19">
-        <v>4301071038</v>
-      </c>
-      <c r="E520" s="18">
-        <v>4607111039248</v>
-      </c>
-      <c r="F520" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="G520" s="21"/>
-      <c r="H520" s="22" t="s">
-        <v>849</v>
-      </c>
+      <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A521" s="17" t="s">
-        <v>789</v>
-      </c>
-      <c r="B521" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C521" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="D521" s="19">
-        <v>4301070981</v>
-      </c>
-      <c r="E521" s="18">
-        <v>4607111036728</v>
-      </c>
-      <c r="F521" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="G521" s="21"/>
-      <c r="H521" s="22" t="s">
-        <v>849</v>
-      </c>
+      <c r="A521" s="10" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D521" s="4">
+        <v>4301190116</v>
+      </c>
+      <c r="E521" s="3">
+        <v>4620207491379</v>
+      </c>
+      <c r="F521" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="17" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B522" s="18" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C522" s="18" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D522" s="19">
-        <v>4301071039</v>
+        <v>4301071038</v>
       </c>
       <c r="E522" s="18">
-        <v>4607111039279</v>
+        <v>4607111039248</v>
       </c>
       <c r="F522" s="20" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="G522" s="21"/>
       <c r="H522" s="22" t="s">
@@ -18481,22 +18490,22 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="17" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B523" s="18" t="s">
-        <v>612</v>
+        <v>106</v>
       </c>
       <c r="C523" s="18" t="s">
-        <v>613</v>
+        <v>257</v>
       </c>
       <c r="D523" s="19">
-        <v>4301071051</v>
+        <v>4301070981</v>
       </c>
       <c r="E523" s="18">
-        <v>4607111039262</v>
+        <v>4607111036728</v>
       </c>
       <c r="F523" s="20" t="s">
-        <v>614</v>
+        <v>258</v>
       </c>
       <c r="G523" s="21"/>
       <c r="H523" s="22" t="s">
@@ -18505,22 +18514,22 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="17" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B524" s="18" t="s">
-        <v>289</v>
+        <v>624</v>
       </c>
       <c r="C524" s="18" t="s">
-        <v>290</v>
+        <v>625</v>
       </c>
       <c r="D524" s="19">
-        <v>4301132080</v>
+        <v>4301071039</v>
       </c>
       <c r="E524" s="18">
-        <v>4640242180397</v>
+        <v>4607111039279</v>
       </c>
       <c r="F524" s="20" t="s">
-        <v>291</v>
+        <v>626</v>
       </c>
       <c r="G524" s="21"/>
       <c r="H524" s="22" t="s">
@@ -18529,22 +18538,22 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="17" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B525" s="18" t="s">
-        <v>111</v>
+        <v>612</v>
       </c>
       <c r="C525" s="18" t="s">
-        <v>520</v>
+        <v>613</v>
       </c>
       <c r="D525" s="19">
-        <v>4301071029</v>
+        <v>4301071051</v>
       </c>
       <c r="E525" s="18">
-        <v>4607111035899</v>
+        <v>4607111039262</v>
       </c>
       <c r="F525" s="20" t="s">
-        <v>112</v>
+        <v>614</v>
       </c>
       <c r="G525" s="21"/>
       <c r="H525" s="22" t="s">
@@ -18553,22 +18562,22 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="17" t="s">
-        <v>794</v>
-      </c>
-      <c r="B526" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C526" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D526" s="4">
-        <v>4301136053</v>
-      </c>
-      <c r="E526" s="3">
-        <v>4640242180236</v>
-      </c>
-      <c r="F526" s="5" t="s">
-        <v>300</v>
+        <v>792</v>
+      </c>
+      <c r="B526" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C526" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="D526" s="19">
+        <v>4301132080</v>
+      </c>
+      <c r="E526" s="18">
+        <v>4640242180397</v>
+      </c>
+      <c r="F526" s="20" t="s">
+        <v>291</v>
       </c>
       <c r="G526" s="21"/>
       <c r="H526" s="22" t="s">
@@ -18577,22 +18586,22 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="17" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B527" s="18" t="s">
-        <v>314</v>
+        <v>111</v>
       </c>
       <c r="C527" s="18" t="s">
-        <v>315</v>
+        <v>520</v>
       </c>
       <c r="D527" s="19">
-        <v>4301070977</v>
+        <v>4301071029</v>
       </c>
       <c r="E527" s="18">
-        <v>4607111037411</v>
+        <v>4607111035899</v>
       </c>
       <c r="F527" s="20" t="s">
-        <v>316</v>
+        <v>112</v>
       </c>
       <c r="G527" s="21"/>
       <c r="H527" s="22" t="s">
@@ -18601,22 +18610,22 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="17" t="s">
-        <v>796</v>
-      </c>
-      <c r="B528" s="18" t="s">
-        <v>549</v>
-      </c>
-      <c r="C528" s="18" t="s">
-        <v>550</v>
-      </c>
-      <c r="D528" s="19">
-        <v>4301135375</v>
-      </c>
-      <c r="E528" s="18">
-        <v>4640242181486</v>
-      </c>
-      <c r="F528" s="20" t="s">
-        <v>551</v>
+        <v>794</v>
+      </c>
+      <c r="B528" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D528" s="4">
+        <v>4301136053</v>
+      </c>
+      <c r="E528" s="3">
+        <v>4640242180236</v>
+      </c>
+      <c r="F528" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="G528" s="21"/>
       <c r="H528" s="22" t="s">
@@ -18625,46 +18634,46 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="17" t="s">
-        <v>797</v>
-      </c>
-      <c r="B529" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="C529" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="D529" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E529" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F529" s="5" t="s">
-        <v>942</v>
+        <v>795</v>
+      </c>
+      <c r="B529" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="C529" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="D529" s="19">
+        <v>4301070977</v>
+      </c>
+      <c r="E529" s="18">
+        <v>4607111037411</v>
+      </c>
+      <c r="F529" s="20" t="s">
+        <v>316</v>
       </c>
       <c r="G529" s="21"/>
-      <c r="H529" s="16" t="s">
-        <v>936</v>
+      <c r="H529" s="22" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="17" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B530" s="18" t="s">
-        <v>110</v>
+        <v>549</v>
       </c>
       <c r="C530" s="18" t="s">
-        <v>627</v>
+        <v>550</v>
       </c>
       <c r="D530" s="19">
-        <v>4301071050</v>
+        <v>4301135375</v>
       </c>
       <c r="E530" s="18">
-        <v>4607111036216</v>
+        <v>4640242181486</v>
       </c>
       <c r="F530" s="20" t="s">
-        <v>628</v>
+        <v>551</v>
       </c>
       <c r="G530" s="21"/>
       <c r="H530" s="22" t="s">
@@ -18673,46 +18682,46 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="17" t="s">
-        <v>799</v>
-      </c>
-      <c r="B531" s="18" t="s">
-        <v>620</v>
-      </c>
-      <c r="C531" s="18" t="s">
-        <v>621</v>
-      </c>
-      <c r="D531" s="19">
-        <v>4301071049</v>
-      </c>
-      <c r="E531" s="18">
-        <v>4607111039293</v>
-      </c>
-      <c r="F531" s="20" t="s">
-        <v>622</v>
+        <v>797</v>
+      </c>
+      <c r="B531" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="D531" s="4">
+        <v>4301135760</v>
+      </c>
+      <c r="E531" s="3">
+        <v>4620207491010</v>
+      </c>
+      <c r="F531" s="5" t="s">
+        <v>942</v>
       </c>
       <c r="G531" s="21"/>
-      <c r="H531" s="22" t="s">
-        <v>849</v>
+      <c r="H531" s="16" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="17" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B532" s="18" t="s">
-        <v>647</v>
+        <v>110</v>
       </c>
       <c r="C532" s="18" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="D532" s="19">
-        <v>4301135532</v>
+        <v>4301071050</v>
       </c>
       <c r="E532" s="18">
-        <v>4607111033994</v>
+        <v>4607111036216</v>
       </c>
       <c r="F532" s="20" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="G532" s="21"/>
       <c r="H532" s="22" t="s">
@@ -18721,22 +18730,22 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="17" t="s">
-        <v>801</v>
-      </c>
-      <c r="B533" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="C533" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="D533" s="4">
-        <v>4301135555</v>
-      </c>
-      <c r="E533" s="3">
-        <v>4607111034014</v>
-      </c>
-      <c r="F533" s="5" t="s">
-        <v>652</v>
+        <v>799</v>
+      </c>
+      <c r="B533" s="18" t="s">
+        <v>620</v>
+      </c>
+      <c r="C533" s="18" t="s">
+        <v>621</v>
+      </c>
+      <c r="D533" s="19">
+        <v>4301071049</v>
+      </c>
+      <c r="E533" s="18">
+        <v>4607111039293</v>
+      </c>
+      <c r="F533" s="20" t="s">
+        <v>622</v>
       </c>
       <c r="G533" s="21"/>
       <c r="H533" s="22" t="s">
@@ -18745,46 +18754,46 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="17" t="s">
-        <v>802</v>
-      </c>
-      <c r="B534" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="C534" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="D534" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E534" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F534" s="5" t="s">
-        <v>935</v>
+        <v>800</v>
+      </c>
+      <c r="B534" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="C534" s="18" t="s">
+        <v>648</v>
+      </c>
+      <c r="D534" s="19">
+        <v>4301135532</v>
+      </c>
+      <c r="E534" s="18">
+        <v>4607111033994</v>
+      </c>
+      <c r="F534" s="20" t="s">
+        <v>649</v>
       </c>
       <c r="G534" s="21"/>
-      <c r="H534" s="16" t="s">
-        <v>936</v>
+      <c r="H534" s="22" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="17" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>378</v>
+        <v>650</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>379</v>
+        <v>651</v>
       </c>
       <c r="D535" s="4">
-        <v>4301136052</v>
+        <v>4301135555</v>
       </c>
       <c r="E535" s="3">
-        <v>4640242180410</v>
+        <v>4607111034014</v>
       </c>
       <c r="F535" s="5" t="s">
-        <v>380</v>
+        <v>652</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="22" t="s">
@@ -18793,46 +18802,46 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="17" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>545</v>
+        <v>933</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>546</v>
+        <v>934</v>
       </c>
       <c r="D536" s="4">
-        <v>4301135518</v>
+        <v>4301135793</v>
       </c>
       <c r="E536" s="3">
-        <v>4640242181561</v>
+        <v>4620207491003</v>
       </c>
       <c r="F536" s="5" t="s">
-        <v>547</v>
+        <v>935</v>
       </c>
       <c r="G536" s="21"/>
-      <c r="H536" s="22" t="s">
-        <v>849</v>
+      <c r="H536" s="16" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="17" t="s">
-        <v>805</v>
-      </c>
-      <c r="B537" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="C537" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="D537" s="19">
-        <v>4301135374</v>
-      </c>
-      <c r="E537" s="18">
-        <v>4640242181424</v>
-      </c>
-      <c r="F537" s="20" t="s">
-        <v>597</v>
+        <v>803</v>
+      </c>
+      <c r="B537" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D537" s="4">
+        <v>4301136052</v>
+      </c>
+      <c r="E537" s="3">
+        <v>4640242180410</v>
+      </c>
+      <c r="F537" s="5" t="s">
+        <v>380</v>
       </c>
       <c r="G537" s="21"/>
       <c r="H537" s="22" t="s">
@@ -18841,22 +18850,22 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="17" t="s">
-        <v>806</v>
-      </c>
-      <c r="B538" s="18" t="s">
-        <v>850</v>
-      </c>
-      <c r="C538" s="18" t="s">
-        <v>851</v>
-      </c>
-      <c r="D538" s="19">
-        <v>4301132079</v>
-      </c>
-      <c r="E538" s="18">
-        <v>4607111038487</v>
-      </c>
-      <c r="F538" s="20" t="s">
-        <v>421</v>
+        <v>804</v>
+      </c>
+      <c r="B538" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D538" s="4">
+        <v>4301135518</v>
+      </c>
+      <c r="E538" s="3">
+        <v>4640242181561</v>
+      </c>
+      <c r="F538" s="5" t="s">
+        <v>547</v>
       </c>
       <c r="G538" s="21"/>
       <c r="H538" s="22" t="s">
@@ -18865,22 +18874,22 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="17" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B539" s="18" t="s">
-        <v>160</v>
+        <v>595</v>
       </c>
       <c r="C539" s="18" t="s">
-        <v>630</v>
+        <v>596</v>
       </c>
       <c r="D539" s="19">
-        <v>4301071056</v>
+        <v>4301135374</v>
       </c>
       <c r="E539" s="18">
-        <v>4640242180250</v>
+        <v>4640242181424</v>
       </c>
       <c r="F539" s="20" t="s">
-        <v>631</v>
+        <v>597</v>
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="22" t="s">
@@ -18889,22 +18898,22 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="17" t="s">
-        <v>808</v>
-      </c>
-      <c r="B540" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C540" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D540" s="4">
-        <v>4301136051</v>
-      </c>
-      <c r="E540" s="3">
-        <v>4640242180304</v>
-      </c>
-      <c r="F540" s="5" t="s">
-        <v>297</v>
+        <v>806</v>
+      </c>
+      <c r="B540" s="18" t="s">
+        <v>850</v>
+      </c>
+      <c r="C540" s="18" t="s">
+        <v>851</v>
+      </c>
+      <c r="D540" s="19">
+        <v>4301132079</v>
+      </c>
+      <c r="E540" s="18">
+        <v>4607111038487</v>
+      </c>
+      <c r="F540" s="20" t="s">
+        <v>421</v>
       </c>
       <c r="G540" s="21"/>
       <c r="H540" s="22" t="s">
@@ -18913,22 +18922,22 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="17" t="s">
-        <v>809</v>
-      </c>
-      <c r="B541" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C541" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D541" s="4">
-        <v>4301071109</v>
-      </c>
-      <c r="E541" s="3">
-        <v>4607111035929</v>
-      </c>
-      <c r="F541" s="5" t="s">
-        <v>1003</v>
+        <v>807</v>
+      </c>
+      <c r="B541" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C541" s="18" t="s">
+        <v>630</v>
+      </c>
+      <c r="D541" s="19">
+        <v>4301071056</v>
+      </c>
+      <c r="E541" s="18">
+        <v>4640242180250</v>
+      </c>
+      <c r="F541" s="20" t="s">
+        <v>631</v>
       </c>
       <c r="G541" s="21"/>
       <c r="H541" s="22" t="s">
@@ -18937,22 +18946,22 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="17" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>738</v>
+        <v>295</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>739</v>
+        <v>296</v>
       </c>
       <c r="D542" s="4">
-        <v>4301135550</v>
+        <v>4301136051</v>
       </c>
       <c r="E542" s="3">
-        <v>4607111034199</v>
+        <v>4640242180304</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>740</v>
+        <v>297</v>
       </c>
       <c r="G542" s="21"/>
       <c r="H542" s="22" t="s">
@@ -18961,22 +18970,22 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="17" t="s">
-        <v>811</v>
-      </c>
-      <c r="B543" s="18" t="s">
-        <v>735</v>
-      </c>
-      <c r="C543" s="18" t="s">
-        <v>736</v>
-      </c>
-      <c r="D543" s="19">
-        <v>4301132186</v>
-      </c>
-      <c r="E543" s="18">
-        <v>4607111036520</v>
-      </c>
-      <c r="F543" s="20" t="s">
-        <v>737</v>
+        <v>809</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D543" s="4">
+        <v>4301071109</v>
+      </c>
+      <c r="E543" s="3">
+        <v>4607111035929</v>
+      </c>
+      <c r="F543" s="5" t="s">
+        <v>1003</v>
       </c>
       <c r="G543" s="21"/>
       <c r="H543" s="22" t="s">
@@ -18985,22 +18994,22 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="17" t="s">
-        <v>812</v>
-      </c>
-      <c r="B544" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="C544" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="D544" s="19">
-        <v>4301071047</v>
-      </c>
-      <c r="E544" s="18">
-        <v>4607111039330</v>
-      </c>
-      <c r="F544" s="20" t="s">
-        <v>610</v>
+        <v>810</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D544" s="4">
+        <v>4301135550</v>
+      </c>
+      <c r="E544" s="3">
+        <v>4607111034199</v>
+      </c>
+      <c r="F544" s="5" t="s">
+        <v>740</v>
       </c>
       <c r="G544" s="21"/>
       <c r="H544" s="22" t="s">
@@ -19009,22 +19018,22 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="17" t="s">
-        <v>813</v>
-      </c>
-      <c r="B545" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="C545" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D545" s="4">
-        <v>4301131047</v>
-      </c>
-      <c r="E545" s="3">
-        <v>4607111034120</v>
-      </c>
-      <c r="F545" s="5" t="s">
-        <v>779</v>
+        <v>811</v>
+      </c>
+      <c r="B545" s="18" t="s">
+        <v>735</v>
+      </c>
+      <c r="C545" s="18" t="s">
+        <v>736</v>
+      </c>
+      <c r="D545" s="19">
+        <v>4301132186</v>
+      </c>
+      <c r="E545" s="18">
+        <v>4607111036520</v>
+      </c>
+      <c r="F545" s="20" t="s">
+        <v>737</v>
       </c>
       <c r="G545" s="21"/>
       <c r="H545" s="22" t="s">
@@ -19033,46 +19042,46 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="17" t="s">
-        <v>814</v>
-      </c>
-      <c r="B546" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="C546" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="D546" s="4">
-        <v>4301135763</v>
-      </c>
-      <c r="E546" s="3">
-        <v>4620207491027</v>
-      </c>
-      <c r="F546" s="5" t="s">
-        <v>898</v>
+        <v>812</v>
+      </c>
+      <c r="B546" s="18" t="s">
+        <v>608</v>
+      </c>
+      <c r="C546" s="18" t="s">
+        <v>609</v>
+      </c>
+      <c r="D546" s="19">
+        <v>4301071047</v>
+      </c>
+      <c r="E546" s="18">
+        <v>4607111039330</v>
+      </c>
+      <c r="F546" s="20" t="s">
+        <v>610</v>
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
-        <v>955</v>
+        <v>849</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="17" t="s">
-        <v>815</v>
-      </c>
-      <c r="B547" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="C547" s="18" t="s">
-        <v>554</v>
-      </c>
-      <c r="D547" s="19">
-        <v>4301135405</v>
-      </c>
-      <c r="E547" s="18">
-        <v>4640242181523</v>
-      </c>
-      <c r="F547" s="20" t="s">
-        <v>555</v>
+        <v>813</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="D547" s="4">
+        <v>4301131047</v>
+      </c>
+      <c r="E547" s="3">
+        <v>4607111034120</v>
+      </c>
+      <c r="F547" s="5" t="s">
+        <v>779</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
@@ -19081,46 +19090,46 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="17" t="s">
-        <v>816</v>
-      </c>
-      <c r="B548" s="18" t="s">
-        <v>702</v>
-      </c>
-      <c r="C548" s="18" t="s">
-        <v>703</v>
-      </c>
-      <c r="D548" s="19">
-        <v>4301135402</v>
-      </c>
-      <c r="E548" s="18">
-        <v>4640242181493</v>
-      </c>
-      <c r="F548" s="20" t="s">
-        <v>701</v>
+        <v>814</v>
+      </c>
+      <c r="B548" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="D548" s="4">
+        <v>4301135763</v>
+      </c>
+      <c r="E548" s="3">
+        <v>4620207491027</v>
+      </c>
+      <c r="F548" s="5" t="s">
+        <v>898</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
-        <v>849</v>
+        <v>955</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="17" t="s">
-        <v>817</v>
-      </c>
-      <c r="B549" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="C549" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="D549" s="4">
-        <v>4301131046</v>
-      </c>
-      <c r="E549" s="3">
-        <v>4607111034137</v>
-      </c>
-      <c r="F549" s="5" t="s">
-        <v>877</v>
+        <v>815</v>
+      </c>
+      <c r="B549" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="C549" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="D549" s="19">
+        <v>4301135405</v>
+      </c>
+      <c r="E549" s="18">
+        <v>4640242181523</v>
+      </c>
+      <c r="F549" s="20" t="s">
+        <v>555</v>
       </c>
       <c r="G549" s="21"/>
       <c r="H549" s="22" t="s">
@@ -19129,22 +19138,22 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="17" t="s">
-        <v>818</v>
-      </c>
-      <c r="B550" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="C550" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="D550" s="4">
-        <v>4301136079</v>
-      </c>
-      <c r="E550" s="3">
-        <v>4607025784319</v>
-      </c>
-      <c r="F550" s="5" t="s">
-        <v>883</v>
+        <v>816</v>
+      </c>
+      <c r="B550" s="18" t="s">
+        <v>702</v>
+      </c>
+      <c r="C550" s="18" t="s">
+        <v>703</v>
+      </c>
+      <c r="D550" s="19">
+        <v>4301135402</v>
+      </c>
+      <c r="E550" s="18">
+        <v>4640242181493</v>
+      </c>
+      <c r="F550" s="20" t="s">
+        <v>701</v>
       </c>
       <c r="G550" s="21"/>
       <c r="H550" s="22" t="s">
@@ -19153,22 +19162,22 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="17" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>949</v>
+        <v>875</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>950</v>
+        <v>876</v>
       </c>
       <c r="D551" s="4">
-        <v>4301135753</v>
+        <v>4301131046</v>
       </c>
       <c r="E551" s="3">
-        <v>4620207490914</v>
+        <v>4607111034137</v>
       </c>
       <c r="F551" s="5" t="s">
-        <v>951</v>
+        <v>877</v>
       </c>
       <c r="G551" s="21"/>
       <c r="H551" s="22" t="s">
@@ -19177,46 +19186,46 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="17" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>937</v>
+        <v>881</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>938</v>
+        <v>882</v>
       </c>
       <c r="D552" s="4">
-        <v>4301135778</v>
+        <v>4301136079</v>
       </c>
       <c r="E552" s="3">
-        <v>4620207490853</v>
+        <v>4607025784319</v>
       </c>
       <c r="F552" s="5" t="s">
-        <v>939</v>
+        <v>883</v>
       </c>
       <c r="G552" s="21"/>
-      <c r="H552" s="16" t="s">
-        <v>943</v>
+      <c r="H552" s="22" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="17" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>865</v>
+        <v>949</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>866</v>
+        <v>950</v>
       </c>
       <c r="D553" s="4">
-        <v>4301132179</v>
+        <v>4301135753</v>
       </c>
       <c r="E553" s="3">
-        <v>4607111035691</v>
+        <v>4620207490914</v>
       </c>
       <c r="F553" s="5" t="s">
-        <v>867</v>
+        <v>951</v>
       </c>
       <c r="G553" s="21"/>
       <c r="H553" s="22" t="s">
@@ -19225,46 +19234,46 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="17" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>732</v>
+        <v>937</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>733</v>
+        <v>938</v>
       </c>
       <c r="D554" s="4">
-        <v>4301132190</v>
+        <v>4301135778</v>
       </c>
       <c r="E554" s="3">
-        <v>4607111036537</v>
+        <v>4620207490853</v>
       </c>
       <c r="F554" s="5" t="s">
-        <v>734</v>
+        <v>939</v>
       </c>
       <c r="G554" s="21"/>
-      <c r="H554" s="22" t="s">
-        <v>849</v>
+      <c r="H554" s="16" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="17" t="s">
-        <v>823</v>
-      </c>
-      <c r="B555" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="C555" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D555" s="19">
-        <v>4301131019</v>
-      </c>
-      <c r="E555" s="18">
-        <v>4640242180427</v>
-      </c>
-      <c r="F555" s="20" t="s">
-        <v>373</v>
+        <v>821</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="D555" s="4">
+        <v>4301132179</v>
+      </c>
+      <c r="E555" s="3">
+        <v>4607111035691</v>
+      </c>
+      <c r="F555" s="5" t="s">
+        <v>867</v>
       </c>
       <c r="G555" s="21"/>
       <c r="H555" s="22" t="s">
@@ -19273,22 +19282,22 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="17" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>884</v>
+        <v>732</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>885</v>
+        <v>733</v>
       </c>
       <c r="D556" s="4">
-        <v>4301135571</v>
+        <v>4301132190</v>
       </c>
       <c r="E556" s="3">
-        <v>4607111035028</v>
+        <v>4607111036537</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>886</v>
+        <v>734</v>
       </c>
       <c r="G556" s="21"/>
       <c r="H556" s="22" t="s">
@@ -19297,46 +19306,46 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="17" t="s">
-        <v>825</v>
-      </c>
-      <c r="B557" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="C557" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="D557" s="4">
-        <v>4301135768</v>
-      </c>
-      <c r="E557" s="3">
-        <v>4620207491034</v>
-      </c>
-      <c r="F557" s="5" t="s">
-        <v>921</v>
+        <v>823</v>
+      </c>
+      <c r="B557" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C557" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D557" s="19">
+        <v>4301131019</v>
+      </c>
+      <c r="E557" s="18">
+        <v>4640242180427</v>
+      </c>
+      <c r="F557" s="20" t="s">
+        <v>373</v>
       </c>
       <c r="G557" s="21"/>
-      <c r="H557" s="16" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="558" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="H557" s="22" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="17" t="s">
-        <v>827</v>
-      </c>
-      <c r="B558" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C558" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="D558" s="19">
-        <v>4301070960</v>
-      </c>
-      <c r="E558" s="18">
-        <v>4607111038623</v>
-      </c>
-      <c r="F558" s="20" t="s">
-        <v>485</v>
+        <v>824</v>
+      </c>
+      <c r="B558" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="D558" s="4">
+        <v>4301135571</v>
+      </c>
+      <c r="E558" s="3">
+        <v>4607111035028</v>
+      </c>
+      <c r="F558" s="5" t="s">
+        <v>886</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="22" t="s">
@@ -19345,70 +19354,70 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="17" t="s">
-        <v>828</v>
-      </c>
-      <c r="B559" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C559" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="D559" s="19">
-        <v>4301070966</v>
-      </c>
-      <c r="E559" s="18">
-        <v>4607111038135</v>
-      </c>
-      <c r="F559" s="20" t="s">
-        <v>363</v>
+        <v>825</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="D559" s="4">
+        <v>4301135768</v>
+      </c>
+      <c r="E559" s="3">
+        <v>4620207491034</v>
+      </c>
+      <c r="F559" s="5" t="s">
+        <v>921</v>
       </c>
       <c r="G559" s="21"/>
-      <c r="H559" s="22" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A560" s="10" t="s">
-        <v>893</v>
-      </c>
-      <c r="B560" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="C560" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="D560" s="4">
-        <v>4301070990</v>
-      </c>
-      <c r="E560" s="3">
-        <v>4607111038494</v>
-      </c>
-      <c r="F560" s="5" t="s">
-        <v>854</v>
-      </c>
-      <c r="G560" s="1"/>
-      <c r="H560" s="16" t="s">
+      <c r="H559" s="16" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A560" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="B560" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="C560" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="D560" s="19">
+        <v>4301070960</v>
+      </c>
+      <c r="E560" s="18">
+        <v>4607111038623</v>
+      </c>
+      <c r="F560" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="G560" s="21"/>
+      <c r="H560" s="22" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="17" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B561" s="18" t="s">
-        <v>852</v>
+        <v>364</v>
       </c>
       <c r="C561" s="18" t="s">
-        <v>853</v>
+        <v>365</v>
       </c>
       <c r="D561" s="19">
-        <v>4301070990</v>
+        <v>4301070966</v>
       </c>
       <c r="E561" s="18">
-        <v>4607111038494</v>
+        <v>4607111038135</v>
       </c>
       <c r="F561" s="20" t="s">
-        <v>854</v>
+        <v>363</v>
       </c>
       <c r="G561" s="21"/>
       <c r="H561" s="22" t="s">
@@ -19416,47 +19425,47 @@
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A562" s="17" t="s">
-        <v>830</v>
+      <c r="A562" s="10" t="s">
+        <v>893</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>1018</v>
+        <v>852</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>1019</v>
+        <v>853</v>
       </c>
       <c r="D562" s="4">
-        <v>4301071107</v>
+        <v>4301070990</v>
       </c>
       <c r="E562" s="3">
-        <v>4607111035905</v>
+        <v>4607111038494</v>
       </c>
       <c r="F562" s="5" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G562" s="21"/>
-      <c r="H562" s="22" t="s">
+        <v>854</v>
+      </c>
+      <c r="G562" s="1"/>
+      <c r="H562" s="16" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" s="17" t="s">
-        <v>831</v>
-      </c>
-      <c r="B563" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C563" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D563" s="4">
-        <v>4301135824</v>
-      </c>
-      <c r="E563" s="3">
-        <v>4607111039095</v>
-      </c>
-      <c r="F563" s="5" t="s">
-        <v>1009</v>
+        <v>829</v>
+      </c>
+      <c r="B563" s="18" t="s">
+        <v>852</v>
+      </c>
+      <c r="C563" s="18" t="s">
+        <v>853</v>
+      </c>
+      <c r="D563" s="19">
+        <v>4301070990</v>
+      </c>
+      <c r="E563" s="18">
+        <v>4607111038494</v>
+      </c>
+      <c r="F563" s="20" t="s">
+        <v>854</v>
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="22" t="s">
@@ -19465,22 +19474,22 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="17" t="s">
-        <v>832</v>
-      </c>
-      <c r="B564" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C564" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="D564" s="19">
-        <v>4301135285</v>
-      </c>
-      <c r="E564" s="18">
-        <v>4607111036407</v>
-      </c>
-      <c r="F564" s="20" t="s">
-        <v>182</v>
+        <v>830</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D564" s="4">
+        <v>4301071107</v>
+      </c>
+      <c r="E564" s="3">
+        <v>4607111035905</v>
+      </c>
+      <c r="F564" s="5" t="s">
+        <v>1020</v>
       </c>
       <c r="G564" s="21"/>
       <c r="H564" s="22" t="s">
@@ -19489,22 +19498,22 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="17" t="s">
-        <v>708</v>
+        <v>831</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>706</v>
+        <v>1007</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>707</v>
+        <v>1008</v>
       </c>
       <c r="D565" s="4">
-        <v>4301135607</v>
+        <v>4301135824</v>
       </c>
       <c r="E565" s="3">
-        <v>4607111039613</v>
+        <v>4607111039095</v>
       </c>
       <c r="F565" s="5" t="s">
-        <v>708</v>
+        <v>1009</v>
       </c>
       <c r="G565" s="21"/>
       <c r="H565" s="22" t="s">
@@ -19513,22 +19522,22 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="17" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B566" s="18" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="C566" s="18" t="s">
-        <v>126</v>
+        <v>522</v>
       </c>
       <c r="D566" s="19">
-        <v>4301080153</v>
+        <v>4301135285</v>
       </c>
       <c r="E566" s="18">
-        <v>4607111036827</v>
+        <v>4607111036407</v>
       </c>
       <c r="F566" s="20" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="G566" s="21"/>
       <c r="H566" s="22" t="s">
@@ -19537,22 +19546,22 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="17" t="s">
-        <v>834</v>
+        <v>708</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="D567" s="4">
-        <v>4301135574</v>
+        <v>4301135607</v>
       </c>
       <c r="E567" s="3">
-        <v>4607111033659</v>
+        <v>4607111039613</v>
       </c>
       <c r="F567" s="5" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="G567" s="21"/>
       <c r="H567" s="22" t="s">
@@ -19561,22 +19570,22 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="17" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B568" s="18" t="s">
-        <v>664</v>
+        <v>125</v>
       </c>
       <c r="C568" s="18" t="s">
-        <v>665</v>
+        <v>126</v>
       </c>
       <c r="D568" s="19">
-        <v>4301071044</v>
+        <v>4301080153</v>
       </c>
       <c r="E568" s="18">
-        <v>4607111039385</v>
+        <v>4607111036827</v>
       </c>
       <c r="F568" s="20" t="s">
-        <v>666</v>
+        <v>127</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19585,22 +19594,22 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" s="17" t="s">
-        <v>836</v>
-      </c>
-      <c r="B569" s="18" t="s">
-        <v>681</v>
-      </c>
-      <c r="C569" s="18" t="s">
-        <v>682</v>
-      </c>
-      <c r="D569" s="19">
-        <v>4301071031</v>
-      </c>
-      <c r="E569" s="18">
-        <v>4607111038982</v>
-      </c>
-      <c r="F569" s="20" t="s">
-        <v>683</v>
+        <v>834</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="D569" s="4">
+        <v>4301135574</v>
+      </c>
+      <c r="E569" s="3">
+        <v>4607111033659</v>
+      </c>
+      <c r="F569" s="5" t="s">
+        <v>722</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
@@ -19609,22 +19618,22 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" s="17" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B570" s="18" t="s">
-        <v>177</v>
+        <v>664</v>
       </c>
       <c r="C570" s="18" t="s">
-        <v>178</v>
+        <v>665</v>
       </c>
       <c r="D570" s="19">
-        <v>4301070917</v>
+        <v>4301071044</v>
       </c>
       <c r="E570" s="18">
-        <v>4607111035912</v>
+        <v>4607111039385</v>
       </c>
       <c r="F570" s="20" t="s">
-        <v>179</v>
+        <v>666</v>
       </c>
       <c r="G570" s="21"/>
       <c r="H570" s="22" t="s">
@@ -19633,22 +19642,22 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="17" t="s">
-        <v>838</v>
-      </c>
-      <c r="B571" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C571" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D571" s="4">
-        <v>4301136070</v>
-      </c>
-      <c r="E571" s="3">
-        <v>4607025784012</v>
-      </c>
-      <c r="F571" s="5" t="s">
-        <v>166</v>
+        <v>836</v>
+      </c>
+      <c r="B571" s="18" t="s">
+        <v>681</v>
+      </c>
+      <c r="C571" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="D571" s="19">
+        <v>4301071031</v>
+      </c>
+      <c r="E571" s="18">
+        <v>4607111038982</v>
+      </c>
+      <c r="F571" s="20" t="s">
+        <v>683</v>
       </c>
       <c r="G571" s="21"/>
       <c r="H571" s="22" t="s">
@@ -19657,118 +19666,118 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="17" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B572" s="18" t="s">
-        <v>604</v>
+        <v>177</v>
       </c>
       <c r="C572" s="18" t="s">
-        <v>605</v>
+        <v>178</v>
       </c>
       <c r="D572" s="19">
-        <v>4301071046</v>
+        <v>4301070917</v>
       </c>
       <c r="E572" s="18">
-        <v>4607111039354</v>
+        <v>4607111035912</v>
       </c>
       <c r="F572" s="20" t="s">
-        <v>606</v>
+        <v>179</v>
       </c>
       <c r="G572" s="21"/>
       <c r="H572" s="22" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="573" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="17" t="s">
-        <v>840</v>
-      </c>
-      <c r="B573" s="18" t="s">
-        <v>855</v>
-      </c>
-      <c r="C573" s="18" t="s">
-        <v>856</v>
-      </c>
-      <c r="D573" s="19">
-        <v>4301070959</v>
-      </c>
-      <c r="E573" s="18">
-        <v>4607111038616</v>
-      </c>
-      <c r="F573" s="20" t="s">
-        <v>857</v>
+        <v>838</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D573" s="4">
+        <v>4301136070</v>
+      </c>
+      <c r="E573" s="3">
+        <v>4607025784012</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="G573" s="21"/>
       <c r="H573" s="22" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="574" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="17" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B574" s="18" t="s">
-        <v>858</v>
+        <v>604</v>
       </c>
       <c r="C574" s="18" t="s">
-        <v>859</v>
+        <v>605</v>
       </c>
       <c r="D574" s="19">
-        <v>4301070962</v>
+        <v>4301071046</v>
       </c>
       <c r="E574" s="18">
-        <v>4607111038609</v>
+        <v>4607111039354</v>
       </c>
       <c r="F574" s="20" t="s">
-        <v>860</v>
+        <v>606</v>
       </c>
       <c r="G574" s="21"/>
       <c r="H574" s="22" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A575" s="17" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B575" s="18" t="s">
-        <v>250</v>
+        <v>855</v>
       </c>
       <c r="C575" s="18" t="s">
-        <v>251</v>
+        <v>856</v>
       </c>
       <c r="D575" s="19">
-        <v>4301070948</v>
+        <v>4301070959</v>
       </c>
       <c r="E575" s="18">
-        <v>4607111037022</v>
+        <v>4607111038616</v>
       </c>
       <c r="F575" s="20" t="s">
-        <v>150</v>
+        <v>857</v>
       </c>
       <c r="G575" s="21"/>
       <c r="H575" s="22" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A576" s="17" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B576" s="18" t="s">
-        <v>695</v>
+        <v>858</v>
       </c>
       <c r="C576" s="18" t="s">
-        <v>696</v>
+        <v>859</v>
       </c>
       <c r="D576" s="19">
-        <v>4301135570</v>
+        <v>4301070962</v>
       </c>
       <c r="E576" s="18">
-        <v>4607111035806</v>
+        <v>4607111038609</v>
       </c>
       <c r="F576" s="20" t="s">
-        <v>697</v>
+        <v>860</v>
       </c>
       <c r="G576" s="21"/>
       <c r="H576" s="22" t="s">
@@ -19777,22 +19786,22 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" s="17" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B577" s="18" t="s">
-        <v>724</v>
+        <v>250</v>
       </c>
       <c r="C577" s="18" t="s">
-        <v>725</v>
+        <v>251</v>
       </c>
       <c r="D577" s="19">
-        <v>4301071032</v>
+        <v>4301070948</v>
       </c>
       <c r="E577" s="18">
-        <v>4607111038999</v>
+        <v>4607111037022</v>
       </c>
       <c r="F577" s="20" t="s">
-        <v>726</v>
+        <v>150</v>
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
@@ -19801,22 +19810,22 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" s="17" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B578" s="18" t="s">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="C578" s="18" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="D578" s="19">
-        <v>4301071045</v>
+        <v>4301135570</v>
       </c>
       <c r="E578" s="18">
-        <v>4607111039392</v>
+        <v>4607111035806</v>
       </c>
       <c r="F578" s="20" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="G578" s="21"/>
       <c r="H578" s="22" t="s">
@@ -19825,22 +19834,22 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" s="17" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B579" s="18" t="s">
-        <v>479</v>
+        <v>724</v>
       </c>
       <c r="C579" s="18" t="s">
-        <v>480</v>
+        <v>725</v>
       </c>
       <c r="D579" s="19">
-        <v>4301070963</v>
+        <v>4301071032</v>
       </c>
       <c r="E579" s="18">
-        <v>4607111038630</v>
+        <v>4607111038999</v>
       </c>
       <c r="F579" s="20" t="s">
-        <v>481</v>
+        <v>726</v>
       </c>
       <c r="G579" s="21"/>
       <c r="H579" s="22" t="s">
@@ -19849,22 +19858,22 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" s="17" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B580" s="18" t="s">
-        <v>586</v>
+        <v>668</v>
       </c>
       <c r="C580" s="18" t="s">
-        <v>587</v>
+        <v>669</v>
       </c>
       <c r="D580" s="19">
-        <v>4301071054</v>
+        <v>4301071045</v>
       </c>
       <c r="E580" s="18">
-        <v>4607111035639</v>
+        <v>4607111039392</v>
       </c>
       <c r="F580" s="20" t="s">
-        <v>588</v>
+        <v>670</v>
       </c>
       <c r="G580" s="21"/>
       <c r="H580" s="22" t="s">
@@ -19873,30 +19882,78 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="17" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B581" s="18" t="s">
-        <v>336</v>
+        <v>479</v>
       </c>
       <c r="C581" s="18" t="s">
-        <v>556</v>
+        <v>480</v>
       </c>
       <c r="D581" s="19">
-        <v>4301135540</v>
+        <v>4301070963</v>
       </c>
       <c r="E581" s="18">
-        <v>4607111035646</v>
+        <v>4607111038630</v>
       </c>
       <c r="F581" s="20" t="s">
-        <v>557</v>
+        <v>481</v>
       </c>
       <c r="G581" s="21"/>
       <c r="H581" s="22" t="s">
         <v>849</v>
       </c>
     </row>
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A582" s="17" t="s">
+        <v>847</v>
+      </c>
+      <c r="B582" s="18" t="s">
+        <v>586</v>
+      </c>
+      <c r="C582" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="D582" s="19">
+        <v>4301071054</v>
+      </c>
+      <c r="E582" s="18">
+        <v>4607111035639</v>
+      </c>
+      <c r="F582" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="G582" s="21"/>
+      <c r="H582" s="22" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A583" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="B583" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C583" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="D583" s="19">
+        <v>4301135540</v>
+      </c>
+      <c r="E583" s="18">
+        <v>4607111035646</v>
+      </c>
+      <c r="F583" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="G583" s="21"/>
+      <c r="H583" s="22" t="s">
+        <v>849</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F581" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
+  <autoFilter ref="A1:F583" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F256">
       <sortCondition ref="A1:A187"/>
     </sortState>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332C59DA-D947-4EFA-AF1E-73C3535C9F0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26134F9E-DF8C-463E-A245-083967857062}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$583</definedName>
-    <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$522</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$584</definedName>
+    <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$523</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2514" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2518" uniqueCount="1045">
   <si>
     <t>1С</t>
   </si>
@@ -3165,6 +3165,15 @@
   </si>
   <si>
     <t>Изделия хлебобулочные «Хрустипай манго чили» Фикс.вес 0,18 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>Пельмени «Медвежье ушко Премиум Мясные» 0,8 классическая форма ТМ «Медвежье ушко»</t>
+  </si>
+  <si>
+    <t>SU004022</t>
+  </si>
+  <si>
+    <t>P005158</t>
   </si>
 </sst>
 </file>
@@ -6420,7 +6429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H583"/>
+  <dimension ref="A1:H584"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88" style="11" customWidth="1"/>
@@ -18465,47 +18474,44 @@
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A522" s="17" t="s">
-        <v>788</v>
-      </c>
-      <c r="B522" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="C522" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="D522" s="19">
-        <v>4301071038</v>
-      </c>
-      <c r="E522" s="18">
-        <v>4607111039248</v>
-      </c>
-      <c r="F522" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="G522" s="21"/>
-      <c r="H522" s="22" t="s">
-        <v>849</v>
-      </c>
+      <c r="A522" s="10" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D522" s="4">
+        <v>4301071112</v>
+      </c>
+      <c r="E522" s="3">
+        <v>4620207491256</v>
+      </c>
+      <c r="F522" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="17" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B523" s="18" t="s">
-        <v>106</v>
+        <v>616</v>
       </c>
       <c r="C523" s="18" t="s">
-        <v>257</v>
+        <v>617</v>
       </c>
       <c r="D523" s="19">
-        <v>4301070981</v>
+        <v>4301071038</v>
       </c>
       <c r="E523" s="18">
-        <v>4607111036728</v>
+        <v>4607111039248</v>
       </c>
       <c r="F523" s="20" t="s">
-        <v>258</v>
+        <v>618</v>
       </c>
       <c r="G523" s="21"/>
       <c r="H523" s="22" t="s">
@@ -18514,22 +18520,22 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="17" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B524" s="18" t="s">
-        <v>624</v>
+        <v>106</v>
       </c>
       <c r="C524" s="18" t="s">
-        <v>625</v>
+        <v>257</v>
       </c>
       <c r="D524" s="19">
-        <v>4301071039</v>
+        <v>4301070981</v>
       </c>
       <c r="E524" s="18">
-        <v>4607111039279</v>
+        <v>4607111036728</v>
       </c>
       <c r="F524" s="20" t="s">
-        <v>626</v>
+        <v>258</v>
       </c>
       <c r="G524" s="21"/>
       <c r="H524" s="22" t="s">
@@ -18538,22 +18544,22 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="17" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B525" s="18" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C525" s="18" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="D525" s="19">
-        <v>4301071051</v>
+        <v>4301071039</v>
       </c>
       <c r="E525" s="18">
-        <v>4607111039262</v>
+        <v>4607111039279</v>
       </c>
       <c r="F525" s="20" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="G525" s="21"/>
       <c r="H525" s="22" t="s">
@@ -18562,22 +18568,22 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="17" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B526" s="18" t="s">
-        <v>289</v>
+        <v>612</v>
       </c>
       <c r="C526" s="18" t="s">
-        <v>290</v>
+        <v>613</v>
       </c>
       <c r="D526" s="19">
-        <v>4301132080</v>
+        <v>4301071051</v>
       </c>
       <c r="E526" s="18">
-        <v>4640242180397</v>
+        <v>4607111039262</v>
       </c>
       <c r="F526" s="20" t="s">
-        <v>291</v>
+        <v>614</v>
       </c>
       <c r="G526" s="21"/>
       <c r="H526" s="22" t="s">
@@ -18586,22 +18592,22 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="17" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B527" s="18" t="s">
-        <v>111</v>
+        <v>289</v>
       </c>
       <c r="C527" s="18" t="s">
-        <v>520</v>
+        <v>290</v>
       </c>
       <c r="D527" s="19">
-        <v>4301071029</v>
+        <v>4301132080</v>
       </c>
       <c r="E527" s="18">
-        <v>4607111035899</v>
+        <v>4640242180397</v>
       </c>
       <c r="F527" s="20" t="s">
-        <v>112</v>
+        <v>291</v>
       </c>
       <c r="G527" s="21"/>
       <c r="H527" s="22" t="s">
@@ -18610,22 +18616,22 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="17" t="s">
-        <v>794</v>
-      </c>
-      <c r="B528" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C528" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D528" s="4">
-        <v>4301136053</v>
-      </c>
-      <c r="E528" s="3">
-        <v>4640242180236</v>
-      </c>
-      <c r="F528" s="5" t="s">
-        <v>300</v>
+        <v>793</v>
+      </c>
+      <c r="B528" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C528" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="D528" s="19">
+        <v>4301071029</v>
+      </c>
+      <c r="E528" s="18">
+        <v>4607111035899</v>
+      </c>
+      <c r="F528" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="G528" s="21"/>
       <c r="H528" s="22" t="s">
@@ -18634,22 +18640,22 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="17" t="s">
-        <v>795</v>
-      </c>
-      <c r="B529" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="C529" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="D529" s="19">
-        <v>4301070977</v>
-      </c>
-      <c r="E529" s="18">
-        <v>4607111037411</v>
-      </c>
-      <c r="F529" s="20" t="s">
-        <v>316</v>
+        <v>794</v>
+      </c>
+      <c r="B529" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D529" s="4">
+        <v>4301136053</v>
+      </c>
+      <c r="E529" s="3">
+        <v>4640242180236</v>
+      </c>
+      <c r="F529" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="G529" s="21"/>
       <c r="H529" s="22" t="s">
@@ -18658,22 +18664,22 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="17" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B530" s="18" t="s">
-        <v>549</v>
+        <v>314</v>
       </c>
       <c r="C530" s="18" t="s">
-        <v>550</v>
+        <v>315</v>
       </c>
       <c r="D530" s="19">
-        <v>4301135375</v>
+        <v>4301070977</v>
       </c>
       <c r="E530" s="18">
-        <v>4640242181486</v>
+        <v>4607111037411</v>
       </c>
       <c r="F530" s="20" t="s">
-        <v>551</v>
+        <v>316</v>
       </c>
       <c r="G530" s="21"/>
       <c r="H530" s="22" t="s">
@@ -18682,70 +18688,70 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="17" t="s">
-        <v>797</v>
-      </c>
-      <c r="B531" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="C531" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="D531" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E531" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F531" s="5" t="s">
-        <v>942</v>
+        <v>796</v>
+      </c>
+      <c r="B531" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="C531" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="D531" s="19">
+        <v>4301135375</v>
+      </c>
+      <c r="E531" s="18">
+        <v>4640242181486</v>
+      </c>
+      <c r="F531" s="20" t="s">
+        <v>551</v>
       </c>
       <c r="G531" s="21"/>
-      <c r="H531" s="16" t="s">
-        <v>936</v>
+      <c r="H531" s="22" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="17" t="s">
-        <v>798</v>
-      </c>
-      <c r="B532" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C532" s="18" t="s">
-        <v>627</v>
-      </c>
-      <c r="D532" s="19">
-        <v>4301071050</v>
-      </c>
-      <c r="E532" s="18">
-        <v>4607111036216</v>
-      </c>
-      <c r="F532" s="20" t="s">
-        <v>628</v>
+        <v>797</v>
+      </c>
+      <c r="B532" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="D532" s="4">
+        <v>4301135760</v>
+      </c>
+      <c r="E532" s="3">
+        <v>4620207491010</v>
+      </c>
+      <c r="F532" s="5" t="s">
+        <v>942</v>
       </c>
       <c r="G532" s="21"/>
-      <c r="H532" s="22" t="s">
-        <v>849</v>
+      <c r="H532" s="16" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="17" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B533" s="18" t="s">
-        <v>620</v>
+        <v>110</v>
       </c>
       <c r="C533" s="18" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D533" s="19">
-        <v>4301071049</v>
+        <v>4301071050</v>
       </c>
       <c r="E533" s="18">
-        <v>4607111039293</v>
+        <v>4607111036216</v>
       </c>
       <c r="F533" s="20" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="G533" s="21"/>
       <c r="H533" s="22" t="s">
@@ -18754,22 +18760,22 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="17" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B534" s="18" t="s">
-        <v>647</v>
+        <v>620</v>
       </c>
       <c r="C534" s="18" t="s">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="D534" s="19">
-        <v>4301135532</v>
+        <v>4301071049</v>
       </c>
       <c r="E534" s="18">
-        <v>4607111033994</v>
+        <v>4607111039293</v>
       </c>
       <c r="F534" s="20" t="s">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="G534" s="21"/>
       <c r="H534" s="22" t="s">
@@ -18778,22 +18784,22 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="17" t="s">
-        <v>801</v>
-      </c>
-      <c r="B535" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="C535" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="D535" s="4">
-        <v>4301135555</v>
-      </c>
-      <c r="E535" s="3">
-        <v>4607111034014</v>
-      </c>
-      <c r="F535" s="5" t="s">
-        <v>652</v>
+        <v>800</v>
+      </c>
+      <c r="B535" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="C535" s="18" t="s">
+        <v>648</v>
+      </c>
+      <c r="D535" s="19">
+        <v>4301135532</v>
+      </c>
+      <c r="E535" s="18">
+        <v>4607111033994</v>
+      </c>
+      <c r="F535" s="20" t="s">
+        <v>649</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="22" t="s">
@@ -18802,70 +18808,70 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="17" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>933</v>
+        <v>650</v>
       </c>
       <c r="C536" s="3" t="s">
-        <v>934</v>
+        <v>651</v>
       </c>
       <c r="D536" s="4">
-        <v>4301135793</v>
+        <v>4301135555</v>
       </c>
       <c r="E536" s="3">
-        <v>4620207491003</v>
+        <v>4607111034014</v>
       </c>
       <c r="F536" s="5" t="s">
-        <v>935</v>
+        <v>652</v>
       </c>
       <c r="G536" s="21"/>
-      <c r="H536" s="16" t="s">
-        <v>936</v>
+      <c r="H536" s="22" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="17" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>378</v>
+        <v>933</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>379</v>
+        <v>934</v>
       </c>
       <c r="D537" s="4">
-        <v>4301136052</v>
+        <v>4301135793</v>
       </c>
       <c r="E537" s="3">
-        <v>4640242180410</v>
+        <v>4620207491003</v>
       </c>
       <c r="F537" s="5" t="s">
-        <v>380</v>
+        <v>935</v>
       </c>
       <c r="G537" s="21"/>
-      <c r="H537" s="22" t="s">
-        <v>849</v>
+      <c r="H537" s="16" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="17" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>545</v>
+        <v>378</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>546</v>
+        <v>379</v>
       </c>
       <c r="D538" s="4">
-        <v>4301135518</v>
+        <v>4301136052</v>
       </c>
       <c r="E538" s="3">
-        <v>4640242181561</v>
+        <v>4640242180410</v>
       </c>
       <c r="F538" s="5" t="s">
-        <v>547</v>
+        <v>380</v>
       </c>
       <c r="G538" s="21"/>
       <c r="H538" s="22" t="s">
@@ -18874,22 +18880,22 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="17" t="s">
-        <v>805</v>
-      </c>
-      <c r="B539" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="C539" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="D539" s="19">
-        <v>4301135374</v>
-      </c>
-      <c r="E539" s="18">
-        <v>4640242181424</v>
-      </c>
-      <c r="F539" s="20" t="s">
-        <v>597</v>
+        <v>804</v>
+      </c>
+      <c r="B539" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D539" s="4">
+        <v>4301135518</v>
+      </c>
+      <c r="E539" s="3">
+        <v>4640242181561</v>
+      </c>
+      <c r="F539" s="5" t="s">
+        <v>547</v>
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="22" t="s">
@@ -18898,22 +18904,22 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B540" s="18" t="s">
-        <v>850</v>
+        <v>595</v>
       </c>
       <c r="C540" s="18" t="s">
-        <v>851</v>
+        <v>596</v>
       </c>
       <c r="D540" s="19">
-        <v>4301132079</v>
+        <v>4301135374</v>
       </c>
       <c r="E540" s="18">
-        <v>4607111038487</v>
+        <v>4640242181424</v>
       </c>
       <c r="F540" s="20" t="s">
-        <v>421</v>
+        <v>597</v>
       </c>
       <c r="G540" s="21"/>
       <c r="H540" s="22" t="s">
@@ -18922,22 +18928,22 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="17" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B541" s="18" t="s">
-        <v>160</v>
+        <v>850</v>
       </c>
       <c r="C541" s="18" t="s">
-        <v>630</v>
+        <v>851</v>
       </c>
       <c r="D541" s="19">
-        <v>4301071056</v>
+        <v>4301132079</v>
       </c>
       <c r="E541" s="18">
-        <v>4640242180250</v>
+        <v>4607111038487</v>
       </c>
       <c r="F541" s="20" t="s">
-        <v>631</v>
+        <v>421</v>
       </c>
       <c r="G541" s="21"/>
       <c r="H541" s="22" t="s">
@@ -18946,22 +18952,22 @@
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="17" t="s">
-        <v>808</v>
-      </c>
-      <c r="B542" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C542" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D542" s="4">
-        <v>4301136051</v>
-      </c>
-      <c r="E542" s="3">
-        <v>4640242180304</v>
-      </c>
-      <c r="F542" s="5" t="s">
-        <v>297</v>
+        <v>807</v>
+      </c>
+      <c r="B542" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C542" s="18" t="s">
+        <v>630</v>
+      </c>
+      <c r="D542" s="19">
+        <v>4301071056</v>
+      </c>
+      <c r="E542" s="18">
+        <v>4640242180250</v>
+      </c>
+      <c r="F542" s="20" t="s">
+        <v>631</v>
       </c>
       <c r="G542" s="21"/>
       <c r="H542" s="22" t="s">
@@ -18970,22 +18976,22 @@
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1001</v>
+        <v>295</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>1002</v>
+        <v>296</v>
       </c>
       <c r="D543" s="4">
-        <v>4301071109</v>
+        <v>4301136051</v>
       </c>
       <c r="E543" s="3">
-        <v>4607111035929</v>
+        <v>4640242180304</v>
       </c>
       <c r="F543" s="5" t="s">
-        <v>1003</v>
+        <v>297</v>
       </c>
       <c r="G543" s="21"/>
       <c r="H543" s="22" t="s">
@@ -18994,22 +19000,22 @@
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="17" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>738</v>
+        <v>1001</v>
       </c>
       <c r="C544" s="3" t="s">
-        <v>739</v>
+        <v>1002</v>
       </c>
       <c r="D544" s="4">
-        <v>4301135550</v>
+        <v>4301071109</v>
       </c>
       <c r="E544" s="3">
-        <v>4607111034199</v>
+        <v>4607111035929</v>
       </c>
       <c r="F544" s="5" t="s">
-        <v>740</v>
+        <v>1003</v>
       </c>
       <c r="G544" s="21"/>
       <c r="H544" s="22" t="s">
@@ -19018,22 +19024,22 @@
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="17" t="s">
-        <v>811</v>
-      </c>
-      <c r="B545" s="18" t="s">
-        <v>735</v>
-      </c>
-      <c r="C545" s="18" t="s">
-        <v>736</v>
-      </c>
-      <c r="D545" s="19">
-        <v>4301132186</v>
-      </c>
-      <c r="E545" s="18">
-        <v>4607111036520</v>
-      </c>
-      <c r="F545" s="20" t="s">
-        <v>737</v>
+        <v>810</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D545" s="4">
+        <v>4301135550</v>
+      </c>
+      <c r="E545" s="3">
+        <v>4607111034199</v>
+      </c>
+      <c r="F545" s="5" t="s">
+        <v>740</v>
       </c>
       <c r="G545" s="21"/>
       <c r="H545" s="22" t="s">
@@ -19042,22 +19048,22 @@
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="17" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B546" s="18" t="s">
-        <v>608</v>
+        <v>735</v>
       </c>
       <c r="C546" s="18" t="s">
-        <v>609</v>
+        <v>736</v>
       </c>
       <c r="D546" s="19">
-        <v>4301071047</v>
+        <v>4301132186</v>
       </c>
       <c r="E546" s="18">
-        <v>4607111039330</v>
+        <v>4607111036520</v>
       </c>
       <c r="F546" s="20" t="s">
-        <v>610</v>
+        <v>737</v>
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
@@ -19066,22 +19072,22 @@
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="17" t="s">
-        <v>813</v>
-      </c>
-      <c r="B547" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="C547" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D547" s="4">
-        <v>4301131047</v>
-      </c>
-      <c r="E547" s="3">
-        <v>4607111034120</v>
-      </c>
-      <c r="F547" s="5" t="s">
-        <v>779</v>
+        <v>812</v>
+      </c>
+      <c r="B547" s="18" t="s">
+        <v>608</v>
+      </c>
+      <c r="C547" s="18" t="s">
+        <v>609</v>
+      </c>
+      <c r="D547" s="19">
+        <v>4301071047</v>
+      </c>
+      <c r="E547" s="18">
+        <v>4607111039330</v>
+      </c>
+      <c r="F547" s="20" t="s">
+        <v>610</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
@@ -19090,70 +19096,70 @@
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="17" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>896</v>
+        <v>777</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>897</v>
+        <v>778</v>
       </c>
       <c r="D548" s="4">
-        <v>4301135763</v>
+        <v>4301131047</v>
       </c>
       <c r="E548" s="3">
-        <v>4620207491027</v>
+        <v>4607111034120</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>898</v>
+        <v>779</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
-        <v>955</v>
+        <v>849</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="17" t="s">
-        <v>815</v>
-      </c>
-      <c r="B549" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="C549" s="18" t="s">
-        <v>554</v>
-      </c>
-      <c r="D549" s="19">
-        <v>4301135405</v>
-      </c>
-      <c r="E549" s="18">
-        <v>4640242181523</v>
-      </c>
-      <c r="F549" s="20" t="s">
-        <v>555</v>
+        <v>814</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="D549" s="4">
+        <v>4301135763</v>
+      </c>
+      <c r="E549" s="3">
+        <v>4620207491027</v>
+      </c>
+      <c r="F549" s="5" t="s">
+        <v>898</v>
       </c>
       <c r="G549" s="21"/>
       <c r="H549" s="22" t="s">
-        <v>849</v>
+        <v>955</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="17" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B550" s="18" t="s">
-        <v>702</v>
+        <v>553</v>
       </c>
       <c r="C550" s="18" t="s">
-        <v>703</v>
+        <v>554</v>
       </c>
       <c r="D550" s="19">
-        <v>4301135402</v>
+        <v>4301135405</v>
       </c>
       <c r="E550" s="18">
-        <v>4640242181493</v>
+        <v>4640242181523</v>
       </c>
       <c r="F550" s="20" t="s">
-        <v>701</v>
+        <v>555</v>
       </c>
       <c r="G550" s="21"/>
       <c r="H550" s="22" t="s">
@@ -19162,22 +19168,22 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="17" t="s">
-        <v>817</v>
-      </c>
-      <c r="B551" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="C551" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="D551" s="4">
-        <v>4301131046</v>
-      </c>
-      <c r="E551" s="3">
-        <v>4607111034137</v>
-      </c>
-      <c r="F551" s="5" t="s">
-        <v>877</v>
+        <v>816</v>
+      </c>
+      <c r="B551" s="18" t="s">
+        <v>702</v>
+      </c>
+      <c r="C551" s="18" t="s">
+        <v>703</v>
+      </c>
+      <c r="D551" s="19">
+        <v>4301135402</v>
+      </c>
+      <c r="E551" s="18">
+        <v>4640242181493</v>
+      </c>
+      <c r="F551" s="20" t="s">
+        <v>701</v>
       </c>
       <c r="G551" s="21"/>
       <c r="H551" s="22" t="s">
@@ -19186,22 +19192,22 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="17" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="D552" s="4">
-        <v>4301136079</v>
+        <v>4301131046</v>
       </c>
       <c r="E552" s="3">
-        <v>4607025784319</v>
+        <v>4607111034137</v>
       </c>
       <c r="F552" s="5" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
@@ -19210,22 +19216,22 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="17" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>949</v>
+        <v>881</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>950</v>
+        <v>882</v>
       </c>
       <c r="D553" s="4">
-        <v>4301135753</v>
+        <v>4301136079</v>
       </c>
       <c r="E553" s="3">
-        <v>4620207490914</v>
+        <v>4607025784319</v>
       </c>
       <c r="F553" s="5" t="s">
-        <v>951</v>
+        <v>883</v>
       </c>
       <c r="G553" s="21"/>
       <c r="H553" s="22" t="s">
@@ -19234,70 +19240,70 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="D554" s="4">
-        <v>4301135778</v>
+        <v>4301135753</v>
       </c>
       <c r="E554" s="3">
-        <v>4620207490853</v>
+        <v>4620207490914</v>
       </c>
       <c r="F554" s="5" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="G554" s="21"/>
-      <c r="H554" s="16" t="s">
-        <v>943</v>
+      <c r="H554" s="22" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>865</v>
+        <v>937</v>
       </c>
       <c r="C555" s="3" t="s">
-        <v>866</v>
+        <v>938</v>
       </c>
       <c r="D555" s="4">
-        <v>4301132179</v>
+        <v>4301135778</v>
       </c>
       <c r="E555" s="3">
-        <v>4607111035691</v>
+        <v>4620207490853</v>
       </c>
       <c r="F555" s="5" t="s">
-        <v>867</v>
+        <v>939</v>
       </c>
       <c r="G555" s="21"/>
-      <c r="H555" s="22" t="s">
-        <v>849</v>
+      <c r="H555" s="16" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="17" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>732</v>
+        <v>865</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>733</v>
+        <v>866</v>
       </c>
       <c r="D556" s="4">
-        <v>4301132190</v>
+        <v>4301132179</v>
       </c>
       <c r="E556" s="3">
-        <v>4607111036537</v>
+        <v>4607111035691</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>734</v>
+        <v>867</v>
       </c>
       <c r="G556" s="21"/>
       <c r="H556" s="22" t="s">
@@ -19306,22 +19312,22 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="17" t="s">
-        <v>823</v>
-      </c>
-      <c r="B557" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="C557" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D557" s="19">
-        <v>4301131019</v>
-      </c>
-      <c r="E557" s="18">
-        <v>4640242180427</v>
-      </c>
-      <c r="F557" s="20" t="s">
-        <v>373</v>
+        <v>822</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="D557" s="4">
+        <v>4301132190</v>
+      </c>
+      <c r="E557" s="3">
+        <v>4607111036537</v>
+      </c>
+      <c r="F557" s="5" t="s">
+        <v>734</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
@@ -19330,22 +19336,22 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="17" t="s">
-        <v>824</v>
-      </c>
-      <c r="B558" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="C558" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="D558" s="4">
-        <v>4301135571</v>
-      </c>
-      <c r="E558" s="3">
-        <v>4607111035028</v>
-      </c>
-      <c r="F558" s="5" t="s">
-        <v>886</v>
+        <v>823</v>
+      </c>
+      <c r="B558" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C558" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D558" s="19">
+        <v>4301131019</v>
+      </c>
+      <c r="E558" s="18">
+        <v>4640242180427</v>
+      </c>
+      <c r="F558" s="20" t="s">
+        <v>373</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="22" t="s">
@@ -19354,70 +19360,70 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="D559" s="4">
+        <v>4301135571</v>
+      </c>
+      <c r="E559" s="3">
+        <v>4607111035028</v>
+      </c>
+      <c r="F559" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="G559" s="21"/>
+      <c r="H559" s="22" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A560" s="17" t="s">
         <v>825</v>
       </c>
-      <c r="B559" s="3" t="s">
+      <c r="B560" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="C559" s="3" t="s">
+      <c r="C560" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D559" s="4">
+      <c r="D560" s="4">
         <v>4301135768</v>
       </c>
-      <c r="E559" s="3">
+      <c r="E560" s="3">
         <v>4620207491034</v>
       </c>
-      <c r="F559" s="5" t="s">
+      <c r="F560" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="G559" s="21"/>
-      <c r="H559" s="16" t="s">
+      <c r="G560" s="21"/>
+      <c r="H560" s="16" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="560" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A560" s="17" t="s">
+    <row r="561" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A561" s="17" t="s">
         <v>827</v>
       </c>
-      <c r="B560" s="18" t="s">
+      <c r="B561" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="C560" s="18" t="s">
+      <c r="C561" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="D560" s="19">
+      <c r="D561" s="19">
         <v>4301070960</v>
       </c>
-      <c r="E560" s="18">
+      <c r="E561" s="18">
         <v>4607111038623</v>
       </c>
-      <c r="F560" s="20" t="s">
+      <c r="F561" s="20" t="s">
         <v>485</v>
-      </c>
-      <c r="G560" s="21"/>
-      <c r="H560" s="22" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A561" s="17" t="s">
-        <v>828</v>
-      </c>
-      <c r="B561" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C561" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="D561" s="19">
-        <v>4301070966</v>
-      </c>
-      <c r="E561" s="18">
-        <v>4607111038135</v>
-      </c>
-      <c r="F561" s="20" t="s">
-        <v>363</v>
       </c>
       <c r="G561" s="21"/>
       <c r="H561" s="22" t="s">
@@ -19425,71 +19431,71 @@
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A562" s="10" t="s">
+      <c r="A562" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="B562" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="C562" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="D562" s="19">
+        <v>4301070966</v>
+      </c>
+      <c r="E562" s="18">
+        <v>4607111038135</v>
+      </c>
+      <c r="F562" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="G562" s="21"/>
+      <c r="H562" s="22" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A563" s="10" t="s">
         <v>893</v>
       </c>
-      <c r="B562" s="3" t="s">
+      <c r="B563" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="C562" s="3" t="s">
+      <c r="C563" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="D562" s="4">
+      <c r="D563" s="4">
         <v>4301070990</v>
       </c>
-      <c r="E562" s="3">
+      <c r="E563" s="3">
         <v>4607111038494</v>
       </c>
-      <c r="F562" s="5" t="s">
+      <c r="F563" s="5" t="s">
         <v>854</v>
       </c>
-      <c r="G562" s="1"/>
-      <c r="H562" s="16" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A563" s="17" t="s">
-        <v>829</v>
-      </c>
-      <c r="B563" s="18" t="s">
-        <v>852</v>
-      </c>
-      <c r="C563" s="18" t="s">
-        <v>853</v>
-      </c>
-      <c r="D563" s="19">
-        <v>4301070990</v>
-      </c>
-      <c r="E563" s="18">
-        <v>4607111038494</v>
-      </c>
-      <c r="F563" s="20" t="s">
-        <v>854</v>
-      </c>
-      <c r="G563" s="21"/>
-      <c r="H563" s="22" t="s">
+      <c r="G563" s="1"/>
+      <c r="H563" s="16" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="17" t="s">
-        <v>830</v>
-      </c>
-      <c r="B564" s="3" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C564" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D564" s="4">
-        <v>4301071107</v>
-      </c>
-      <c r="E564" s="3">
-        <v>4607111035905</v>
-      </c>
-      <c r="F564" s="5" t="s">
-        <v>1020</v>
+        <v>829</v>
+      </c>
+      <c r="B564" s="18" t="s">
+        <v>852</v>
+      </c>
+      <c r="C564" s="18" t="s">
+        <v>853</v>
+      </c>
+      <c r="D564" s="19">
+        <v>4301070990</v>
+      </c>
+      <c r="E564" s="18">
+        <v>4607111038494</v>
+      </c>
+      <c r="F564" s="20" t="s">
+        <v>854</v>
       </c>
       <c r="G564" s="21"/>
       <c r="H564" s="22" t="s">
@@ -19498,22 +19504,22 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="D565" s="4">
-        <v>4301135824</v>
+        <v>4301071107</v>
       </c>
       <c r="E565" s="3">
-        <v>4607111039095</v>
+        <v>4607111035905</v>
       </c>
       <c r="F565" s="5" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="G565" s="21"/>
       <c r="H565" s="22" t="s">
@@ -19522,22 +19528,22 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="17" t="s">
-        <v>832</v>
-      </c>
-      <c r="B566" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C566" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="D566" s="19">
-        <v>4301135285</v>
-      </c>
-      <c r="E566" s="18">
-        <v>4607111036407</v>
-      </c>
-      <c r="F566" s="20" t="s">
-        <v>182</v>
+        <v>831</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D566" s="4">
+        <v>4301135824</v>
+      </c>
+      <c r="E566" s="3">
+        <v>4607111039095</v>
+      </c>
+      <c r="F566" s="5" t="s">
+        <v>1009</v>
       </c>
       <c r="G566" s="21"/>
       <c r="H566" s="22" t="s">
@@ -19546,22 +19552,22 @@
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="17" t="s">
-        <v>708</v>
-      </c>
-      <c r="B567" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="C567" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="D567" s="4">
-        <v>4301135607</v>
-      </c>
-      <c r="E567" s="3">
-        <v>4607111039613</v>
-      </c>
-      <c r="F567" s="5" t="s">
-        <v>708</v>
+        <v>832</v>
+      </c>
+      <c r="B567" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C567" s="18" t="s">
+        <v>522</v>
+      </c>
+      <c r="D567" s="19">
+        <v>4301135285</v>
+      </c>
+      <c r="E567" s="18">
+        <v>4607111036407</v>
+      </c>
+      <c r="F567" s="20" t="s">
+        <v>182</v>
       </c>
       <c r="G567" s="21"/>
       <c r="H567" s="22" t="s">
@@ -19570,22 +19576,22 @@
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="17" t="s">
-        <v>833</v>
-      </c>
-      <c r="B568" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C568" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D568" s="19">
-        <v>4301080153</v>
-      </c>
-      <c r="E568" s="18">
-        <v>4607111036827</v>
-      </c>
-      <c r="F568" s="20" t="s">
-        <v>127</v>
+        <v>708</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D568" s="4">
+        <v>4301135607</v>
+      </c>
+      <c r="E568" s="3">
+        <v>4607111039613</v>
+      </c>
+      <c r="F568" s="5" t="s">
+        <v>708</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19594,22 +19600,22 @@
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" s="17" t="s">
-        <v>834</v>
-      </c>
-      <c r="B569" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="C569" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="D569" s="4">
-        <v>4301135574</v>
-      </c>
-      <c r="E569" s="3">
-        <v>4607111033659</v>
-      </c>
-      <c r="F569" s="5" t="s">
-        <v>722</v>
+        <v>833</v>
+      </c>
+      <c r="B569" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C569" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D569" s="19">
+        <v>4301080153</v>
+      </c>
+      <c r="E569" s="18">
+        <v>4607111036827</v>
+      </c>
+      <c r="F569" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
@@ -19618,22 +19624,22 @@
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" s="17" t="s">
-        <v>835</v>
-      </c>
-      <c r="B570" s="18" t="s">
-        <v>664</v>
-      </c>
-      <c r="C570" s="18" t="s">
-        <v>665</v>
-      </c>
-      <c r="D570" s="19">
-        <v>4301071044</v>
-      </c>
-      <c r="E570" s="18">
-        <v>4607111039385</v>
-      </c>
-      <c r="F570" s="20" t="s">
-        <v>666</v>
+        <v>834</v>
+      </c>
+      <c r="B570" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="D570" s="4">
+        <v>4301135574</v>
+      </c>
+      <c r="E570" s="3">
+        <v>4607111033659</v>
+      </c>
+      <c r="F570" s="5" t="s">
+        <v>722</v>
       </c>
       <c r="G570" s="21"/>
       <c r="H570" s="22" t="s">
@@ -19642,22 +19648,22 @@
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="17" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B571" s="18" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="C571" s="18" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="D571" s="19">
-        <v>4301071031</v>
+        <v>4301071044</v>
       </c>
       <c r="E571" s="18">
-        <v>4607111038982</v>
+        <v>4607111039385</v>
       </c>
       <c r="F571" s="20" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="G571" s="21"/>
       <c r="H571" s="22" t="s">
@@ -19666,22 +19672,22 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B572" s="18" t="s">
-        <v>177</v>
+        <v>681</v>
       </c>
       <c r="C572" s="18" t="s">
-        <v>178</v>
+        <v>682</v>
       </c>
       <c r="D572" s="19">
-        <v>4301070917</v>
+        <v>4301071031</v>
       </c>
       <c r="E572" s="18">
-        <v>4607111035912</v>
+        <v>4607111038982</v>
       </c>
       <c r="F572" s="20" t="s">
-        <v>179</v>
+        <v>683</v>
       </c>
       <c r="G572" s="21"/>
       <c r="H572" s="22" t="s">
@@ -19690,22 +19696,22 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="17" t="s">
-        <v>838</v>
-      </c>
-      <c r="B573" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C573" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D573" s="4">
-        <v>4301136070</v>
-      </c>
-      <c r="E573" s="3">
-        <v>4607025784012</v>
-      </c>
-      <c r="F573" s="5" t="s">
-        <v>166</v>
+        <v>837</v>
+      </c>
+      <c r="B573" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C573" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="D573" s="19">
+        <v>4301070917</v>
+      </c>
+      <c r="E573" s="18">
+        <v>4607111035912</v>
+      </c>
+      <c r="F573" s="20" t="s">
+        <v>179</v>
       </c>
       <c r="G573" s="21"/>
       <c r="H573" s="22" t="s">
@@ -19714,46 +19720,46 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="17" t="s">
-        <v>839</v>
-      </c>
-      <c r="B574" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="C574" s="18" t="s">
-        <v>605</v>
-      </c>
-      <c r="D574" s="19">
-        <v>4301071046</v>
-      </c>
-      <c r="E574" s="18">
-        <v>4607111039354</v>
-      </c>
-      <c r="F574" s="20" t="s">
-        <v>606</v>
+        <v>838</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D574" s="4">
+        <v>4301136070</v>
+      </c>
+      <c r="E574" s="3">
+        <v>4607025784012</v>
+      </c>
+      <c r="F574" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="G574" s="21"/>
       <c r="H574" s="22" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="575" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="17" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B575" s="18" t="s">
-        <v>855</v>
+        <v>604</v>
       </c>
       <c r="C575" s="18" t="s">
-        <v>856</v>
+        <v>605</v>
       </c>
       <c r="D575" s="19">
-        <v>4301070959</v>
+        <v>4301071046</v>
       </c>
       <c r="E575" s="18">
-        <v>4607111038616</v>
+        <v>4607111039354</v>
       </c>
       <c r="F575" s="20" t="s">
-        <v>857</v>
+        <v>606</v>
       </c>
       <c r="G575" s="21"/>
       <c r="H575" s="22" t="s">
@@ -19762,46 +19768,46 @@
     </row>
     <row r="576" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A576" s="17" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B576" s="18" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C576" s="18" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D576" s="19">
-        <v>4301070962</v>
+        <v>4301070959</v>
       </c>
       <c r="E576" s="18">
-        <v>4607111038609</v>
+        <v>4607111038616</v>
       </c>
       <c r="F576" s="20" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="G576" s="21"/>
       <c r="H576" s="22" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A577" s="17" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B577" s="18" t="s">
-        <v>250</v>
+        <v>858</v>
       </c>
       <c r="C577" s="18" t="s">
-        <v>251</v>
+        <v>859</v>
       </c>
       <c r="D577" s="19">
-        <v>4301070948</v>
+        <v>4301070962</v>
       </c>
       <c r="E577" s="18">
-        <v>4607111037022</v>
+        <v>4607111038609</v>
       </c>
       <c r="F577" s="20" t="s">
-        <v>150</v>
+        <v>860</v>
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
@@ -19810,22 +19816,22 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B578" s="18" t="s">
-        <v>695</v>
+        <v>250</v>
       </c>
       <c r="C578" s="18" t="s">
-        <v>696</v>
+        <v>251</v>
       </c>
       <c r="D578" s="19">
-        <v>4301135570</v>
+        <v>4301070948</v>
       </c>
       <c r="E578" s="18">
-        <v>4607111035806</v>
+        <v>4607111037022</v>
       </c>
       <c r="F578" s="20" t="s">
-        <v>697</v>
+        <v>150</v>
       </c>
       <c r="G578" s="21"/>
       <c r="H578" s="22" t="s">
@@ -19834,22 +19840,22 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" s="17" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B579" s="18" t="s">
-        <v>724</v>
+        <v>695</v>
       </c>
       <c r="C579" s="18" t="s">
-        <v>725</v>
+        <v>696</v>
       </c>
       <c r="D579" s="19">
-        <v>4301071032</v>
+        <v>4301135570</v>
       </c>
       <c r="E579" s="18">
-        <v>4607111038999</v>
+        <v>4607111035806</v>
       </c>
       <c r="F579" s="20" t="s">
-        <v>726</v>
+        <v>697</v>
       </c>
       <c r="G579" s="21"/>
       <c r="H579" s="22" t="s">
@@ -19858,22 +19864,22 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" s="17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B580" s="18" t="s">
-        <v>668</v>
+        <v>724</v>
       </c>
       <c r="C580" s="18" t="s">
-        <v>669</v>
+        <v>725</v>
       </c>
       <c r="D580" s="19">
-        <v>4301071045</v>
+        <v>4301071032</v>
       </c>
       <c r="E580" s="18">
-        <v>4607111039392</v>
+        <v>4607111038999</v>
       </c>
       <c r="F580" s="20" t="s">
-        <v>670</v>
+        <v>726</v>
       </c>
       <c r="G580" s="21"/>
       <c r="H580" s="22" t="s">
@@ -19882,22 +19888,22 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="17" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B581" s="18" t="s">
-        <v>479</v>
+        <v>668</v>
       </c>
       <c r="C581" s="18" t="s">
-        <v>480</v>
+        <v>669</v>
       </c>
       <c r="D581" s="19">
-        <v>4301070963</v>
+        <v>4301071045</v>
       </c>
       <c r="E581" s="18">
-        <v>4607111038630</v>
+        <v>4607111039392</v>
       </c>
       <c r="F581" s="20" t="s">
-        <v>481</v>
+        <v>670</v>
       </c>
       <c r="G581" s="21"/>
       <c r="H581" s="22" t="s">
@@ -19906,22 +19912,22 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B582" s="18" t="s">
-        <v>586</v>
+        <v>479</v>
       </c>
       <c r="C582" s="18" t="s">
-        <v>587</v>
+        <v>480</v>
       </c>
       <c r="D582" s="19">
-        <v>4301071054</v>
+        <v>4301070963</v>
       </c>
       <c r="E582" s="18">
-        <v>4607111035639</v>
+        <v>4607111038630</v>
       </c>
       <c r="F582" s="20" t="s">
-        <v>588</v>
+        <v>481</v>
       </c>
       <c r="G582" s="21"/>
       <c r="H582" s="22" t="s">
@@ -19930,30 +19936,54 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" s="17" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B583" s="18" t="s">
-        <v>336</v>
+        <v>586</v>
       </c>
       <c r="C583" s="18" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="D583" s="19">
-        <v>4301135540</v>
+        <v>4301071054</v>
       </c>
       <c r="E583" s="18">
-        <v>4607111035646</v>
+        <v>4607111035639</v>
       </c>
       <c r="F583" s="20" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="G583" s="21"/>
       <c r="H583" s="22" t="s">
         <v>849</v>
       </c>
     </row>
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A584" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="B584" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C584" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="D584" s="19">
+        <v>4301135540</v>
+      </c>
+      <c r="E584" s="18">
+        <v>4607111035646</v>
+      </c>
+      <c r="F584" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="G584" s="21"/>
+      <c r="H584" s="22" t="s">
+        <v>849</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F583" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
+  <autoFilter ref="A1:F584" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F256">
       <sortCondition ref="A1:A187"/>
     </sortState>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF01FAB-A9DA-43CA-9E60-6274A66EF725}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54977F89-D7B3-4403-8547-8FD7F5E3463B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$586</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$588</definedName>
     <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$525</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="1057">
   <si>
     <t>1С</t>
   </si>
@@ -2699,15 +2699,6 @@
     <t>Пельмени Бульмени мини с мясом и оливковым маслом  ТС Бульмени ГШ флоу-пак сфера 0,7кг  Поком</t>
   </si>
   <si>
-    <t>SU003601</t>
-  </si>
-  <si>
-    <t>P004597</t>
-  </si>
-  <si>
-    <t>Снеки «Чебуманы с говядиной» Фикс.вес 0,28 Пакет ТМ «Горячая штучка»</t>
-  </si>
-  <si>
     <t>Бульмени хрустящие с мясом ТМ Горячая штучка ТС Бульмени ГШ сфера 0,22 кг  Поком</t>
   </si>
   <si>
@@ -3186,6 +3177,39 @@
   </si>
   <si>
     <t>ротация (23,07,26 Боярко тел.)</t>
+  </si>
+  <si>
+    <t>SU004031 Чебупицца со вкусом Утка по-пекински ТМ Горячая штучка ТС Чебупицца ф/в 0,23 кг.</t>
+  </si>
+  <si>
+    <t>SU004031</t>
+  </si>
+  <si>
+    <t>P005179</t>
+  </si>
+  <si>
+    <t>Снеки «Чебупицца со вкусом Утка по-пекински» Фикс.вес 0,23 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>SU004097 Чебупели со вкусом Фо Бо ТМ Горячая штучка ф/в 0,22 кг УМК МГ</t>
+  </si>
+  <si>
+    <t>SU004097</t>
+  </si>
+  <si>
+    <t>P005291</t>
+  </si>
+  <si>
+    <t>Снеки «Чебупели со вкусом Фо бо» Фикс.вес 0,22 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>SU002961</t>
+  </si>
+  <si>
+    <t>P003431</t>
+  </si>
+  <si>
+    <t>Снеки «Чебуманы с говядиной» Фикс.вес 0,28 лоток ТМ «Горячая штучка»</t>
   </si>
 </sst>
 </file>
@@ -6441,7 +6465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H586"/>
+  <dimension ref="A1:H588"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88" style="11" customWidth="1"/>
@@ -6697,10 +6721,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D11" s="4">
         <v>4301135793</v>
@@ -6709,14 +6733,14 @@
         <v>4620207491003</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G11" s="1" t="e">
         <f>VLOOKUP(E11,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -6724,10 +6748,10 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D12" s="4">
         <v>4301135793</v>
@@ -6736,14 +6760,14 @@
         <v>4620207491003</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G12" s="1" t="e">
         <f>VLOOKUP(E12,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -6751,10 +6775,10 @@
         <v>186</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D13" s="4">
         <v>4301135793</v>
@@ -6763,25 +6787,25 @@
         <v>4620207491003</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G13" s="1" t="e">
         <f>VLOOKUP(E13,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D14" s="4">
         <v>4301135793</v>
@@ -6790,19 +6814,19 @@
         <v>4620207491003</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D15" s="4">
         <v>4301135793</v>
@@ -6811,7 +6835,7 @@
         <v>4620207491003</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -6820,10 +6844,10 @@
         <v>216</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D16" s="4">
         <v>4301135768</v>
@@ -6832,14 +6856,14 @@
         <v>4620207491034</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G16" s="1" t="e">
         <f>VLOOKUP(E16,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6847,10 +6871,10 @@
         <v>412</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D17" s="4">
         <v>4301135768</v>
@@ -6859,14 +6883,14 @@
         <v>4620207491034</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G17" s="1" t="e">
         <f>VLOOKUP(E17,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6874,10 +6898,10 @@
         <v>418</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D18" s="4">
         <v>4301135768</v>
@@ -6886,14 +6910,14 @@
         <v>4620207491034</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G18" s="1" t="e">
         <f>VLOOKUP(E18,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6901,10 +6925,10 @@
         <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D19" s="4">
         <v>4301135768</v>
@@ -6913,25 +6937,25 @@
         <v>4620207491034</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G19" s="1" t="e">
         <f>VLOOKUP(E19,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D20" s="4">
         <v>4301135768</v>
@@ -6940,19 +6964,19 @@
         <v>4620207491034</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D21" s="4">
         <v>4301135768</v>
@@ -6961,7 +6985,7 @@
         <v>4620207491034</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -6970,10 +6994,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D22" s="4">
         <v>4301135760</v>
@@ -6982,14 +7006,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G22" s="1" t="e">
         <f>VLOOKUP(E22,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6997,10 +7021,10 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D23" s="4">
         <v>4301135760</v>
@@ -7009,14 +7033,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G23" s="1" t="e">
         <f>VLOOKUP(E23,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7024,10 +7048,10 @@
         <v>188</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D24" s="4">
         <v>4301135760</v>
@@ -7036,25 +7060,25 @@
         <v>4620207491010</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G24" s="1" t="e">
         <f>VLOOKUP(E24,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D25" s="4">
         <v>4301135760</v>
@@ -7063,19 +7087,19 @@
         <v>4620207491010</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D26" s="4">
         <v>4301135760</v>
@@ -7084,7 +7108,7 @@
         <v>4620207491010</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -7093,10 +7117,10 @@
         <v>128</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D27" s="4">
         <v>4301135763</v>
@@ -7105,14 +7129,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G27" s="1" t="e">
         <f>VLOOKUP(E27,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7120,10 +7144,10 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D28" s="4">
         <v>4301135763</v>
@@ -7132,14 +7156,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G28" s="1" t="e">
         <f>VLOOKUP(E28,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -7147,10 +7171,10 @@
         <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D29" s="4">
         <v>4301135763</v>
@@ -7159,14 +7183,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G29" s="1" t="e">
         <f>VLOOKUP(E29,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7174,10 +7198,10 @@
         <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D30" s="4">
         <v>4301135763</v>
@@ -7186,14 +7210,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G30" s="1" t="e">
         <f>VLOOKUP(E30,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -8378,10 +8402,10 @@
         <v>193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D80" s="4">
         <v>4301135753</v>
@@ -8390,14 +8414,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G80" s="1" t="e">
         <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8405,10 +8429,10 @@
         <v>688</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D81" s="4">
         <v>4301135753</v>
@@ -8417,14 +8441,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G81" s="1" t="e">
         <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8432,10 +8456,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D82" s="4">
         <v>4301135753</v>
@@ -8444,14 +8468,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G82" s="1" t="e">
         <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8459,10 +8483,10 @@
         <v>228</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D83" s="4">
         <v>4301135778</v>
@@ -8471,14 +8495,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G83" s="1" t="e">
         <f>VLOOKUP(E83,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8486,10 +8510,10 @@
         <v>194</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D84" s="4">
         <v>4301135778</v>
@@ -8498,14 +8522,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G84" s="1" t="e">
         <f>VLOOKUP(E84,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8513,10 +8537,10 @@
         <v>692</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D85" s="4">
         <v>4301135778</v>
@@ -8525,14 +8549,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G85" s="1" t="e">
         <f>VLOOKUP(E85,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8540,10 +8564,10 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D86" s="4">
         <v>4301135778</v>
@@ -8552,25 +8576,25 @@
         <v>4620207490853</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G86" s="1" t="e">
         <f>VLOOKUP(E86,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D87" s="4">
         <v>4301135778</v>
@@ -8579,19 +8603,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D88" s="4">
         <v>4301135778</v>
@@ -8600,19 +8624,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D89" s="4">
         <v>4301135778</v>
@@ -8621,7 +8645,7 @@
         <v>4620207490853</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -9134,7 +9158,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>753</v>
@@ -9374,7 +9398,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>730</v>
@@ -11174,10 +11198,10 @@
         <v>109</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D196" s="4">
         <v>4301071109</v>
@@ -11186,7 +11210,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G196" s="1">
         <f>VLOOKUP(E196,[1]Лист1!$D:$M,10,0)</f>
@@ -11198,10 +11222,10 @@
         <v>88</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11210,7 +11234,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11222,10 +11246,10 @@
         <v>150</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D198" s="4">
         <v>4301071107</v>
@@ -11234,7 +11258,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11246,10 +11270,10 @@
         <v>766</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11258,7 +11282,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11270,10 +11294,10 @@
         <v>151</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11282,7 +11306,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11456,7 +11480,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>110</v>
@@ -11504,10 +11528,10 @@
         <v>111</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D210" s="4">
         <v>4301071117</v>
@@ -11516,13 +11540,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="G210" s="1">
         <v>180</v>
       </c>
       <c r="H210" s="16" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -11530,10 +11554,10 @@
         <v>90</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11542,13 +11566,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -13148,7 +13172,7 @@
         <v>319</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D278" s="4">
         <v>4301071062</v>
@@ -13157,7 +13181,7 @@
         <v>4607111036384</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="G278" s="1">
         <f>VLOOKUP(E278,[1]Лист1!$D:$M,10,0)</f>
@@ -13172,7 +13196,7 @@
         <v>319</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D279" s="4">
         <v>4301071062</v>
@@ -13181,7 +13205,7 @@
         <v>4607111036384</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="G279" s="1">
         <f>VLOOKUP(E279,[1]Лист1!$D:$M,10,0)</f>
@@ -13262,7 +13286,7 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>882</v>
@@ -13286,7 +13310,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>882</v>
@@ -13478,7 +13502,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>335</v>
@@ -14979,10 +15003,10 @@
         <v>572</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="D358" s="4">
         <v>4301135824</v>
@@ -14991,7 +15015,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F358" s="5" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G358" s="1"/>
     </row>
@@ -15000,10 +15024,10 @@
         <v>759</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="D359" s="4">
         <v>4301135824</v>
@@ -15012,7 +15036,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G359" s="1"/>
     </row>
@@ -15021,10 +15045,10 @@
         <v>546</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="D360" s="4">
         <v>4301135824</v>
@@ -15033,7 +15057,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -16176,19 +16200,19 @@
         <v>768</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>886</v>
+        <v>1054</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>887</v>
+        <v>1055</v>
       </c>
       <c r="D415" s="4">
-        <v>4301135591</v>
+        <v>4301135184</v>
       </c>
       <c r="E415" s="3">
         <v>4607111036568</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>888</v>
+        <v>1056</v>
       </c>
       <c r="G415" s="1">
         <v>180</v>
@@ -16199,19 +16223,19 @@
         <v>862</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>886</v>
+        <v>1054</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>887</v>
+        <v>1055</v>
       </c>
       <c r="D416" s="4">
-        <v>4301135591</v>
+        <v>4301135184</v>
       </c>
       <c r="E416" s="3">
         <v>4607111036568</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>888</v>
+        <v>1056</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16222,19 +16246,19 @@
         <v>697</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>886</v>
+        <v>1054</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>887</v>
+        <v>1055</v>
       </c>
       <c r="D417" s="4">
-        <v>4301135591</v>
+        <v>4301135184</v>
       </c>
       <c r="E417" s="3">
         <v>4607111036568</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>888</v>
+        <v>1056</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16242,7 +16266,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>700</v>
@@ -16815,10 +16839,10 @@
         <v>878</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D444" s="4">
         <v>4301135826</v>
@@ -16835,13 +16859,13 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16858,13 +16882,13 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16884,10 +16908,10 @@
         <v>869</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16967,13 +16991,13 @@
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D451" s="4">
         <v>4301135763</v>
@@ -16982,19 +17006,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F451" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G451" s="1"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D452" s="4">
         <v>4301135763</v>
@@ -17003,19 +17027,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F452" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G452" s="1"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D453" s="4">
         <v>4301135763</v>
@@ -17024,19 +17048,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G453" s="1"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D454" s="4">
         <v>4301135763</v>
@@ -17045,19 +17069,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G454" s="1"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D455" s="4">
         <v>4301135665</v>
@@ -17066,19 +17090,19 @@
         <v>4607111039729</v>
       </c>
       <c r="F455" s="5" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="G455" s="1"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="D456" s="4">
         <v>4301135702</v>
@@ -17087,13 +17111,13 @@
         <v>4620207490228</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="G456" s="1"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>744</v>
@@ -17112,12 +17136,12 @@
       </c>
       <c r="G457" s="1"/>
       <c r="H457" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>750</v>
@@ -17136,12 +17160,12 @@
       </c>
       <c r="G458" s="1"/>
       <c r="H458" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>722</v>
@@ -17160,12 +17184,12 @@
       </c>
       <c r="G459" s="1"/>
       <c r="H459" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>662</v>
@@ -17184,12 +17208,12 @@
       </c>
       <c r="G460" s="1"/>
       <c r="H460" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>614</v>
@@ -17208,12 +17232,12 @@
       </c>
       <c r="G461" s="1"/>
       <c r="H461" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>610</v>
@@ -17232,12 +17256,12 @@
       </c>
       <c r="G462" s="1"/>
       <c r="H462" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>618</v>
@@ -17252,16 +17276,16 @@
         <v>4607111039293</v>
       </c>
       <c r="F463" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="G463" s="1"/>
       <c r="H463" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>622</v>
@@ -17280,7 +17304,7 @@
       </c>
       <c r="G464" s="1"/>
       <c r="H464" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
@@ -17288,10 +17312,10 @@
         <v>639</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D465" s="4">
         <v>4301135760</v>
@@ -17300,11 +17324,11 @@
         <v>4620207491010</v>
       </c>
       <c r="F465" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G465" s="1"/>
       <c r="H465" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
@@ -17328,18 +17352,18 @@
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="16" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D467" s="4">
         <v>4301135768</v>
@@ -17348,19 +17372,19 @@
         <v>4620207491034</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G467" s="1"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D468" s="4">
         <v>4301071097</v>
@@ -17369,19 +17393,19 @@
         <v>4620207491096</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="G468" s="1"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D469" s="4">
         <v>4301071097</v>
@@ -17390,19 +17414,19 @@
         <v>4620207491096</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="G469" s="1"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D470" s="4">
         <v>4301132227</v>
@@ -17411,19 +17435,19 @@
         <v>4620207491133</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="G470" s="1"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C471" s="3" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D471" s="4">
         <v>4301132227</v>
@@ -17432,19 +17456,19 @@
         <v>4620207491133</v>
       </c>
       <c r="F471" s="5" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="G471" s="1"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D472" s="4">
         <v>4301135753</v>
@@ -17453,13 +17477,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G472" s="1"/>
     </row>
     <row r="473" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>856</v>
@@ -17480,7 +17504,7 @@
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>853</v>
@@ -17501,13 +17525,13 @@
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D475" s="4">
         <v>4301071075</v>
@@ -17516,19 +17540,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="G475" s="1"/>
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17537,7 +17561,7 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="G476" s="1"/>
     </row>
@@ -17585,13 +17609,13 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D479" s="4">
         <v>4301135753</v>
@@ -17600,7 +17624,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G479" s="1"/>
     </row>
@@ -17711,7 +17735,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>618</v>
@@ -17726,7 +17750,7 @@
         <v>4607111039293</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="G485" s="1"/>
     </row>
@@ -17774,13 +17798,13 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D488" s="4">
         <v>4301071094</v>
@@ -17789,19 +17813,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="G488" s="1"/>
     </row>
     <row r="489" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D489" s="4">
         <v>4301071093</v>
@@ -17810,13 +17834,13 @@
         <v>4620207490709</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>730</v>
@@ -17837,7 +17861,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>753</v>
@@ -17858,7 +17882,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>744</v>
@@ -17879,7 +17903,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>750</v>
@@ -17900,7 +17924,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>662</v>
@@ -17921,7 +17945,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>718</v>
@@ -17942,7 +17966,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>775</v>
@@ -17963,7 +17987,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>873</v>
@@ -17984,13 +18008,13 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D498" s="4">
         <v>4301135793</v>
@@ -17999,19 +18023,19 @@
         <v>4620207491003</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G498" s="1"/>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D499" s="4">
         <v>4301135760</v>
@@ -18020,13 +18044,13 @@
         <v>4620207491010</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G499" s="1"/>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>180</v>
@@ -18047,7 +18071,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>164</v>
@@ -18068,7 +18092,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>610</v>
@@ -18089,7 +18113,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>614</v>
@@ -18110,7 +18134,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>618</v>
@@ -18125,13 +18149,13 @@
         <v>4607111039293</v>
       </c>
       <c r="F504" s="5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="G504" s="1"/>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>622</v>
@@ -18152,7 +18176,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>648</v>
@@ -18173,7 +18197,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>645</v>
@@ -18194,7 +18218,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>736</v>
@@ -18215,13 +18239,13 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D509" s="4">
         <v>4301135753</v>
@@ -18230,13 +18254,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>693</v>
@@ -18257,7 +18281,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>863</v>
@@ -18278,13 +18302,13 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="D512" s="4">
         <v>4301071063</v>
@@ -18293,13 +18317,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F512" s="5" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="G512" s="1"/>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>491</v>
@@ -18320,13 +18344,13 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="D514" s="4">
         <v>4301135834</v>
@@ -18335,19 +18359,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F514" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="G514" s="1"/>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18356,19 +18380,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18377,19 +18401,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D517" s="4">
         <v>4301135873</v>
@@ -18398,19 +18422,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="D518" s="4">
         <v>4301135850</v>
@@ -18419,19 +18443,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="D519" s="4">
         <v>4301190117</v>
@@ -18440,19 +18464,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D520" s="4">
         <v>4301190115</v>
@@ -18461,19 +18485,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="D521" s="4">
         <v>4301135865</v>
@@ -18482,19 +18506,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="D522" s="4">
         <v>4301190116</v>
@@ -18503,19 +18527,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D523" s="4">
         <v>4301071112</v>
@@ -18524,19 +18548,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18545,7 +18569,7 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="G524" s="1"/>
     </row>
@@ -18674,10 +18698,10 @@
         <v>791</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D530" s="4">
         <v>4301071117</v>
@@ -18686,7 +18710,7 @@
         <v>4620207491737</v>
       </c>
       <c r="F530" s="5" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="G530" s="1">
         <v>180</v>
@@ -18772,10 +18796,10 @@
         <v>795</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D534" s="4">
         <v>4301135760</v>
@@ -18784,11 +18808,11 @@
         <v>4620207491010</v>
       </c>
       <c r="F534" s="5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="G534" s="21"/>
       <c r="H534" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
@@ -18892,10 +18916,10 @@
         <v>800</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D539" s="4">
         <v>4301135793</v>
@@ -18904,11 +18928,11 @@
         <v>4620207491003</v>
       </c>
       <c r="F539" s="5" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
@@ -19060,10 +19084,10 @@
         <v>807</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D546" s="4">
         <v>4301071109</v>
@@ -19072,7 +19096,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F546" s="5" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
@@ -19180,10 +19204,10 @@
         <v>812</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D551" s="4">
         <v>4301135763</v>
@@ -19192,11 +19216,11 @@
         <v>4620207491027</v>
       </c>
       <c r="F551" s="5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G551" s="21"/>
       <c r="H551" s="22" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
@@ -19300,10 +19324,10 @@
         <v>817</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="D556" s="4">
         <v>4301135753</v>
@@ -19312,7 +19336,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="G556" s="21"/>
       <c r="H556" s="22" t="s">
@@ -19324,10 +19348,10 @@
         <v>818</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D557" s="4">
         <v>4301135778</v>
@@ -19336,11 +19360,11 @@
         <v>4620207490853</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="16" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
@@ -19444,10 +19468,10 @@
         <v>823</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D562" s="4">
         <v>4301135768</v>
@@ -19456,11 +19480,11 @@
         <v>4620207491034</v>
       </c>
       <c r="F562" s="5" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G562" s="21"/>
       <c r="H562" s="16" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="563" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
@@ -19513,7 +19537,7 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B565" s="3" t="s">
         <v>850</v>
@@ -19564,10 +19588,10 @@
         <v>828</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="D567" s="4">
         <v>4301071107</v>
@@ -19576,7 +19600,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F567" s="5" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="G567" s="21"/>
       <c r="H567" s="22" t="s">
@@ -19588,10 +19612,10 @@
         <v>829</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="D568" s="4">
         <v>4301135824</v>
@@ -19600,7 +19624,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -20039,8 +20063,50 @@
         <v>847</v>
       </c>
     </row>
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A587" s="10" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D587" s="4">
+        <v>4301135848</v>
+      </c>
+      <c r="E587" s="3">
+        <v>4620207491799</v>
+      </c>
+      <c r="F587" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G587" s="1"/>
+    </row>
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A588" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B588" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D588" s="4">
+        <v>4301190118</v>
+      </c>
+      <c r="E588" s="3">
+        <v>4620207491461</v>
+      </c>
+      <c r="F588" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G588" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F586" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
+  <autoFilter ref="A1:F588" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F257">
       <sortCondition ref="A1:A187"/>
     </sortState>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54977F89-D7B3-4403-8547-8FD7F5E3463B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E964E00D-D4AE-4447-AF97-95538B255B5B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="1058">
   <si>
     <t>1С</t>
   </si>
@@ -2249,12 +2249,6 @@
     <t>Наггетсы «Нагетосы Сочная курочка в хрустящей панировке» Фикс.вес 0,25 ТМ «Горячая штучка»</t>
   </si>
   <si>
-    <t>SU003576</t>
-  </si>
-  <si>
-    <t>P004489</t>
-  </si>
-  <si>
     <t>Снеки «Хотстеры» Фикс.вес 0,25 Пакет ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -3210,6 +3204,15 @@
   </si>
   <si>
     <t>Снеки «Чебуманы с говядиной» Фикс.вес 0,28 лоток ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>SU004226</t>
+  </si>
+  <si>
+    <t>P005492</t>
+  </si>
+  <si>
+    <t>Снеки «Готовые хотстеры» Фикс.вес 0,25 ТМ «Горячая штучка»</t>
   </si>
 </sst>
 </file>
@@ -6721,10 +6724,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D11" s="4">
         <v>4301135793</v>
@@ -6733,14 +6736,14 @@
         <v>4620207491003</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G11" s="1" t="e">
         <f>VLOOKUP(E11,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -6748,10 +6751,10 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D12" s="4">
         <v>4301135793</v>
@@ -6760,14 +6763,14 @@
         <v>4620207491003</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G12" s="1" t="e">
         <f>VLOOKUP(E12,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -6775,10 +6778,10 @@
         <v>186</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D13" s="4">
         <v>4301135793</v>
@@ -6787,25 +6790,25 @@
         <v>4620207491003</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G13" s="1" t="e">
         <f>VLOOKUP(E13,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D14" s="4">
         <v>4301135793</v>
@@ -6814,19 +6817,19 @@
         <v>4620207491003</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D15" s="4">
         <v>4301135793</v>
@@ -6835,7 +6838,7 @@
         <v>4620207491003</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -6844,10 +6847,10 @@
         <v>216</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D16" s="4">
         <v>4301135768</v>
@@ -6856,14 +6859,14 @@
         <v>4620207491034</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G16" s="1" t="e">
         <f>VLOOKUP(E16,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6871,10 +6874,10 @@
         <v>412</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D17" s="4">
         <v>4301135768</v>
@@ -6883,14 +6886,14 @@
         <v>4620207491034</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G17" s="1" t="e">
         <f>VLOOKUP(E17,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6898,10 +6901,10 @@
         <v>418</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D18" s="4">
         <v>4301135768</v>
@@ -6910,14 +6913,14 @@
         <v>4620207491034</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G18" s="1" t="e">
         <f>VLOOKUP(E18,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6925,10 +6928,10 @@
         <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D19" s="4">
         <v>4301135768</v>
@@ -6937,25 +6940,25 @@
         <v>4620207491034</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G19" s="1" t="e">
         <f>VLOOKUP(E19,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D20" s="4">
         <v>4301135768</v>
@@ -6964,19 +6967,19 @@
         <v>4620207491034</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D21" s="4">
         <v>4301135768</v>
@@ -6985,7 +6988,7 @@
         <v>4620207491034</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -6994,10 +6997,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D22" s="4">
         <v>4301135760</v>
@@ -7006,14 +7009,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G22" s="1" t="e">
         <f>VLOOKUP(E22,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7021,10 +7024,10 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D23" s="4">
         <v>4301135760</v>
@@ -7033,14 +7036,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G23" s="1" t="e">
         <f>VLOOKUP(E23,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7048,10 +7051,10 @@
         <v>188</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D24" s="4">
         <v>4301135760</v>
@@ -7060,25 +7063,25 @@
         <v>4620207491010</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G24" s="1" t="e">
         <f>VLOOKUP(E24,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D25" s="4">
         <v>4301135760</v>
@@ -7087,19 +7090,19 @@
         <v>4620207491010</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D26" s="4">
         <v>4301135760</v>
@@ -7108,7 +7111,7 @@
         <v>4620207491010</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -7117,10 +7120,10 @@
         <v>128</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D27" s="4">
         <v>4301135763</v>
@@ -7129,14 +7132,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G27" s="1" t="e">
         <f>VLOOKUP(E27,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7144,10 +7147,10 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D28" s="4">
         <v>4301135763</v>
@@ -7156,14 +7159,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G28" s="1" t="e">
         <f>VLOOKUP(E28,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -7171,10 +7174,10 @@
         <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D29" s="4">
         <v>4301135763</v>
@@ -7183,14 +7186,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G29" s="1" t="e">
         <f>VLOOKUP(E29,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7198,10 +7201,10 @@
         <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D30" s="4">
         <v>4301135763</v>
@@ -7210,14 +7213,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G30" s="1" t="e">
         <f>VLOOKUP(E30,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -7225,10 +7228,10 @@
         <v>400</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D31" s="4">
         <v>4301136079</v>
@@ -7237,7 +7240,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(E31,[1]Лист1!$D:$M,10,0)</f>
@@ -7249,10 +7252,10 @@
         <v>421</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D32" s="4">
         <v>4301136079</v>
@@ -7261,7 +7264,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(E32,[1]Лист1!$D:$M,10,0)</f>
@@ -7273,10 +7276,10 @@
         <v>503</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D33" s="4">
         <v>4301136079</v>
@@ -7285,7 +7288,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(E33,[1]Лист1!$D:$M,10,0)</f>
@@ -7297,10 +7300,10 @@
         <v>190</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D34" s="4">
         <v>4301136079</v>
@@ -7309,7 +7312,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(E34,[1]Лист1!$D:$M,10,0)</f>
@@ -8402,10 +8405,10 @@
         <v>193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D80" s="4">
         <v>4301135753</v>
@@ -8414,14 +8417,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G80" s="1" t="e">
         <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8429,10 +8432,10 @@
         <v>688</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D81" s="4">
         <v>4301135753</v>
@@ -8441,14 +8444,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G81" s="1" t="e">
         <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8456,10 +8459,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D82" s="4">
         <v>4301135753</v>
@@ -8468,14 +8471,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G82" s="1" t="e">
         <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8483,10 +8486,10 @@
         <v>228</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D83" s="4">
         <v>4301135778</v>
@@ -8495,14 +8498,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G83" s="1" t="e">
         <f>VLOOKUP(E83,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8510,10 +8513,10 @@
         <v>194</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D84" s="4">
         <v>4301135778</v>
@@ -8522,14 +8525,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G84" s="1" t="e">
         <f>VLOOKUP(E84,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8537,10 +8540,10 @@
         <v>692</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D85" s="4">
         <v>4301135778</v>
@@ -8549,14 +8552,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G85" s="1" t="e">
         <f>VLOOKUP(E85,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8564,10 +8567,10 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D86" s="4">
         <v>4301135778</v>
@@ -8576,25 +8579,25 @@
         <v>4620207490853</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G86" s="1" t="e">
         <f>VLOOKUP(E86,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D87" s="4">
         <v>4301135778</v>
@@ -8603,19 +8606,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D88" s="4">
         <v>4301135778</v>
@@ -8624,19 +8627,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D89" s="4">
         <v>4301135778</v>
@@ -8645,7 +8648,7 @@
         <v>4620207490853</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -8654,10 +8657,10 @@
         <v>116</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D90" s="4">
         <v>4301131046</v>
@@ -8666,7 +8669,7 @@
         <v>4607111034137</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G90" s="1">
         <f>VLOOKUP(E90,[1]Лист1!$D:$M,10,0)</f>
@@ -8678,10 +8681,10 @@
         <v>121</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D91" s="4">
         <v>4301131046</v>
@@ -8690,7 +8693,7 @@
         <v>4607111034137</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G91" s="1">
         <f>VLOOKUP(E91,[1]Лист1!$D:$M,10,0)</f>
@@ -8702,10 +8705,10 @@
         <v>195</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D92" s="4">
         <v>4301131046</v>
@@ -8714,7 +8717,7 @@
         <v>4607111034137</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G92" s="1">
         <f>VLOOKUP(E92,[1]Лист1!$D:$M,10,0)</f>
@@ -8726,10 +8729,10 @@
         <v>117</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D93" s="4">
         <v>4301131047</v>
@@ -8738,7 +8741,7 @@
         <v>4607111034120</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G93" s="1">
         <f>VLOOKUP(E93,[1]Лист1!$D:$M,10,0)</f>
@@ -8750,10 +8753,10 @@
         <v>122</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D94" s="4">
         <v>4301131047</v>
@@ -8762,7 +8765,7 @@
         <v>4607111034120</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G94" s="1">
         <f>VLOOKUP(E94,[1]Лист1!$D:$M,10,0)</f>
@@ -8774,10 +8777,10 @@
         <v>196</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D95" s="4">
         <v>4301131047</v>
@@ -8786,7 +8789,7 @@
         <v>4607111034120</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G95" s="1">
         <f>VLOOKUP(E95,[1]Лист1!$D:$M,10,0)</f>
@@ -9089,10 +9092,10 @@
         <v>427</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D108" s="4">
         <v>4301132184</v>
@@ -9101,7 +9104,7 @@
         <v>4607111036599</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G108" s="1">
         <f>VLOOKUP(E108,[1]Лист1!$D:$M,10,0)</f>
@@ -9113,10 +9116,10 @@
         <v>218</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D109" s="4">
         <v>4301132184</v>
@@ -9125,7 +9128,7 @@
         <v>4607111036599</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G109" s="1">
         <f>VLOOKUP(E109,[1]Лист1!$D:$M,10,0)</f>
@@ -9137,10 +9140,10 @@
         <v>199</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D110" s="4">
         <v>4301132184</v>
@@ -9149,7 +9152,7 @@
         <v>4607111036599</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G110" s="1">
         <f>VLOOKUP(E110,[1]Лист1!$D:$M,10,0)</f>
@@ -9158,13 +9161,13 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D111" s="4">
         <v>4301132188</v>
@@ -9173,7 +9176,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G111" s="1">
         <f>VLOOKUP(E111,[1]Лист1!$D:$M,10,0)</f>
@@ -9185,10 +9188,10 @@
         <v>402</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D112" s="4">
         <v>4301132188</v>
@@ -9197,7 +9200,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G112" s="1">
         <f>VLOOKUP(E112,[1]Лист1!$D:$M,10,0)</f>
@@ -9209,10 +9212,10 @@
         <v>219</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D113" s="4">
         <v>4301132188</v>
@@ -9221,7 +9224,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G113" s="1">
         <f>VLOOKUP(E113,[1]Лист1!$D:$M,10,0)</f>
@@ -9233,10 +9236,10 @@
         <v>200</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D114" s="4">
         <v>4301132188</v>
@@ -9245,7 +9248,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G114" s="1">
         <f>VLOOKUP(E114,[1]Лист1!$D:$M,10,0)</f>
@@ -9257,10 +9260,10 @@
         <v>201</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D115" s="4">
         <v>4301132179</v>
@@ -9269,7 +9272,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G115" s="1">
         <f>VLOOKUP(E115,[1]Лист1!$D:$M,10,0)</f>
@@ -9281,10 +9284,10 @@
         <v>98</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D116" s="4">
         <v>4301132179</v>
@@ -9293,7 +9296,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G116" s="1">
         <f>VLOOKUP(E116,[1]Лист1!$D:$M,10,0)</f>
@@ -9305,10 +9308,10 @@
         <v>638</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D117" s="4">
         <v>4301132179</v>
@@ -9317,7 +9320,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G117" s="1">
         <f>VLOOKUP(E117,[1]Лист1!$D:$M,10,0)</f>
@@ -9329,10 +9332,10 @@
         <v>77</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D118" s="4">
         <v>4301132179</v>
@@ -9341,7 +9344,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G118" s="1">
         <f>VLOOKUP(E118,[1]Лист1!$D:$M,10,0)</f>
@@ -9398,7 +9401,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>730</v>
@@ -9449,10 +9452,10 @@
         <v>644</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D123" s="4">
         <v>4301132182</v>
@@ -9461,7 +9464,7 @@
         <v>4607111035721</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G123" s="1">
         <f>VLOOKUP(E123,[1]Лист1!$D:$M,10,0)</f>
@@ -9473,10 +9476,10 @@
         <v>698</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D124" s="4">
         <v>4301132182</v>
@@ -9485,7 +9488,7 @@
         <v>4607111035721</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G124" s="1">
         <f>VLOOKUP(E124,[1]Лист1!$D:$M,10,0)</f>
@@ -9497,10 +9500,10 @@
         <v>79</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D125" s="4">
         <v>4301132182</v>
@@ -9509,7 +9512,7 @@
         <v>4607111035721</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G125" s="1">
         <f>VLOOKUP(E125,[1]Лист1!$D:$M,10,0)</f>
@@ -9518,13 +9521,13 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D126" s="4">
         <v>4301132182</v>
@@ -9533,11 +9536,11 @@
         <v>4607111035721</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G126" s="21"/>
       <c r="H126" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -11198,10 +11201,10 @@
         <v>109</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D196" s="4">
         <v>4301071109</v>
@@ -11210,7 +11213,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G196" s="1">
         <f>VLOOKUP(E196,[1]Лист1!$D:$M,10,0)</f>
@@ -11222,10 +11225,10 @@
         <v>88</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11234,7 +11237,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11246,10 +11249,10 @@
         <v>150</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D198" s="4">
         <v>4301071107</v>
@@ -11258,7 +11261,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11267,13 +11270,13 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11282,7 +11285,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11294,10 +11297,10 @@
         <v>151</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11306,7 +11309,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11432,7 +11435,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>110</v>
@@ -11480,7 +11483,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>110</v>
@@ -11528,10 +11531,10 @@
         <v>111</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D210" s="4">
         <v>4301071117</v>
@@ -11540,13 +11543,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G210" s="1">
         <v>180</v>
       </c>
       <c r="H210" s="16" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -11554,10 +11557,10 @@
         <v>90</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11566,13 +11569,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -11874,96 +11877,84 @@
         <v>184</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D224" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E224" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G224" s="1">
-        <f>VLOOKUP(E224,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1057</v>
+      </c>
+      <c r="G224" s="1"/>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="10" t="s">
         <v>112</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D225" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E225" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G225" s="1">
-        <f>VLOOKUP(E225,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1057</v>
+      </c>
+      <c r="G225" s="1"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D226" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E226" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G226" s="1">
-        <f>VLOOKUP(E226,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1057</v>
+      </c>
+      <c r="G226" s="1"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
         <v>92</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D227" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E227" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G227" s="1">
-        <f>VLOOKUP(E227,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1057</v>
+      </c>
+      <c r="G227" s="1"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
@@ -12158,7 +12149,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>180</v>
@@ -12302,7 +12293,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>648</v>
@@ -12398,7 +12389,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>645</v>
@@ -13172,7 +13163,7 @@
         <v>319</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D278" s="4">
         <v>4301071062</v>
@@ -13181,7 +13172,7 @@
         <v>4607111036384</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G278" s="1">
         <f>VLOOKUP(E278,[1]Лист1!$D:$M,10,0)</f>
@@ -13196,7 +13187,7 @@
         <v>319</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D279" s="4">
         <v>4301071062</v>
@@ -13205,7 +13196,7 @@
         <v>4607111036384</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G279" s="1">
         <f>VLOOKUP(E279,[1]Лист1!$D:$M,10,0)</f>
@@ -13217,10 +13208,10 @@
         <v>403</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D280" s="4">
         <v>4301135571</v>
@@ -13229,7 +13220,7 @@
         <v>4607111035028</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G280" s="1">
         <f>VLOOKUP(E280,[1]Лист1!$D:$M,10,0)</f>
@@ -13241,10 +13232,10 @@
         <v>323</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D281" s="4">
         <v>4301135571</v>
@@ -13253,7 +13244,7 @@
         <v>4607111035028</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G281" s="1">
         <f>VLOOKUP(E281,[1]Лист1!$D:$M,10,0)</f>
@@ -13262,13 +13253,13 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D282" s="4">
         <v>4301135571</v>
@@ -13277,7 +13268,7 @@
         <v>4607111035028</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G282" s="1">
         <f>VLOOKUP(E282,[1]Лист1!$D:$M,10,0)</f>
@@ -13286,13 +13277,13 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D283" s="4">
         <v>4301135571</v>
@@ -13301,7 +13292,7 @@
         <v>4607111035028</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G283" s="1">
         <f>VLOOKUP(E283,[1]Лист1!$D:$M,10,0)</f>
@@ -13310,13 +13301,13 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D284" s="4">
         <v>4301135571</v>
@@ -13325,7 +13316,7 @@
         <v>4607111035028</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G284" s="1">
         <f>VLOOKUP(E284,[1]Лист1!$D:$M,10,0)</f>
@@ -13337,10 +13328,10 @@
         <v>322</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D285" s="4">
         <v>4301135571</v>
@@ -13349,7 +13340,7 @@
         <v>4607111035028</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G285" s="1">
         <f>VLOOKUP(E285,[1]Лист1!$D:$M,10,0)</f>
@@ -13502,7 +13493,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>335</v>
@@ -13865,10 +13856,10 @@
         <v>420</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D307" s="4">
         <v>4301132170</v>
@@ -13877,7 +13868,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G307" s="1">
         <f>VLOOKUP(E307,[1]Лист1!$D:$M,10,0)</f>
@@ -13889,10 +13880,10 @@
         <v>448</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D308" s="4">
         <v>4301132170</v>
@@ -13901,7 +13892,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F308" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G308" s="1">
         <f>VLOOKUP(E308,[1]Лист1!$D:$M,10,0)</f>
@@ -13913,10 +13904,10 @@
         <v>451</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D309" s="4">
         <v>4301132170</v>
@@ -13925,7 +13916,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G309" s="1">
         <f>VLOOKUP(E309,[1]Лист1!$D:$M,10,0)</f>
@@ -13937,10 +13928,10 @@
         <v>419</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D310" s="4">
         <v>4301132170</v>
@@ -13949,7 +13940,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F310" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G310" s="1">
         <f>VLOOKUP(E310,[1]Лист1!$D:$M,10,0)</f>
@@ -15003,10 +14994,10 @@
         <v>572</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D358" s="4">
         <v>4301135824</v>
@@ -15015,19 +15006,19 @@
         <v>4607111039095</v>
       </c>
       <c r="F358" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G358" s="1"/>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D359" s="4">
         <v>4301135824</v>
@@ -15036,7 +15027,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G359" s="1"/>
     </row>
@@ -15045,10 +15036,10 @@
         <v>546</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D360" s="4">
         <v>4301135824</v>
@@ -15057,7 +15048,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -16029,7 +16020,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>662</v>
@@ -16197,13 +16188,13 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D415" s="4">
         <v>4301135184</v>
@@ -16212,7 +16203,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G415" s="1">
         <v>180</v>
@@ -16220,13 +16211,13 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D416" s="4">
         <v>4301135184</v>
@@ -16235,7 +16226,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16246,10 +16237,10 @@
         <v>697</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D417" s="4">
         <v>4301135184</v>
@@ -16258,7 +16249,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16266,7 +16257,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>700</v>
@@ -16350,7 +16341,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>704</v>
@@ -16413,7 +16404,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>713</v>
@@ -16520,7 +16511,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>722</v>
@@ -16543,7 +16534,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>722</v>
@@ -16566,7 +16557,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>722</v>
@@ -16612,13 +16603,13 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C434" s="3" t="s">
         <v>740</v>
-      </c>
-      <c r="B434" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C434" s="3" t="s">
-        <v>742</v>
       </c>
       <c r="D434" s="4">
         <v>4301135404</v>
@@ -16627,19 +16618,19 @@
         <v>4640242181516</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G434" s="1"/>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D435" s="4">
         <v>4301071090</v>
@@ -16648,7 +16639,7 @@
         <v>4620207490075</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G435" s="1">
         <v>180</v>
@@ -16656,13 +16647,13 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C436" s="3" t="s">
         <v>743</v>
-      </c>
-      <c r="B436" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>745</v>
       </c>
       <c r="D436" s="4">
         <v>4301071090</v>
@@ -16671,7 +16662,7 @@
         <v>4620207490075</v>
       </c>
       <c r="F436" s="5" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G436" s="1">
         <v>180</v>
@@ -16679,13 +16670,13 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D437" s="4">
         <v>4301071092</v>
@@ -16694,7 +16685,7 @@
         <v>4620207490174</v>
       </c>
       <c r="F437" s="5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G437" s="1">
         <v>180</v>
@@ -16702,13 +16693,13 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D438" s="4">
         <v>4301071092</v>
@@ -16717,7 +16708,7 @@
         <v>4620207490174</v>
       </c>
       <c r="F438" s="5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G438" s="1">
         <v>180</v>
@@ -16725,13 +16716,13 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C439" s="3" t="s">
         <v>746</v>
-      </c>
-      <c r="B439" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>748</v>
       </c>
       <c r="D439" s="4">
         <v>4301071092</v>
@@ -16740,7 +16731,7 @@
         <v>4620207490174</v>
       </c>
       <c r="F439" s="5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G439" s="1">
         <v>180</v>
@@ -16748,13 +16739,13 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D440" s="4">
         <v>4301071091</v>
@@ -16763,7 +16754,7 @@
         <v>4620207490044</v>
       </c>
       <c r="F440" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G440" s="1">
         <v>180</v>
@@ -16771,13 +16762,13 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C441" s="3" t="s">
         <v>749</v>
-      </c>
-      <c r="B441" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="C441" s="3" t="s">
-        <v>751</v>
       </c>
       <c r="D441" s="4">
         <v>4301071091</v>
@@ -16786,7 +16777,7 @@
         <v>4620207490044</v>
       </c>
       <c r="F441" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G441" s="1">
         <v>180</v>
@@ -16794,13 +16785,13 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C442" s="3" t="s">
         <v>760</v>
-      </c>
-      <c r="B442" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>762</v>
       </c>
       <c r="D442" s="4">
         <v>4301132044</v>
@@ -16809,19 +16800,19 @@
         <v>4607111036971</v>
       </c>
       <c r="F442" s="5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G442" s="1"/>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="C443" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="B443" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="C443" s="3" t="s">
-        <v>783</v>
       </c>
       <c r="D443" s="4">
         <v>4301135127</v>
@@ -16830,19 +16821,19 @@
         <v>4607111036995</v>
       </c>
       <c r="F443" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G443" s="1"/>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D444" s="4">
         <v>4301135826</v>
@@ -16851,7 +16842,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F444" s="5" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G444" s="1">
         <v>180</v>
@@ -16859,13 +16850,13 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16874,7 +16865,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F445" s="5" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G445" s="1">
         <v>180</v>
@@ -16882,13 +16873,13 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16897,7 +16888,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F446" s="5" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G446" s="1">
         <v>180</v>
@@ -16905,13 +16896,13 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16920,7 +16911,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F447" s="5" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G447" s="1">
         <v>180</v>
@@ -16928,13 +16919,13 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D448" s="4">
         <v>4301071074</v>
@@ -16943,19 +16934,19 @@
         <v>4620207491157</v>
       </c>
       <c r="F448" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G448" s="1"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D449" s="4">
         <v>4301071074</v>
@@ -16964,19 +16955,19 @@
         <v>4620207491157</v>
       </c>
       <c r="F449" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G449" s="1"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C450" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="B450" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="C450" s="3" t="s">
-        <v>872</v>
       </c>
       <c r="D450" s="4">
         <v>4301071074</v>
@@ -16985,19 +16976,19 @@
         <v>4620207491157</v>
       </c>
       <c r="F450" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G450" s="1"/>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D451" s="4">
         <v>4301135763</v>
@@ -17006,19 +16997,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F451" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G451" s="1"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D452" s="4">
         <v>4301135763</v>
@@ -17027,19 +17018,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F452" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G452" s="1"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D453" s="4">
         <v>4301135763</v>
@@ -17048,19 +17039,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G453" s="1"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="B454" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="C454" s="3" t="s">
         <v>890</v>
-      </c>
-      <c r="B454" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>892</v>
       </c>
       <c r="D454" s="4">
         <v>4301135763</v>
@@ -17069,19 +17060,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G454" s="1"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="B455" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="C455" s="3" t="s">
         <v>894</v>
-      </c>
-      <c r="B455" s="3" t="s">
-        <v>895</v>
-      </c>
-      <c r="C455" s="3" t="s">
-        <v>896</v>
       </c>
       <c r="D455" s="4">
         <v>4301135665</v>
@@ -17090,19 +17081,19 @@
         <v>4607111039729</v>
       </c>
       <c r="F455" s="5" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G455" s="1"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="C456" s="3" t="s">
         <v>898</v>
-      </c>
-      <c r="B456" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="C456" s="3" t="s">
-        <v>900</v>
       </c>
       <c r="D456" s="4">
         <v>4301135702</v>
@@ -17111,19 +17102,19 @@
         <v>4620207490228</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G456" s="1"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D457" s="4">
         <v>4301071090</v>
@@ -17132,22 +17123,22 @@
         <v>4620207490075</v>
       </c>
       <c r="F457" s="5" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G457" s="1"/>
       <c r="H457" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D458" s="4">
         <v>4301071091</v>
@@ -17156,16 +17147,16 @@
         <v>4620207490044</v>
       </c>
       <c r="F458" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G458" s="1"/>
       <c r="H458" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>722</v>
@@ -17184,12 +17175,12 @@
       </c>
       <c r="G459" s="1"/>
       <c r="H459" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>662</v>
@@ -17208,12 +17199,12 @@
       </c>
       <c r="G460" s="1"/>
       <c r="H460" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>614</v>
@@ -17232,12 +17223,12 @@
       </c>
       <c r="G461" s="1"/>
       <c r="H461" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>610</v>
@@ -17256,12 +17247,12 @@
       </c>
       <c r="G462" s="1"/>
       <c r="H462" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>618</v>
@@ -17276,16 +17267,16 @@
         <v>4607111039293</v>
       </c>
       <c r="F463" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G463" s="1"/>
       <c r="H463" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>622</v>
@@ -17304,7 +17295,7 @@
       </c>
       <c r="G464" s="1"/>
       <c r="H464" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
@@ -17312,10 +17303,10 @@
         <v>639</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D465" s="4">
         <v>4301135760</v>
@@ -17324,11 +17315,11 @@
         <v>4620207491010</v>
       </c>
       <c r="F465" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G465" s="1"/>
       <c r="H465" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
@@ -17352,18 +17343,18 @@
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
+        <v>914</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="C467" s="3" t="s">
         <v>916</v>
-      </c>
-      <c r="B467" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="C467" s="3" t="s">
-        <v>918</v>
       </c>
       <c r="D467" s="4">
         <v>4301135768</v>
@@ -17372,19 +17363,19 @@
         <v>4620207491034</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G467" s="1"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D468" s="4">
         <v>4301071097</v>
@@ -17393,19 +17384,19 @@
         <v>4620207491096</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G468" s="1"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="C469" s="3" t="s">
         <v>919</v>
-      </c>
-      <c r="B469" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="C469" s="3" t="s">
-        <v>921</v>
       </c>
       <c r="D469" s="4">
         <v>4301071097</v>
@@ -17414,19 +17405,19 @@
         <v>4620207491096</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G469" s="1"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D470" s="4">
         <v>4301132227</v>
@@ -17435,19 +17426,19 @@
         <v>4620207491133</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G470" s="1"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
+        <v>920</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="C471" s="3" t="s">
         <v>922</v>
-      </c>
-      <c r="B471" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="C471" s="3" t="s">
-        <v>924</v>
       </c>
       <c r="D471" s="4">
         <v>4301132227</v>
@@ -17456,19 +17447,19 @@
         <v>4620207491133</v>
       </c>
       <c r="F471" s="5" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G471" s="1"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
+        <v>941</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="C472" s="3" t="s">
         <v>943</v>
-      </c>
-      <c r="B472" s="3" t="s">
-        <v>944</v>
-      </c>
-      <c r="C472" s="3" t="s">
-        <v>945</v>
       </c>
       <c r="D472" s="4">
         <v>4301135753</v>
@@ -17477,19 +17468,19 @@
         <v>4620207490914</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G472" s="1"/>
     </row>
     <row r="473" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D473" s="4">
         <v>4301070962</v>
@@ -17498,19 +17489,19 @@
         <v>4607111038609</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="G473" s="1"/>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D474" s="4">
         <v>4301070959</v>
@@ -17519,19 +17510,19 @@
         <v>4607111038616</v>
       </c>
       <c r="F474" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G474" s="1"/>
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D475" s="4">
         <v>4301071075</v>
@@ -17540,19 +17531,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G475" s="1"/>
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
+        <v>949</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="C476" s="3" t="s">
         <v>951</v>
-      </c>
-      <c r="B476" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="C476" s="3" t="s">
-        <v>953</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17561,7 +17552,7 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G476" s="1"/>
     </row>
@@ -17588,34 +17579,34 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D478" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E478" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>738</v>
+        <v>1057</v>
       </c>
       <c r="G478" s="1"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D479" s="4">
         <v>4301135753</v>
@@ -17624,19 +17615,19 @@
         <v>4620207490914</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D480" s="4">
         <v>4301131046</v>
@@ -17645,19 +17636,19 @@
         <v>4607111034137</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G480" s="1"/>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C481" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D481" s="4">
         <v>4301131047</v>
@@ -17666,19 +17657,19 @@
         <v>4607111034120</v>
       </c>
       <c r="F481" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G481" s="1"/>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C482" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D482" s="4">
         <v>4301132188</v>
@@ -17687,19 +17678,19 @@
         <v>4607111036605</v>
       </c>
       <c r="F482" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G482" s="1"/>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C483" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D483" s="4">
         <v>4301132179</v>
@@ -17708,7 +17699,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G483" s="1"/>
     </row>
@@ -17735,7 +17726,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>618</v>
@@ -17750,7 +17741,7 @@
         <v>4607111039293</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G485" s="1"/>
     </row>
@@ -17798,13 +17789,13 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488" s="10" t="s">
+        <v>955</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="C488" s="3" t="s">
         <v>957</v>
-      </c>
-      <c r="B488" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="C488" s="3" t="s">
-        <v>959</v>
       </c>
       <c r="D488" s="4">
         <v>4301071094</v>
@@ -17813,19 +17804,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="G488" s="1"/>
     </row>
     <row r="489" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
+        <v>959</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="C489" s="3" t="s">
         <v>961</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="C489" s="3" t="s">
-        <v>963</v>
       </c>
       <c r="D489" s="4">
         <v>4301071093</v>
@@ -17834,13 +17825,13 @@
         <v>4620207490709</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>730</v>
@@ -17861,13 +17852,13 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D491" s="4">
         <v>4301132188</v>
@@ -17876,19 +17867,19 @@
         <v>4607111036605</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G491" s="1"/>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D492" s="4">
         <v>4301071090</v>
@@ -17897,19 +17888,19 @@
         <v>4620207490075</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G492" s="1"/>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D493" s="4">
         <v>4301071091</v>
@@ -17918,13 +17909,13 @@
         <v>4620207490044</v>
       </c>
       <c r="F493" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G493" s="1"/>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>662</v>
@@ -17945,7 +17936,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>718</v>
@@ -17966,13 +17957,13 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D496" s="4">
         <v>4301131047</v>
@@ -17981,19 +17972,19 @@
         <v>4607111034120</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G496" s="1"/>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D497" s="4">
         <v>4301131046</v>
@@ -18002,19 +17993,19 @@
         <v>4607111034137</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G497" s="1"/>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D498" s="4">
         <v>4301135793</v>
@@ -18023,19 +18014,19 @@
         <v>4620207491003</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G498" s="1"/>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D499" s="4">
         <v>4301135760</v>
@@ -18044,13 +18035,13 @@
         <v>4620207491010</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G499" s="1"/>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>180</v>
@@ -18071,7 +18062,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>164</v>
@@ -18092,7 +18083,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>610</v>
@@ -18113,7 +18104,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>614</v>
@@ -18134,7 +18125,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>618</v>
@@ -18149,13 +18140,13 @@
         <v>4607111039293</v>
       </c>
       <c r="F504" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G504" s="1"/>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>622</v>
@@ -18176,7 +18167,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>648</v>
@@ -18197,7 +18188,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>645</v>
@@ -18218,34 +18209,34 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D508" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E508" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F508" s="5" t="s">
-        <v>738</v>
+        <v>1057</v>
       </c>
       <c r="G508" s="1"/>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D509" s="4">
         <v>4301135753</v>
@@ -18254,13 +18245,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>693</v>
@@ -18281,13 +18272,13 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D511" s="4">
         <v>4301132179</v>
@@ -18296,19 +18287,19 @@
         <v>4607111035691</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G511" s="1"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="D512" s="4">
         <v>4301071063</v>
@@ -18317,13 +18308,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F512" s="5" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G512" s="1"/>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>491</v>
@@ -18344,13 +18335,13 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C514" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D514" s="4">
         <v>4301135834</v>
@@ -18359,19 +18350,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F514" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G514" s="1"/>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18380,19 +18371,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18401,19 +18392,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B517" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C517" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="B517" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C517" s="3" t="s">
-        <v>1010</v>
       </c>
       <c r="D517" s="4">
         <v>4301135873</v>
@@ -18422,19 +18413,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C518" s="3" t="s">
         <v>1016</v>
-      </c>
-      <c r="B518" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C518" s="3" t="s">
-        <v>1018</v>
       </c>
       <c r="D518" s="4">
         <v>4301135850</v>
@@ -18443,19 +18434,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C519" s="3" t="s">
         <v>1020</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>1022</v>
       </c>
       <c r="D519" s="4">
         <v>4301190117</v>
@@ -18464,19 +18455,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C520" s="3" t="s">
         <v>1024</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C520" s="3" t="s">
-        <v>1026</v>
       </c>
       <c r="D520" s="4">
         <v>4301190115</v>
@@ -18485,19 +18476,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C521" s="3" t="s">
         <v>1028</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>1030</v>
       </c>
       <c r="D521" s="4">
         <v>4301135865</v>
@@ -18506,19 +18497,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C522" s="3" t="s">
         <v>1033</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>1035</v>
       </c>
       <c r="D522" s="4">
         <v>4301190116</v>
@@ -18527,19 +18518,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D523" s="4">
         <v>4301071112</v>
@@ -18548,19 +18539,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B524" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C524" s="3" t="s">
         <v>1037</v>
-      </c>
-      <c r="B524" s="3" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C524" s="3" t="s">
-        <v>1039</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18569,13 +18560,13 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G524" s="1"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="17" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B525" s="18" t="s">
         <v>614</v>
@@ -18594,12 +18585,12 @@
       </c>
       <c r="G525" s="21"/>
       <c r="H525" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="17" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B526" s="18" t="s">
         <v>106</v>
@@ -18618,12 +18609,12 @@
       </c>
       <c r="G526" s="21"/>
       <c r="H526" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="17" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B527" s="18" t="s">
         <v>622</v>
@@ -18642,12 +18633,12 @@
       </c>
       <c r="G527" s="21"/>
       <c r="H527" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="17" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B528" s="18" t="s">
         <v>610</v>
@@ -18666,12 +18657,12 @@
       </c>
       <c r="G528" s="21"/>
       <c r="H528" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="17" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B529" s="18" t="s">
         <v>288</v>
@@ -18690,18 +18681,18 @@
       </c>
       <c r="G529" s="21"/>
       <c r="H529" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="17" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D530" s="4">
         <v>4301071117</v>
@@ -18710,18 +18701,18 @@
         <v>4620207491737</v>
       </c>
       <c r="F530" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G530" s="1">
         <v>180</v>
       </c>
       <c r="H530" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="17" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>297</v>
@@ -18740,12 +18731,12 @@
       </c>
       <c r="G531" s="21"/>
       <c r="H531" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="17" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B532" s="18" t="s">
         <v>313</v>
@@ -18764,12 +18755,12 @@
       </c>
       <c r="G532" s="21"/>
       <c r="H532" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="17" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B533" s="18" t="s">
         <v>547</v>
@@ -18788,18 +18779,18 @@
       </c>
       <c r="G533" s="21"/>
       <c r="H533" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="17" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D534" s="4">
         <v>4301135760</v>
@@ -18808,16 +18799,16 @@
         <v>4620207491010</v>
       </c>
       <c r="F534" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G534" s="21"/>
       <c r="H534" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="17" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B535" s="3" t="s">
         <v>110</v>
@@ -18836,12 +18827,12 @@
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="17" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B536" s="18" t="s">
         <v>618</v>
@@ -18860,12 +18851,12 @@
       </c>
       <c r="G536" s="21"/>
       <c r="H536" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="17" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B537" s="18" t="s">
         <v>645</v>
@@ -18884,12 +18875,12 @@
       </c>
       <c r="G537" s="21"/>
       <c r="H537" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="17" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B538" s="3" t="s">
         <v>648</v>
@@ -18908,18 +18899,18 @@
       </c>
       <c r="G538" s="21"/>
       <c r="H538" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="17" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D539" s="4">
         <v>4301135793</v>
@@ -18928,16 +18919,16 @@
         <v>4620207491003</v>
       </c>
       <c r="F539" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="17" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>377</v>
@@ -18956,12 +18947,12 @@
       </c>
       <c r="G540" s="21"/>
       <c r="H540" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="17" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>543</v>
@@ -18980,12 +18971,12 @@
       </c>
       <c r="G541" s="21"/>
       <c r="H541" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="17" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B542" s="18" t="s">
         <v>593</v>
@@ -19004,18 +18995,18 @@
       </c>
       <c r="G542" s="21"/>
       <c r="H542" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="17" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B543" s="18" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C543" s="18" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D543" s="19">
         <v>4301132079</v>
@@ -19028,12 +19019,12 @@
       </c>
       <c r="G543" s="21"/>
       <c r="H543" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="17" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B544" s="18" t="s">
         <v>159</v>
@@ -19052,12 +19043,12 @@
       </c>
       <c r="G544" s="21"/>
       <c r="H544" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="17" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>294</v>
@@ -19076,18 +19067,18 @@
       </c>
       <c r="G545" s="21"/>
       <c r="H545" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="17" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D546" s="4">
         <v>4301071109</v>
@@ -19096,40 +19087,40 @@
         <v>4607111035929</v>
       </c>
       <c r="F546" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="17" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>736</v>
+        <v>1055</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>737</v>
+        <v>1056</v>
       </c>
       <c r="D547" s="4">
-        <v>4301135550</v>
+        <v>4301135946</v>
       </c>
       <c r="E547" s="3">
-        <v>4607111034199</v>
+        <v>4620207491553</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>738</v>
+        <v>1057</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="17" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B548" s="18" t="s">
         <v>733</v>
@@ -19148,12 +19139,12 @@
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="17" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B549" s="18" t="s">
         <v>606</v>
@@ -19172,18 +19163,18 @@
       </c>
       <c r="G549" s="21"/>
       <c r="H549" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="17" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B550" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C550" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D550" s="4">
         <v>4301131047</v>
@@ -19192,22 +19183,22 @@
         <v>4607111034120</v>
       </c>
       <c r="F550" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G550" s="21"/>
       <c r="H550" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="17" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D551" s="4">
         <v>4301135763</v>
@@ -19216,16 +19207,16 @@
         <v>4620207491027</v>
       </c>
       <c r="F551" s="5" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G551" s="21"/>
       <c r="H551" s="22" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="17" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B552" s="18" t="s">
         <v>551</v>
@@ -19244,12 +19235,12 @@
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="17" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B553" s="18" t="s">
         <v>700</v>
@@ -19268,18 +19259,18 @@
       </c>
       <c r="G553" s="21"/>
       <c r="H553" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="17" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C554" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D554" s="4">
         <v>4301131046</v>
@@ -19288,22 +19279,22 @@
         <v>4607111034137</v>
       </c>
       <c r="F554" s="5" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G554" s="21"/>
       <c r="H554" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="17" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C555" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D555" s="4">
         <v>4301136079</v>
@@ -19312,22 +19303,22 @@
         <v>4607025784319</v>
       </c>
       <c r="F555" s="5" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G555" s="21"/>
       <c r="H555" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="17" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D556" s="4">
         <v>4301135753</v>
@@ -19336,22 +19327,22 @@
         <v>4620207490914</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="G556" s="21"/>
       <c r="H556" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="17" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D557" s="4">
         <v>4301135778</v>
@@ -19360,22 +19351,22 @@
         <v>4620207490853</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="17" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D558" s="4">
         <v>4301132179</v>
@@ -19384,16 +19375,16 @@
         <v>4607111035691</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="17" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B559" s="3" t="s">
         <v>730</v>
@@ -19412,12 +19403,12 @@
       </c>
       <c r="G559" s="21"/>
       <c r="H559" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" s="17" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B560" s="18" t="s">
         <v>370</v>
@@ -19436,18 +19427,18 @@
       </c>
       <c r="G560" s="21"/>
       <c r="H560" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="17" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C561" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D561" s="4">
         <v>4301135571</v>
@@ -19456,22 +19447,22 @@
         <v>4607111035028</v>
       </c>
       <c r="F561" s="5" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G561" s="21"/>
       <c r="H561" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" s="17" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D562" s="4">
         <v>4301135768</v>
@@ -19480,16 +19471,16 @@
         <v>4620207491034</v>
       </c>
       <c r="F562" s="5" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G562" s="21"/>
       <c r="H562" s="16" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="563" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A563" s="17" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B563" s="18" t="s">
         <v>482</v>
@@ -19508,12 +19499,12 @@
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="17" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B564" s="18" t="s">
         <v>363</v>
@@ -19532,18 +19523,18 @@
       </c>
       <c r="G564" s="21"/>
       <c r="H564" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="10" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C565" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D565" s="4">
         <v>4301070990</v>
@@ -19552,22 +19543,22 @@
         <v>4607111038494</v>
       </c>
       <c r="F565" s="5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G565" s="1"/>
       <c r="H565" s="16" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="17" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B566" s="18" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C566" s="18" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D566" s="19">
         <v>4301070990</v>
@@ -19576,22 +19567,22 @@
         <v>4607111038494</v>
       </c>
       <c r="F566" s="20" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G566" s="21"/>
       <c r="H566" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="17" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C567" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D567" s="4">
         <v>4301071107</v>
@@ -19600,22 +19591,22 @@
         <v>4607111035905</v>
       </c>
       <c r="F567" s="5" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G567" s="21"/>
       <c r="H567" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="17" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D568" s="4">
         <v>4301135824</v>
@@ -19624,16 +19615,16 @@
         <v>4607111039095</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" s="17" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B569" s="18" t="s">
         <v>180</v>
@@ -19652,7 +19643,7 @@
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -19676,12 +19667,12 @@
       </c>
       <c r="G570" s="21"/>
       <c r="H570" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="17" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B571" s="18" t="s">
         <v>124</v>
@@ -19700,12 +19691,12 @@
       </c>
       <c r="G571" s="21"/>
       <c r="H571" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="17" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B572" s="3" t="s">
         <v>718</v>
@@ -19724,12 +19715,12 @@
       </c>
       <c r="G572" s="21"/>
       <c r="H572" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="17" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B573" s="18" t="s">
         <v>662</v>
@@ -19748,12 +19739,12 @@
       </c>
       <c r="G573" s="21"/>
       <c r="H573" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="17" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B574" s="18" t="s">
         <v>679</v>
@@ -19772,12 +19763,12 @@
       </c>
       <c r="G574" s="21"/>
       <c r="H574" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="17" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B575" s="18" t="s">
         <v>176</v>
@@ -19796,12 +19787,12 @@
       </c>
       <c r="G575" s="21"/>
       <c r="H575" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" s="17" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B576" s="3" t="s">
         <v>164</v>
@@ -19820,12 +19811,12 @@
       </c>
       <c r="G576" s="21"/>
       <c r="H576" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" s="17" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B577" s="18" t="s">
         <v>602</v>
@@ -19844,18 +19835,18 @@
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="578" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A578" s="17" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B578" s="18" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C578" s="18" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D578" s="19">
         <v>4301070959</v>
@@ -19864,22 +19855,22 @@
         <v>4607111038616</v>
       </c>
       <c r="F578" s="20" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G578" s="21"/>
       <c r="H578" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="579" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A579" s="17" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B579" s="18" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C579" s="18" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D579" s="19">
         <v>4301070962</v>
@@ -19888,16 +19879,16 @@
         <v>4607111038609</v>
       </c>
       <c r="F579" s="20" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="G579" s="21"/>
       <c r="H579" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" s="17" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B580" s="18" t="s">
         <v>249</v>
@@ -19916,12 +19907,12 @@
       </c>
       <c r="G580" s="21"/>
       <c r="H580" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="17" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B581" s="18" t="s">
         <v>693</v>
@@ -19940,12 +19931,12 @@
       </c>
       <c r="G581" s="21"/>
       <c r="H581" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" s="17" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B582" s="18" t="s">
         <v>722</v>
@@ -19964,12 +19955,12 @@
       </c>
       <c r="G582" s="21"/>
       <c r="H582" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" s="17" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B583" s="18" t="s">
         <v>666</v>
@@ -19988,12 +19979,12 @@
       </c>
       <c r="G583" s="21"/>
       <c r="H583" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" s="17" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B584" s="18" t="s">
         <v>478</v>
@@ -20012,12 +20003,12 @@
       </c>
       <c r="G584" s="21"/>
       <c r="H584" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" s="17" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B585" s="18" t="s">
         <v>584</v>
@@ -20036,12 +20027,12 @@
       </c>
       <c r="G585" s="21"/>
       <c r="H585" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" s="17" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B586" s="18" t="s">
         <v>335</v>
@@ -20060,18 +20051,18 @@
       </c>
       <c r="G586" s="21"/>
       <c r="H586" s="22" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" s="10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C587" s="3" t="s">
         <v>1046</v>
-      </c>
-      <c r="B587" s="3" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C587" s="3" t="s">
-        <v>1048</v>
       </c>
       <c r="D587" s="4">
         <v>4301135848</v>
@@ -20080,19 +20071,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F587" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G587" s="1"/>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B588" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C588" s="3" t="s">
         <v>1050</v>
-      </c>
-      <c r="B588" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C588" s="3" t="s">
-        <v>1052</v>
       </c>
       <c r="D588" s="4">
         <v>4301190118</v>
@@ -20101,7 +20092,7 @@
         <v>4620207491461</v>
       </c>
       <c r="F588" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G588" s="1"/>
     </row>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF980C1-4958-439F-B7AF-26AECCB9AF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446B7082-654D-460F-8FA5-7264CDA1573A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,10 +23,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$591</definedName>
     <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$526</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2804,12 +2810,6 @@
     <t>Пельмени Мясные с говядиной ТМ Стародворье сфера флоу-пак 1 кг  ПОКОМ</t>
   </si>
   <si>
-    <t>SU003889</t>
-  </si>
-  <si>
-    <t>P004971</t>
-  </si>
-  <si>
     <t>Снеки «Готовые чебупели с ветчиной и сыром» Фикс.вес 0,24 ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -3182,15 +3182,6 @@
     <t>Снеки «Чебупели со вкусом Фо бо» Фикс.вес 0,22 ТМ «Горячая штучка»</t>
   </si>
   <si>
-    <t>SU002961</t>
-  </si>
-  <si>
-    <t>P003431</t>
-  </si>
-  <si>
-    <t>Снеки «Чебуманы с говядиной» Фикс.вес 0,28 лоток ТМ «Горячая штучка»</t>
-  </si>
-  <si>
     <t>SU004226</t>
   </si>
   <si>
@@ -3216,6 +3207,21 @@
   </si>
   <si>
     <t>Мини-сосиски в ароматном тесте ВЕС ТМ Зареченские продукты  ПОКОМ</t>
+  </si>
+  <si>
+    <t>SU003601</t>
+  </si>
+  <si>
+    <t>P004597</t>
+  </si>
+  <si>
+    <t>Снеки «Чебуманы с говядиной» Фикс.вес 0,28 Пакет ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>SU004207</t>
+  </si>
+  <si>
+    <t>P005473</t>
   </si>
 </sst>
 </file>
@@ -3451,7 +3457,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Лист1"/>
@@ -6727,26 +6733,26 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D11" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D11" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E11" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G11" s="1" t="e">
         <f>VLOOKUP(E11,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -6754,26 +6760,26 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D12" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E12" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G12" s="1" t="e">
         <f>VLOOKUP(E12,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -6781,67 +6787,67 @@
         <v>186</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D13" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D13" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E13" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G13" s="1" t="e">
         <f>VLOOKUP(E13,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D14" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E14" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D15" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D15" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -6869,7 +6875,7 @@
         <v>#N/A</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6896,7 +6902,7 @@
         <v>#N/A</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6923,7 +6929,7 @@
         <v>#N/A</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6950,12 +6956,12 @@
         <v>#N/A</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>912</v>
@@ -6976,7 +6982,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>912</v>
@@ -7000,10 +7006,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D22" s="4">
         <v>4301135760</v>
@@ -7012,14 +7018,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G22" s="1" t="e">
         <f>VLOOKUP(E22,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7027,10 +7033,10 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D23" s="4">
         <v>4301135760</v>
@@ -7039,14 +7045,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G23" s="1" t="e">
         <f>VLOOKUP(E23,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7054,10 +7060,10 @@
         <v>188</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D24" s="4">
         <v>4301135760</v>
@@ -7066,25 +7072,25 @@
         <v>4620207491010</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G24" s="1" t="e">
         <f>VLOOKUP(E24,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D25" s="4">
         <v>4301135760</v>
@@ -7093,19 +7099,19 @@
         <v>4620207491010</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D26" s="4">
         <v>4301135760</v>
@@ -7114,7 +7120,7 @@
         <v>4620207491010</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -7142,7 +7148,7 @@
         <v>#N/A</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7169,7 +7175,7 @@
         <v>#N/A</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -7196,7 +7202,7 @@
         <v>#N/A</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7223,7 +7229,7 @@
         <v>#N/A</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -8408,10 +8414,10 @@
         <v>193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D80" s="4">
         <v>4301135753</v>
@@ -8420,14 +8426,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G80" s="1" t="e">
         <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8435,10 +8441,10 @@
         <v>685</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D81" s="4">
         <v>4301135753</v>
@@ -8447,14 +8453,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G81" s="1" t="e">
         <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8462,10 +8468,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D82" s="4">
         <v>4301135753</v>
@@ -8474,14 +8480,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G82" s="1" t="e">
         <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8489,10 +8495,10 @@
         <v>228</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D83" s="4">
         <v>4301135778</v>
@@ -8501,14 +8507,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G83" s="1" t="e">
         <f>VLOOKUP(E83,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8516,10 +8522,10 @@
         <v>194</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D84" s="4">
         <v>4301135778</v>
@@ -8528,14 +8534,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G84" s="1" t="e">
         <f>VLOOKUP(E84,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8543,10 +8549,10 @@
         <v>689</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D85" s="4">
         <v>4301135778</v>
@@ -8555,14 +8561,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G85" s="1" t="e">
         <f>VLOOKUP(E85,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8570,10 +8576,10 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D86" s="4">
         <v>4301135778</v>
@@ -8582,25 +8588,25 @@
         <v>4620207490853</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G86" s="1" t="e">
         <f>VLOOKUP(E86,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D87" s="4">
         <v>4301135778</v>
@@ -8609,19 +8615,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D88" s="4">
         <v>4301135778</v>
@@ -8630,19 +8636,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D89" s="4">
         <v>4301135778</v>
@@ -8651,7 +8657,7 @@
         <v>4620207490853</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -8804,10 +8810,10 @@
         <v>197</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D96" s="4">
         <v>4301137046</v>
@@ -8816,7 +8822,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G96" s="1">
         <v>180</v>
@@ -8827,10 +8833,10 @@
         <v>226</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D97" s="4">
         <v>4301137046</v>
@@ -8839,7 +8845,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G97" s="1">
         <v>180</v>
@@ -8850,10 +8856,10 @@
         <v>340</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D98" s="4">
         <v>4301137046</v>
@@ -8862,7 +8868,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G98" s="1">
         <v>180</v>
@@ -8873,10 +8879,10 @@
         <v>368</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D99" s="4">
         <v>4301137046</v>
@@ -8885,7 +8891,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G99" s="1">
         <v>180</v>
@@ -8896,10 +8902,10 @@
         <v>76</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D100" s="4">
         <v>4301137046</v>
@@ -8908,7 +8914,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G100" s="1">
         <v>180</v>
@@ -8919,10 +8925,10 @@
         <v>543</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D101" s="4">
         <v>4301137046</v>
@@ -8931,7 +8937,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G101" s="1">
         <v>180</v>
@@ -8942,10 +8948,10 @@
         <v>579</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D102" s="4">
         <v>4301137046</v>
@@ -8954,7 +8960,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G102" s="1">
         <v>180</v>
@@ -8962,13 +8968,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D103" s="4">
         <v>4301137046</v>
@@ -8977,7 +8983,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G103" s="1">
         <v>180</v>
@@ -8988,10 +8994,10 @@
         <v>578</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D104" s="4">
         <v>4301137046</v>
@@ -9000,7 +9006,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G104" s="1">
         <v>180</v>
@@ -9172,7 +9178,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>748</v>
@@ -9412,7 +9418,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>727</v>
@@ -11212,10 +11218,10 @@
         <v>109</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11224,7 +11230,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11236,10 +11242,10 @@
         <v>88</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D198" s="4">
         <v>4301071109</v>
@@ -11248,7 +11254,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11260,10 +11266,10 @@
         <v>150</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11272,7 +11278,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11284,10 +11290,10 @@
         <v>761</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11296,7 +11302,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11308,10 +11314,10 @@
         <v>151</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D201" s="4">
         <v>4301071107</v>
@@ -11320,7 +11326,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G201" s="1">
         <f>VLOOKUP(E201,[1]Лист1!$D:$M,10,0)</f>
@@ -11494,7 +11500,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>110</v>
@@ -11542,10 +11548,10 @@
         <v>111</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11554,13 +11560,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -11568,10 +11574,10 @@
         <v>90</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D212" s="4">
         <v>4301071117</v>
@@ -11580,13 +11586,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G212" s="1">
         <v>180</v>
       </c>
       <c r="H212" s="16" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -11888,10 +11894,10 @@
         <v>184</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D225" s="4">
         <v>4301135946</v>
@@ -11900,7 +11906,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G225" s="1"/>
     </row>
@@ -11909,10 +11915,10 @@
         <v>112</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D226" s="4">
         <v>4301135946</v>
@@ -11921,7 +11927,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G226" s="1"/>
     </row>
@@ -11930,10 +11936,10 @@
         <v>764</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D227" s="4">
         <v>4301135946</v>
@@ -11942,7 +11948,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G227" s="1"/>
     </row>
@@ -11951,10 +11957,10 @@
         <v>92</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D228" s="4">
         <v>4301135946</v>
@@ -11963,7 +11969,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G228" s="1"/>
     </row>
@@ -13288,7 +13294,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>877</v>
@@ -13312,7 +13318,7 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>877</v>
@@ -15005,10 +15011,10 @@
         <v>570</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D359" s="4">
         <v>4301135824</v>
@@ -15017,7 +15023,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G359" s="1"/>
     </row>
@@ -15026,10 +15032,10 @@
         <v>754</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D360" s="4">
         <v>4301135824</v>
@@ -15038,7 +15044,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -15047,10 +15053,10 @@
         <v>544</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D361" s="4">
         <v>4301135824</v>
@@ -15059,7 +15065,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G361" s="1"/>
     </row>
@@ -16202,19 +16208,19 @@
         <v>763</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="D416" s="4">
-        <v>4301135184</v>
+        <v>4301135591</v>
       </c>
       <c r="E416" s="3">
         <v>4607111036568</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16225,19 +16231,19 @@
         <v>857</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="D417" s="4">
-        <v>4301135184</v>
+        <v>4301135591</v>
       </c>
       <c r="E417" s="3">
         <v>4607111036568</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16248,19 +16254,19 @@
         <v>694</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="D418" s="4">
-        <v>4301135184</v>
+        <v>4301135591</v>
       </c>
       <c r="E418" s="3">
         <v>4607111036568</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="G418" s="1">
         <v>180</v>
@@ -16841,10 +16847,10 @@
         <v>873</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16864,10 +16870,10 @@
         <v>881</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16887,10 +16893,10 @@
         <v>882</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16910,10 +16916,10 @@
         <v>864</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D448" s="4">
         <v>4301135826</v>
@@ -17314,10 +17320,10 @@
         <v>636</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D466" s="4">
         <v>4301135760</v>
@@ -17326,11 +17332,11 @@
         <v>4620207491010</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
@@ -17464,13 +17470,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C473" s="3" t="s">
         <v>938</v>
-      </c>
-      <c r="B473" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="C473" s="3" t="s">
-        <v>940</v>
       </c>
       <c r="D473" s="4">
         <v>4301135753</v>
@@ -17479,13 +17485,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G473" s="1"/>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>851</v>
@@ -17506,7 +17512,7 @@
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>848</v>
@@ -17527,13 +17533,13 @@
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17542,19 +17548,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G476" s="1"/>
     </row>
     <row r="477" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
+        <v>944</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="C477" s="3" t="s">
         <v>946</v>
-      </c>
-      <c r="B477" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="C477" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="D477" s="4">
         <v>4301071075</v>
@@ -17563,7 +17569,7 @@
         <v>4620207491102</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G477" s="1"/>
     </row>
@@ -17593,10 +17599,10 @@
         <v>733</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D479" s="4">
         <v>4301135946</v>
@@ -17605,19 +17611,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D480" s="4">
         <v>4301135753</v>
@@ -17626,7 +17632,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G480" s="1"/>
     </row>
@@ -17800,13 +17806,13 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="C489" s="3" t="s">
         <v>952</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>953</v>
-      </c>
-      <c r="C489" s="3" t="s">
-        <v>954</v>
       </c>
       <c r="D489" s="4">
         <v>4301071094</v>
@@ -17815,19 +17821,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C490" s="3" t="s">
         <v>956</v>
-      </c>
-      <c r="B490" s="3" t="s">
-        <v>957</v>
-      </c>
-      <c r="C490" s="3" t="s">
-        <v>958</v>
       </c>
       <c r="D490" s="4">
         <v>4301071093</v>
@@ -17836,13 +17842,13 @@
         <v>4620207490709</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G490" s="1"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>727</v>
@@ -17863,7 +17869,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>748</v>
@@ -17884,7 +17890,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>739</v>
@@ -17905,7 +17911,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>745</v>
@@ -17926,7 +17932,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>659</v>
@@ -17947,7 +17953,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>715</v>
@@ -17968,7 +17974,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>770</v>
@@ -17989,7 +17995,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>868</v>
@@ -18010,34 +18016,34 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B499" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D499" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E499" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F499" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C499" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D499" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E499" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F499" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G499" s="1"/>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D500" s="4">
         <v>4301135760</v>
@@ -18046,13 +18052,13 @@
         <v>4620207491010</v>
       </c>
       <c r="F500" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G500" s="1"/>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>180</v>
@@ -18073,7 +18079,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>164</v>
@@ -18094,7 +18100,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>607</v>
@@ -18115,7 +18121,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>611</v>
@@ -18136,7 +18142,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>615</v>
@@ -18157,7 +18163,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>619</v>
@@ -18178,7 +18184,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>645</v>
@@ -18199,7 +18205,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>642</v>
@@ -18220,13 +18226,13 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D509" s="4">
         <v>4301135946</v>
@@ -18235,19 +18241,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D510" s="4">
         <v>4301135753</v>
@@ -18256,13 +18262,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G510" s="1"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>690</v>
@@ -18283,7 +18289,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>858</v>
@@ -18304,13 +18310,13 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D513" s="4">
         <v>4301071063</v>
@@ -18319,13 +18325,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G513" s="1"/>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>491</v>
@@ -18346,13 +18352,13 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18361,19 +18367,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18382,19 +18388,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D517" s="4">
         <v>4301135834</v>
@@ -18403,19 +18409,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C518" s="3" t="s">
         <v>1003</v>
-      </c>
-      <c r="B518" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C518" s="3" t="s">
-        <v>1005</v>
       </c>
       <c r="D518" s="4">
         <v>4301135873</v>
@@ -18424,19 +18430,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C519" s="3" t="s">
         <v>1011</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>1013</v>
       </c>
       <c r="D519" s="4">
         <v>4301135850</v>
@@ -18445,19 +18451,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C520" s="3" t="s">
         <v>1015</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C520" s="3" t="s">
-        <v>1017</v>
       </c>
       <c r="D520" s="4">
         <v>4301190117</v>
@@ -18466,19 +18472,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C521" s="3" t="s">
         <v>1019</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>1021</v>
       </c>
       <c r="D521" s="4">
         <v>4301190115</v>
@@ -18487,19 +18493,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C522" s="3" t="s">
         <v>1023</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>1025</v>
       </c>
       <c r="D522" s="4">
         <v>4301135865</v>
@@ -18508,19 +18514,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B523" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C523" s="3" t="s">
         <v>1028</v>
-      </c>
-      <c r="B523" s="3" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>1030</v>
       </c>
       <c r="D523" s="4">
         <v>4301190116</v>
@@ -18529,19 +18535,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18550,19 +18556,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G524" s="1"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B525" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C525" s="3" t="s">
         <v>1032</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C525" s="3" t="s">
-        <v>1034</v>
       </c>
       <c r="D525" s="4">
         <v>4301071112</v>
@@ -18571,7 +18577,7 @@
         <v>4620207491256</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G525" s="1"/>
     </row>
@@ -18700,10 +18706,10 @@
         <v>786</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D531" s="4">
         <v>4301071117</v>
@@ -18712,7 +18718,7 @@
         <v>4620207491737</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G531" s="1">
         <v>180</v>
@@ -18798,10 +18804,10 @@
         <v>790</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D535" s="4">
         <v>4301135760</v>
@@ -18810,11 +18816,11 @@
         <v>4620207491010</v>
       </c>
       <c r="F535" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
@@ -18918,23 +18924,23 @@
         <v>795</v>
       </c>
       <c r="B540" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D540" s="4">
+        <v>4301135914</v>
+      </c>
+      <c r="E540" s="3">
+        <v>4620207491621</v>
+      </c>
+      <c r="F540" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="C540" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="D540" s="4">
-        <v>4301135793</v>
-      </c>
-      <c r="E540" s="3">
-        <v>4620207491003</v>
-      </c>
-      <c r="F540" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="G540" s="21"/>
       <c r="H540" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
@@ -18966,10 +18972,10 @@
         <v>797</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D542" s="4">
         <v>4301137046</v>
@@ -18978,7 +18984,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="G542" s="1">
         <v>180</v>
@@ -19088,10 +19094,10 @@
         <v>802</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D547" s="4">
         <v>4301071109</v>
@@ -19100,7 +19106,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
@@ -19112,10 +19118,10 @@
         <v>803</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="D548" s="4">
         <v>4301135946</v>
@@ -19124,7 +19130,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
@@ -19224,7 +19230,7 @@
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -19328,10 +19334,10 @@
         <v>812</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D557" s="4">
         <v>4301135753</v>
@@ -19340,7 +19346,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
@@ -19352,10 +19358,10 @@
         <v>813</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D558" s="4">
         <v>4301135778</v>
@@ -19364,11 +19370,11 @@
         <v>4620207490853</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="16" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
@@ -19488,7 +19494,7 @@
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="16" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="564" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
@@ -19592,10 +19598,10 @@
         <v>823</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D568" s="4">
         <v>4301071107</v>
@@ -19604,7 +19610,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19616,10 +19622,10 @@
         <v>824</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D569" s="4">
         <v>4301135824</v>
@@ -19628,7 +19634,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F569" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
@@ -20069,13 +20075,13 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D588" s="4">
         <v>4301135848</v>
@@ -20084,19 +20090,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F588" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G588" s="1"/>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C589" s="3" t="s">
         <v>1041</v>
-      </c>
-      <c r="B589" s="3" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C589" s="3" t="s">
-        <v>1043</v>
       </c>
       <c r="D589" s="4">
         <v>4301135848</v>
@@ -20105,19 +20111,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F589" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G589" s="1"/>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D590" s="4">
         <v>4301190118</v>
@@ -20126,19 +20132,19 @@
         <v>4620207491461</v>
       </c>
       <c r="F590" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G590" s="1"/>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C591" s="3" t="s">
         <v>1045</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C591" s="3" t="s">
-        <v>1047</v>
       </c>
       <c r="D591" s="4">
         <v>4301190118</v>
@@ -20147,7 +20153,7 @@
         <v>4620207491461</v>
       </c>
       <c r="F591" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G591" s="1"/>
     </row>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446B7082-654D-460F-8FA5-7264CDA1573A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A766BD-F410-4255-B6DC-E3598635FC09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1063">
   <si>
     <t>1С</t>
   </si>
@@ -2111,12 +2111,6 @@
     <t>Снеки «Круггетсы Сочные» Фикс.вес 0,25 ф/п ТМ «Горячая штучка»</t>
   </si>
   <si>
-    <t>SU003596</t>
-  </si>
-  <si>
-    <t>P004594</t>
-  </si>
-  <si>
     <t>Снеки «Пекерсы с индейкой в сливочном соусе» Фикс.вес 0,25 Пакет ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -2672,12 +2666,6 @@
     <t>Чебуреки «Чебуреки со свининой и говядиной» Фикс.вес 0,36 Пакет ТМ «Горячая штучка»</t>
   </si>
   <si>
-    <t>SU003605</t>
-  </si>
-  <si>
-    <t>P004595</t>
-  </si>
-  <si>
     <t>Снеки «Готовые чебупели сочные с мясом» Фикс.вес 0,48 ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -2777,12 +2765,6 @@
     <t>Снеки «Готовые чебупели с мясом» Фикс.вес 0,24 ТМ «Горячая штучка»</t>
   </si>
   <si>
-    <t>SU003892</t>
-  </si>
-  <si>
-    <t>P004974</t>
-  </si>
-  <si>
     <t>Пельмени «Мясные с говядиной» Фикс.вес 1 сфера ТМ «Стародворье»</t>
   </si>
   <si>
@@ -3222,6 +3204,30 @@
   </si>
   <si>
     <t>P005473</t>
+  </si>
+  <si>
+    <t>SU004257</t>
+  </si>
+  <si>
+    <t>P005598</t>
+  </si>
+  <si>
+    <t>Снеки «Готовые чебупели с мясом» (без свинины) Фикс.вес 0,24 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>SU004258</t>
+  </si>
+  <si>
+    <t>P005556</t>
+  </si>
+  <si>
+    <t>SU004223</t>
+  </si>
+  <si>
+    <t>P005489</t>
+  </si>
+  <si>
+    <t>Снеки «Готовые пекерсы с индейкой в сливочном соусе» Фикс.вес 0,25 ТМ «Горячая штучка»</t>
   </si>
 </sst>
 </file>
@@ -6637,10 +6643,10 @@
         <v>325</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D7" s="4">
         <v>4301135574</v>
@@ -6649,7 +6655,7 @@
         <v>4607111033659</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G7" s="1">
         <f>VLOOKUP(E7,[1]Лист1!$D:$M,10,0)</f>
@@ -6661,10 +6667,10 @@
         <v>338</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D8" s="4">
         <v>4301135574</v>
@@ -6673,7 +6679,7 @@
         <v>4607111033659</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G8" s="1">
         <f>VLOOKUP(E8,[1]Лист1!$D:$M,10,0)</f>
@@ -6685,10 +6691,10 @@
         <v>215</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D9" s="4">
         <v>4301135574</v>
@@ -6697,7 +6703,7 @@
         <v>4607111033659</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G9" s="1">
         <f>VLOOKUP(E9,[1]Лист1!$D:$M,10,0)</f>
@@ -6709,10 +6715,10 @@
         <v>183</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D10" s="4">
         <v>4301135574</v>
@@ -6721,7 +6727,7 @@
         <v>4607111033659</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G10" s="1">
         <f>VLOOKUP(E10,[1]Лист1!$D:$M,10,0)</f>
@@ -6733,10 +6739,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D11" s="4">
         <v>4301135914</v>
@@ -6745,14 +6751,14 @@
         <v>4620207491621</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G11" s="1" t="e">
         <f>VLOOKUP(E11,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -6760,10 +6766,10 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D12" s="4">
         <v>4301135914</v>
@@ -6772,14 +6778,14 @@
         <v>4620207491621</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G12" s="1" t="e">
         <f>VLOOKUP(E12,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -6787,10 +6793,10 @@
         <v>186</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D13" s="4">
         <v>4301135914</v>
@@ -6799,25 +6805,25 @@
         <v>4620207491621</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G13" s="1" t="e">
         <f>VLOOKUP(E13,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D14" s="4">
         <v>4301135914</v>
@@ -6826,19 +6832,19 @@
         <v>4620207491621</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D15" s="4">
         <v>4301135914</v>
@@ -6847,7 +6853,7 @@
         <v>4620207491621</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G15" s="1"/>
     </row>
@@ -6856,26 +6862,26 @@
         <v>216</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D16" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E16" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G16" s="1" t="e">
         <f>VLOOKUP(E16,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6883,26 +6889,26 @@
         <v>412</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D17" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E17" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G17" s="1" t="e">
         <f>VLOOKUP(E17,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6910,26 +6916,26 @@
         <v>418</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D18" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E18" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G18" s="1" t="e">
         <f>VLOOKUP(E18,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6937,67 +6943,67 @@
         <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D19" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E19" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G19" s="1" t="e">
         <f>VLOOKUP(E19,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D20" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E20" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D21" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E21" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -7006,10 +7012,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D22" s="4">
         <v>4301135760</v>
@@ -7018,14 +7024,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G22" s="1" t="e">
         <f>VLOOKUP(E22,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7033,10 +7039,10 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D23" s="4">
         <v>4301135760</v>
@@ -7045,14 +7051,14 @@
         <v>4620207491010</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G23" s="1" t="e">
         <f>VLOOKUP(E23,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7060,10 +7066,10 @@
         <v>188</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D24" s="4">
         <v>4301135760</v>
@@ -7072,25 +7078,25 @@
         <v>4620207491010</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G24" s="1" t="e">
         <f>VLOOKUP(E24,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D25" s="4">
         <v>4301135760</v>
@@ -7099,19 +7105,19 @@
         <v>4620207491010</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D26" s="4">
         <v>4301135760</v>
@@ -7120,7 +7126,7 @@
         <v>4620207491010</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -7129,10 +7135,10 @@
         <v>128</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D27" s="4">
         <v>4301135763</v>
@@ -7141,14 +7147,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G27" s="1" t="e">
         <f>VLOOKUP(E27,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7156,10 +7162,10 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D28" s="4">
         <v>4301135763</v>
@@ -7168,14 +7174,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G28" s="1" t="e">
         <f>VLOOKUP(E28,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -7183,10 +7189,10 @@
         <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D29" s="4">
         <v>4301135763</v>
@@ -7195,14 +7201,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G29" s="1" t="e">
         <f>VLOOKUP(E29,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7210,10 +7216,10 @@
         <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D30" s="4">
         <v>4301135763</v>
@@ -7222,14 +7228,14 @@
         <v>4620207491027</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G30" s="1" t="e">
         <f>VLOOKUP(E30,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -7237,10 +7243,10 @@
         <v>400</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D31" s="4">
         <v>4301136079</v>
@@ -7249,7 +7255,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G31" s="1">
         <f>VLOOKUP(E31,[1]Лист1!$D:$M,10,0)</f>
@@ -7261,10 +7267,10 @@
         <v>421</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D32" s="4">
         <v>4301136079</v>
@@ -7273,7 +7279,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G32" s="1">
         <f>VLOOKUP(E32,[1]Лист1!$D:$M,10,0)</f>
@@ -7285,10 +7291,10 @@
         <v>503</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D33" s="4">
         <v>4301136079</v>
@@ -7297,7 +7303,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G33" s="1">
         <f>VLOOKUP(E33,[1]Лист1!$D:$M,10,0)</f>
@@ -7309,10 +7315,10 @@
         <v>190</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D34" s="4">
         <v>4301136079</v>
@@ -7321,7 +7327,7 @@
         <v>4607025784319</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G34" s="1">
         <f>VLOOKUP(E34,[1]Лист1!$D:$M,10,0)</f>
@@ -8414,10 +8420,10 @@
         <v>193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D80" s="4">
         <v>4301135753</v>
@@ -8426,14 +8432,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G80" s="1" t="e">
         <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8441,10 +8447,10 @@
         <v>685</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D81" s="4">
         <v>4301135753</v>
@@ -8453,14 +8459,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G81" s="1" t="e">
         <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8468,10 +8474,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D82" s="4">
         <v>4301135753</v>
@@ -8480,14 +8486,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G82" s="1" t="e">
         <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8495,10 +8501,10 @@
         <v>228</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D83" s="4">
         <v>4301135778</v>
@@ -8507,14 +8513,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G83" s="1" t="e">
         <f>VLOOKUP(E83,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8522,10 +8528,10 @@
         <v>194</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D84" s="4">
         <v>4301135778</v>
@@ -8534,14 +8540,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G84" s="1" t="e">
         <f>VLOOKUP(E84,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8549,10 +8555,10 @@
         <v>689</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D85" s="4">
         <v>4301135778</v>
@@ -8561,14 +8567,14 @@
         <v>4620207490853</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G85" s="1" t="e">
         <f>VLOOKUP(E85,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8576,10 +8582,10 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D86" s="4">
         <v>4301135778</v>
@@ -8588,25 +8594,25 @@
         <v>4620207490853</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G86" s="1" t="e">
         <f>VLOOKUP(E86,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D87" s="4">
         <v>4301135778</v>
@@ -8615,19 +8621,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D88" s="4">
         <v>4301135778</v>
@@ -8636,19 +8642,19 @@
         <v>4620207490853</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D89" s="4">
         <v>4301135778</v>
@@ -8657,7 +8663,7 @@
         <v>4620207490853</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -8666,10 +8672,10 @@
         <v>116</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D90" s="4">
         <v>4301131046</v>
@@ -8678,7 +8684,7 @@
         <v>4607111034137</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G90" s="1">
         <f>VLOOKUP(E90,[1]Лист1!$D:$M,10,0)</f>
@@ -8690,10 +8696,10 @@
         <v>121</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D91" s="4">
         <v>4301131046</v>
@@ -8702,7 +8708,7 @@
         <v>4607111034137</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G91" s="1">
         <f>VLOOKUP(E91,[1]Лист1!$D:$M,10,0)</f>
@@ -8714,10 +8720,10 @@
         <v>195</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D92" s="4">
         <v>4301131046</v>
@@ -8726,7 +8732,7 @@
         <v>4607111034137</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G92" s="1">
         <f>VLOOKUP(E92,[1]Лист1!$D:$M,10,0)</f>
@@ -8738,10 +8744,10 @@
         <v>117</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D93" s="4">
         <v>4301131047</v>
@@ -8750,7 +8756,7 @@
         <v>4607111034120</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G93" s="1">
         <f>VLOOKUP(E93,[1]Лист1!$D:$M,10,0)</f>
@@ -8762,10 +8768,10 @@
         <v>122</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D94" s="4">
         <v>4301131047</v>
@@ -8774,7 +8780,7 @@
         <v>4607111034120</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G94" s="1">
         <f>VLOOKUP(E94,[1]Лист1!$D:$M,10,0)</f>
@@ -8786,10 +8792,10 @@
         <v>196</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D95" s="4">
         <v>4301131047</v>
@@ -8798,7 +8804,7 @@
         <v>4607111034120</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G95" s="1">
         <f>VLOOKUP(E95,[1]Лист1!$D:$M,10,0)</f>
@@ -8810,10 +8816,10 @@
         <v>197</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D96" s="4">
         <v>4301137046</v>
@@ -8822,7 +8828,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G96" s="1">
         <v>180</v>
@@ -8833,10 +8839,10 @@
         <v>226</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D97" s="4">
         <v>4301137046</v>
@@ -8845,7 +8851,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G97" s="1">
         <v>180</v>
@@ -8856,10 +8862,10 @@
         <v>340</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D98" s="4">
         <v>4301137046</v>
@@ -8868,7 +8874,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G98" s="1">
         <v>180</v>
@@ -8879,10 +8885,10 @@
         <v>368</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D99" s="4">
         <v>4301137046</v>
@@ -8891,7 +8897,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G99" s="1">
         <v>180</v>
@@ -8902,10 +8908,10 @@
         <v>76</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D100" s="4">
         <v>4301137046</v>
@@ -8914,7 +8920,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G100" s="1">
         <v>180</v>
@@ -8925,10 +8931,10 @@
         <v>543</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D101" s="4">
         <v>4301137046</v>
@@ -8937,7 +8943,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G101" s="1">
         <v>180</v>
@@ -8948,10 +8954,10 @@
         <v>579</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D102" s="4">
         <v>4301137046</v>
@@ -8960,7 +8966,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G102" s="1">
         <v>180</v>
@@ -8968,13 +8974,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D103" s="4">
         <v>4301137046</v>
@@ -8983,7 +8989,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G103" s="1">
         <v>180</v>
@@ -8994,10 +9000,10 @@
         <v>578</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D104" s="4">
         <v>4301137046</v>
@@ -9006,7 +9012,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G104" s="1">
         <v>180</v>
@@ -9017,10 +9023,10 @@
         <v>217</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D105" s="4">
         <v>4301132186</v>
@@ -9029,7 +9035,7 @@
         <v>4607111036520</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G105" s="1">
         <v>180</v>
@@ -9040,10 +9046,10 @@
         <v>310</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D106" s="4">
         <v>4301132186</v>
@@ -9052,7 +9058,7 @@
         <v>4607111036520</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G106" s="1">
         <v>180</v>
@@ -9063,10 +9069,10 @@
         <v>444</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D107" s="4">
         <v>4301132186</v>
@@ -9075,7 +9081,7 @@
         <v>4607111036520</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G107" s="1">
         <v>180</v>
@@ -9086,10 +9092,10 @@
         <v>198</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D108" s="4">
         <v>4301132186</v>
@@ -9098,7 +9104,7 @@
         <v>4607111036520</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G108" s="1">
         <v>180</v>
@@ -9109,10 +9115,10 @@
         <v>427</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D109" s="4">
         <v>4301132184</v>
@@ -9121,7 +9127,7 @@
         <v>4607111036599</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G109" s="1">
         <f>VLOOKUP(E109,[1]Лист1!$D:$M,10,0)</f>
@@ -9133,10 +9139,10 @@
         <v>218</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D110" s="4">
         <v>4301132184</v>
@@ -9145,7 +9151,7 @@
         <v>4607111036599</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G110" s="1">
         <f>VLOOKUP(E110,[1]Лист1!$D:$M,10,0)</f>
@@ -9157,10 +9163,10 @@
         <v>199</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D111" s="4">
         <v>4301132184</v>
@@ -9169,7 +9175,7 @@
         <v>4607111036599</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G111" s="1">
         <f>VLOOKUP(E111,[1]Лист1!$D:$M,10,0)</f>
@@ -9178,13 +9184,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D112" s="4">
         <v>4301132188</v>
@@ -9193,7 +9199,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G112" s="1">
         <f>VLOOKUP(E112,[1]Лист1!$D:$M,10,0)</f>
@@ -9205,10 +9211,10 @@
         <v>402</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D113" s="4">
         <v>4301132188</v>
@@ -9217,7 +9223,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G113" s="1">
         <f>VLOOKUP(E113,[1]Лист1!$D:$M,10,0)</f>
@@ -9229,10 +9235,10 @@
         <v>219</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D114" s="4">
         <v>4301132188</v>
@@ -9241,7 +9247,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G114" s="1">
         <f>VLOOKUP(E114,[1]Лист1!$D:$M,10,0)</f>
@@ -9253,10 +9259,10 @@
         <v>200</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D115" s="4">
         <v>4301132188</v>
@@ -9265,7 +9271,7 @@
         <v>4607111036605</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G115" s="1">
         <f>VLOOKUP(E115,[1]Лист1!$D:$M,10,0)</f>
@@ -9277,10 +9283,10 @@
         <v>201</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D116" s="4">
         <v>4301132179</v>
@@ -9289,7 +9295,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G116" s="1">
         <f>VLOOKUP(E116,[1]Лист1!$D:$M,10,0)</f>
@@ -9301,10 +9307,10 @@
         <v>98</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D117" s="4">
         <v>4301132179</v>
@@ -9313,7 +9319,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G117" s="1">
         <f>VLOOKUP(E117,[1]Лист1!$D:$M,10,0)</f>
@@ -9325,10 +9331,10 @@
         <v>635</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D118" s="4">
         <v>4301132179</v>
@@ -9337,7 +9343,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G118" s="1">
         <f>VLOOKUP(E118,[1]Лист1!$D:$M,10,0)</f>
@@ -9349,10 +9355,10 @@
         <v>77</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D119" s="4">
         <v>4301132179</v>
@@ -9361,7 +9367,7 @@
         <v>4607111035691</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G119" s="1">
         <f>VLOOKUP(E119,[1]Лист1!$D:$M,10,0)</f>
@@ -9373,10 +9379,10 @@
         <v>99</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D120" s="4">
         <v>4301132190</v>
@@ -9385,7 +9391,7 @@
         <v>4607111036537</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G120" s="1">
         <f>VLOOKUP(E120,[1]Лист1!$D:$M,10,0)</f>
@@ -9397,10 +9403,10 @@
         <v>686</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D121" s="4">
         <v>4301132190</v>
@@ -9409,7 +9415,7 @@
         <v>4607111036537</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G121" s="1">
         <f>VLOOKUP(E121,[1]Лист1!$D:$M,10,0)</f>
@@ -9418,13 +9424,13 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D122" s="4">
         <v>4301132190</v>
@@ -9433,7 +9439,7 @@
         <v>4607111036537</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G122" s="1">
         <f>VLOOKUP(E122,[1]Лист1!$D:$M,10,0)</f>
@@ -9445,10 +9451,10 @@
         <v>78</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D123" s="4">
         <v>4301132190</v>
@@ -9457,7 +9463,7 @@
         <v>4607111036537</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G123" s="1">
         <f>VLOOKUP(E123,[1]Лист1!$D:$M,10,0)</f>
@@ -9469,10 +9475,10 @@
         <v>641</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D124" s="4">
         <v>4301132182</v>
@@ -9481,7 +9487,7 @@
         <v>4607111035721</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G124" s="1">
         <f>VLOOKUP(E124,[1]Лист1!$D:$M,10,0)</f>
@@ -9490,13 +9496,13 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D125" s="4">
         <v>4301132182</v>
@@ -9505,7 +9511,7 @@
         <v>4607111035721</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G125" s="1">
         <f>VLOOKUP(E125,[1]Лист1!$D:$M,10,0)</f>
@@ -9517,10 +9523,10 @@
         <v>79</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D126" s="4">
         <v>4301132182</v>
@@ -9529,7 +9535,7 @@
         <v>4607111035721</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G126" s="1">
         <f>VLOOKUP(E126,[1]Лист1!$D:$M,10,0)</f>
@@ -9538,13 +9544,13 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D127" s="4">
         <v>4301132182</v>
@@ -9553,11 +9559,11 @@
         <v>4607111035721</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G127" s="21"/>
       <c r="H127" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -9685,144 +9691,126 @@
         <v>332</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D133" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E133" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="G133" s="1">
-        <f>VLOOKUP(E133,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
         <v>339</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D134" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E134" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="G134" s="1">
-        <f>VLOOKUP(E134,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G134" s="1"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>413</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D135" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E135" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="G135" s="1">
-        <f>VLOOKUP(E135,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>422</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D136" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E136" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="G136" s="1">
-        <f>VLOOKUP(E136,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G136" s="1"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D137" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E137" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="G137" s="1">
-        <f>VLOOKUP(E137,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G137" s="1"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>202</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D138" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E138" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="G138" s="1">
-        <f>VLOOKUP(E138,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="G138" s="1"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
@@ -11218,10 +11206,10 @@
         <v>109</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11230,7 +11218,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11242,10 +11230,10 @@
         <v>88</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="D198" s="4">
         <v>4301071109</v>
@@ -11254,7 +11242,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11266,10 +11254,10 @@
         <v>150</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11278,7 +11266,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11287,13 +11275,13 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11302,7 +11290,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11314,10 +11302,10 @@
         <v>151</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D201" s="4">
         <v>4301071107</v>
@@ -11326,7 +11314,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="G201" s="1">
         <f>VLOOKUP(E201,[1]Лист1!$D:$M,10,0)</f>
@@ -11452,7 +11440,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="10" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>110</v>
@@ -11500,7 +11488,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>110</v>
@@ -11548,10 +11536,10 @@
         <v>111</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11560,13 +11548,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -11574,10 +11562,10 @@
         <v>90</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D212" s="4">
         <v>4301071117</v>
@@ -11586,13 +11574,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="G212" s="1">
         <v>180</v>
       </c>
       <c r="H212" s="16" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -11894,10 +11882,10 @@
         <v>184</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D225" s="4">
         <v>4301135946</v>
@@ -11906,7 +11894,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G225" s="1"/>
     </row>
@@ -11915,10 +11903,10 @@
         <v>112</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D226" s="4">
         <v>4301135946</v>
@@ -11927,19 +11915,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G226" s="1"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D227" s="4">
         <v>4301135946</v>
@@ -11948,7 +11936,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G227" s="1"/>
     </row>
@@ -11957,10 +11945,10 @@
         <v>92</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D228" s="4">
         <v>4301135946</v>
@@ -11969,7 +11957,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G228" s="1"/>
     </row>
@@ -12166,7 +12154,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>180</v>
@@ -12310,7 +12298,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="10" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>645</v>
@@ -12406,7 +12394,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="10" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>642</v>
@@ -13126,7 +13114,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="10" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>313</v>
@@ -13180,7 +13168,7 @@
         <v>319</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D279" s="4">
         <v>4301071062</v>
@@ -13189,7 +13177,7 @@
         <v>4607111036384</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G279" s="1">
         <f>VLOOKUP(E279,[1]Лист1!$D:$M,10,0)</f>
@@ -13204,7 +13192,7 @@
         <v>319</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D280" s="4">
         <v>4301071062</v>
@@ -13213,7 +13201,7 @@
         <v>4607111036384</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G280" s="1">
         <f>VLOOKUP(E280,[1]Лист1!$D:$M,10,0)</f>
@@ -13225,144 +13213,126 @@
         <v>403</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D281" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E281" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="G281" s="1">
-        <f>VLOOKUP(E281,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G281" s="1"/>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
         <v>323</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D282" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E282" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="G282" s="1">
-        <f>VLOOKUP(E282,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G282" s="1"/>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="10" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D283" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E283" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="G283" s="1">
-        <f>VLOOKUP(E283,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G283" s="1"/>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D284" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E284" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="G284" s="1">
-        <f>VLOOKUP(E284,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G284" s="1"/>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D285" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E285" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="G285" s="1">
-        <f>VLOOKUP(E285,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G285" s="1"/>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
         <v>322</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D286" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E286" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="G286" s="1">
-        <f>VLOOKUP(E286,[1]Лист1!$D:$M,10,0)</f>
-        <v>180</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G286" s="1"/>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="10" t="s">
@@ -13510,7 +13480,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="10" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>335</v>
@@ -13873,10 +13843,10 @@
         <v>420</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D308" s="4">
         <v>4301132170</v>
@@ -13885,7 +13855,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F308" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G308" s="1">
         <f>VLOOKUP(E308,[1]Лист1!$D:$M,10,0)</f>
@@ -13897,10 +13867,10 @@
         <v>448</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D309" s="4">
         <v>4301132170</v>
@@ -13909,7 +13879,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G309" s="1">
         <f>VLOOKUP(E309,[1]Лист1!$D:$M,10,0)</f>
@@ -13921,10 +13891,10 @@
         <v>451</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D310" s="4">
         <v>4301132170</v>
@@ -13933,7 +13903,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F310" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G310" s="1">
         <f>VLOOKUP(E310,[1]Лист1!$D:$M,10,0)</f>
@@ -13945,10 +13915,10 @@
         <v>419</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D311" s="4">
         <v>4301132170</v>
@@ -13957,7 +13927,7 @@
         <v>4607111038487</v>
       </c>
       <c r="F311" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G311" s="1">
         <f>VLOOKUP(E311,[1]Лист1!$D:$M,10,0)</f>
@@ -15011,10 +14981,10 @@
         <v>570</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D359" s="4">
         <v>4301135824</v>
@@ -15023,19 +14993,19 @@
         <v>4607111039095</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G359" s="1"/>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D360" s="4">
         <v>4301135824</v>
@@ -15044,7 +15014,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -15053,10 +15023,10 @@
         <v>544</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D361" s="4">
         <v>4301135824</v>
@@ -15065,7 +15035,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G361" s="1"/>
     </row>
@@ -15302,7 +15272,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>603</v>
@@ -15428,7 +15398,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>607</v>
@@ -15638,7 +15608,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>615</v>
@@ -15869,7 +15839,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>649</v>
@@ -15932,7 +15902,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>652</v>
@@ -16037,7 +16007,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>659</v>
@@ -16100,7 +16070,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>663</v>
@@ -16163,7 +16133,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>676</v>
@@ -16205,13 +16175,13 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D416" s="4">
         <v>4301135591</v>
@@ -16220,7 +16190,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16228,13 +16198,13 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D417" s="4">
         <v>4301135591</v>
@@ -16243,7 +16213,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16251,13 +16221,13 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D418" s="4">
         <v>4301135591</v>
@@ -16266,7 +16236,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="G418" s="1">
         <v>180</v>
@@ -16274,13 +16244,13 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D419" s="4">
         <v>4301135402</v>
@@ -16289,19 +16259,19 @@
         <v>4640242181493</v>
       </c>
       <c r="F419" s="5" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G419" s="1"/>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C420" s="3" t="s">
         <v>696</v>
-      </c>
-      <c r="B420" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="C420" s="3" t="s">
-        <v>698</v>
       </c>
       <c r="D420" s="4">
         <v>4301135402</v>
@@ -16310,19 +16280,19 @@
         <v>4640242181493</v>
       </c>
       <c r="F420" s="5" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G420" s="1"/>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D421" s="4">
         <v>4301135607</v>
@@ -16331,19 +16301,19 @@
         <v>4607111039613</v>
       </c>
       <c r="F421" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G421" s="1"/>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D422" s="4">
         <v>4301135607</v>
@@ -16352,19 +16322,19 @@
         <v>4607111039613</v>
       </c>
       <c r="F422" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G422" s="1"/>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D423" s="4">
         <v>4301135607</v>
@@ -16373,19 +16343,19 @@
         <v>4607111039613</v>
       </c>
       <c r="F423" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G423" s="1"/>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D424" s="4">
         <v>4301135607</v>
@@ -16394,19 +16364,19 @@
         <v>4607111039613</v>
       </c>
       <c r="F424" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G424" s="1"/>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D425" s="4">
         <v>4301190068</v>
@@ -16415,19 +16385,19 @@
         <v>4620207490365</v>
       </c>
       <c r="F425" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G425" s="1"/>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D426" s="4">
         <v>4301190068</v>
@@ -16436,19 +16406,19 @@
         <v>4620207490365</v>
       </c>
       <c r="F426" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G426" s="1"/>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C427" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="B427" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C427" s="3" t="s">
-        <v>711</v>
       </c>
       <c r="D427" s="4">
         <v>4301190068</v>
@@ -16457,19 +16427,19 @@
         <v>4620207490365</v>
       </c>
       <c r="F427" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G427" s="1"/>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D428" s="4">
         <v>4301190070</v>
@@ -16478,19 +16448,19 @@
         <v>4620207490419</v>
       </c>
       <c r="F428" s="5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G428" s="1"/>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C429" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="B429" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="C429" s="3" t="s">
-        <v>714</v>
       </c>
       <c r="D429" s="4">
         <v>4301190070</v>
@@ -16499,19 +16469,19 @@
         <v>4620207490419</v>
       </c>
       <c r="F429" s="5" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G429" s="1"/>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D430" s="4">
         <v>4301071032</v>
@@ -16520,7 +16490,7 @@
         <v>4607111038999</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G430" s="1">
         <v>180</v>
@@ -16528,13 +16498,13 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D431" s="4">
         <v>4301071032</v>
@@ -16543,7 +16513,7 @@
         <v>4607111038999</v>
       </c>
       <c r="F431" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G431" s="1">
         <v>180</v>
@@ -16551,13 +16521,13 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D432" s="4">
         <v>4301071032</v>
@@ -16566,7 +16536,7 @@
         <v>4607111038999</v>
       </c>
       <c r="F432" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G432" s="1">
         <v>180</v>
@@ -16574,13 +16544,13 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D433" s="4">
         <v>4301071032</v>
@@ -16589,7 +16559,7 @@
         <v>4607111038999</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G433" s="1">
         <v>180</v>
@@ -16597,13 +16567,13 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C434" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="B434" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="C434" s="3" t="s">
-        <v>720</v>
       </c>
       <c r="D434" s="4">
         <v>4301071032</v>
@@ -16612,7 +16582,7 @@
         <v>4607111038999</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G434" s="1">
         <v>180</v>
@@ -16620,13 +16590,13 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="C435" s="3" t="s">
         <v>735</v>
-      </c>
-      <c r="B435" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="C435" s="3" t="s">
-        <v>737</v>
       </c>
       <c r="D435" s="4">
         <v>4301135404</v>
@@ -16635,19 +16605,19 @@
         <v>4640242181516</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G435" s="1"/>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D436" s="4">
         <v>4301071090</v>
@@ -16656,7 +16626,7 @@
         <v>4620207490075</v>
       </c>
       <c r="F436" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G436" s="1">
         <v>180</v>
@@ -16664,13 +16634,13 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C437" s="3" t="s">
         <v>738</v>
-      </c>
-      <c r="B437" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="C437" s="3" t="s">
-        <v>740</v>
       </c>
       <c r="D437" s="4">
         <v>4301071090</v>
@@ -16679,7 +16649,7 @@
         <v>4620207490075</v>
       </c>
       <c r="F437" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G437" s="1">
         <v>180</v>
@@ -16687,13 +16657,13 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D438" s="4">
         <v>4301071092</v>
@@ -16702,7 +16672,7 @@
         <v>4620207490174</v>
       </c>
       <c r="F438" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G438" s="1">
         <v>180</v>
@@ -16710,13 +16680,13 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D439" s="4">
         <v>4301071092</v>
@@ -16725,7 +16695,7 @@
         <v>4620207490174</v>
       </c>
       <c r="F439" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G439" s="1">
         <v>180</v>
@@ -16733,13 +16703,13 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="C440" s="3" t="s">
         <v>741</v>
-      </c>
-      <c r="B440" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="C440" s="3" t="s">
-        <v>743</v>
       </c>
       <c r="D440" s="4">
         <v>4301071092</v>
@@ -16748,7 +16718,7 @@
         <v>4620207490174</v>
       </c>
       <c r="F440" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G440" s="1">
         <v>180</v>
@@ -16756,13 +16726,13 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D441" s="4">
         <v>4301071091</v>
@@ -16771,7 +16741,7 @@
         <v>4620207490044</v>
       </c>
       <c r="F441" s="5" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G441" s="1">
         <v>180</v>
@@ -16779,13 +16749,13 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="C442" s="3" t="s">
         <v>744</v>
-      </c>
-      <c r="B442" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>746</v>
       </c>
       <c r="D442" s="4">
         <v>4301071091</v>
@@ -16794,7 +16764,7 @@
         <v>4620207490044</v>
       </c>
       <c r="F442" s="5" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G442" s="1">
         <v>180</v>
@@ -16802,13 +16772,13 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="C443" s="3" t="s">
         <v>755</v>
-      </c>
-      <c r="B443" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="C443" s="3" t="s">
-        <v>757</v>
       </c>
       <c r="D443" s="4">
         <v>4301132044</v>
@@ -16817,19 +16787,19 @@
         <v>4607111036971</v>
       </c>
       <c r="F443" s="5" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G443" s="1"/>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C444" s="3" t="s">
         <v>776</v>
-      </c>
-      <c r="B444" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>778</v>
       </c>
       <c r="D444" s="4">
         <v>4301135127</v>
@@ -16838,19 +16808,19 @@
         <v>4607111036995</v>
       </c>
       <c r="F444" s="5" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G444" s="1"/>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="10" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16859,7 +16829,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F445" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G445" s="1">
         <v>180</v>
@@ -16867,13 +16837,13 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="10" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16882,7 +16852,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F446" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G446" s="1">
         <v>180</v>
@@ -16890,13 +16860,13 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="10" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16905,7 +16875,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F447" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G447" s="1">
         <v>180</v>
@@ -16913,13 +16883,13 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="10" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="D448" s="4">
         <v>4301135826</v>
@@ -16928,7 +16898,7 @@
         <v>4620207490983</v>
       </c>
       <c r="F448" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G448" s="1">
         <v>180</v>
@@ -16936,13 +16906,13 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="10" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D449" s="4">
         <v>4301071074</v>
@@ -16951,19 +16921,19 @@
         <v>4620207491157</v>
       </c>
       <c r="F449" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G449" s="1"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="10" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D450" s="4">
         <v>4301071074</v>
@@ -16972,19 +16942,19 @@
         <v>4620207491157</v>
       </c>
       <c r="F450" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G450" s="1"/>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="C451" s="3" t="s">
         <v>865</v>
-      </c>
-      <c r="B451" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="C451" s="3" t="s">
-        <v>867</v>
       </c>
       <c r="D451" s="4">
         <v>4301071074</v>
@@ -16993,19 +16963,19 @@
         <v>4620207491157</v>
       </c>
       <c r="F451" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G451" s="1"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="10" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D452" s="4">
         <v>4301135763</v>
@@ -17014,19 +16984,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F452" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G452" s="1"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="10" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D453" s="4">
         <v>4301135763</v>
@@ -17035,19 +17005,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G453" s="1"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="10" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D454" s="4">
         <v>4301135763</v>
@@ -17056,19 +17026,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G454" s="1"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="10" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D455" s="4">
         <v>4301135763</v>
@@ -17077,19 +17047,19 @@
         <v>4620207491027</v>
       </c>
       <c r="F455" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G455" s="1"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="10" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D456" s="4">
         <v>4301135665</v>
@@ -17098,19 +17068,19 @@
         <v>4607111039729</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G456" s="1"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="10" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D457" s="4">
         <v>4301135702</v>
@@ -17119,19 +17089,19 @@
         <v>4620207490228</v>
       </c>
       <c r="F457" s="5" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="G457" s="1"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="10" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D458" s="4">
         <v>4301071090</v>
@@ -17140,22 +17110,22 @@
         <v>4620207490075</v>
       </c>
       <c r="F458" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G458" s="1"/>
       <c r="H458" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="10" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D459" s="4">
         <v>4301071091</v>
@@ -17164,22 +17134,22 @@
         <v>4620207490044</v>
       </c>
       <c r="F459" s="5" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G459" s="1"/>
       <c r="H459" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="10" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D460" s="4">
         <v>4301071032</v>
@@ -17188,16 +17158,16 @@
         <v>4607111038999</v>
       </c>
       <c r="F460" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G460" s="1"/>
       <c r="H460" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="10" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>659</v>
@@ -17216,12 +17186,12 @@
       </c>
       <c r="G461" s="1"/>
       <c r="H461" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="10" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>611</v>
@@ -17240,12 +17210,12 @@
       </c>
       <c r="G462" s="1"/>
       <c r="H462" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="10" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>607</v>
@@ -17264,12 +17234,12 @@
       </c>
       <c r="G463" s="1"/>
       <c r="H463" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="10" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>615</v>
@@ -17284,16 +17254,16 @@
         <v>4607111039293</v>
       </c>
       <c r="F464" s="5" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G464" s="1"/>
       <c r="H464" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="10" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>619</v>
@@ -17312,7 +17282,7 @@
       </c>
       <c r="G465" s="1"/>
       <c r="H465" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
@@ -17320,10 +17290,10 @@
         <v>636</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D466" s="4">
         <v>4301135760</v>
@@ -17332,22 +17302,22 @@
         <v>4620207491010</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D467" s="4">
         <v>4301132190</v>
@@ -17356,43 +17326,43 @@
         <v>4607111036537</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G467" s="1"/>
       <c r="H467" s="16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D468" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E468" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G468" s="1"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="D469" s="4">
         <v>4301071097</v>
@@ -17401,19 +17371,19 @@
         <v>4620207491096</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="G469" s="1"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="D470" s="4">
         <v>4301071097</v>
@@ -17422,19 +17392,19 @@
         <v>4620207491096</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="G470" s="1"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C471" s="3" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="D471" s="4">
         <v>4301132227</v>
@@ -17443,19 +17413,19 @@
         <v>4620207491133</v>
       </c>
       <c r="F471" s="5" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="G471" s="1"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="D472" s="4">
         <v>4301132227</v>
@@ -17464,19 +17434,19 @@
         <v>4620207491133</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="G472" s="1"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D473" s="4">
         <v>4301135753</v>
@@ -17485,19 +17455,19 @@
         <v>4620207490914</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G473" s="1"/>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D474" s="4">
         <v>4301070962</v>
@@ -17506,19 +17476,19 @@
         <v>4607111038609</v>
       </c>
       <c r="F474" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G474" s="1"/>
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D475" s="4">
         <v>4301070959</v>
@@ -17527,19 +17497,19 @@
         <v>4607111038616</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G475" s="1"/>
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17548,19 +17518,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="G476" s="1"/>
     </row>
     <row r="477" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D477" s="4">
         <v>4301071075</v>
@@ -17569,19 +17539,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="G477" s="1"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D478" s="4">
         <v>4301135574</v>
@@ -17590,19 +17560,19 @@
         <v>4607111033659</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G478" s="1"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D479" s="4">
         <v>4301135946</v>
@@ -17611,19 +17581,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D480" s="4">
         <v>4301135753</v>
@@ -17632,19 +17602,19 @@
         <v>4620207490914</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G480" s="1"/>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="10" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C481" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D481" s="4">
         <v>4301131046</v>
@@ -17653,19 +17623,19 @@
         <v>4607111034137</v>
       </c>
       <c r="F481" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G481" s="1"/>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C482" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D482" s="4">
         <v>4301131047</v>
@@ -17674,19 +17644,19 @@
         <v>4607111034120</v>
       </c>
       <c r="F482" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G482" s="1"/>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="10" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C483" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D483" s="4">
         <v>4301132188</v>
@@ -17695,19 +17665,19 @@
         <v>4607111036605</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G483" s="1"/>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="10" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B484" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C484" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D484" s="4">
         <v>4301132179</v>
@@ -17716,34 +17686,34 @@
         <v>4607111035691</v>
       </c>
       <c r="F484" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G484" s="1"/>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="10" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D485" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E485" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>692</v>
+        <v>1062</v>
       </c>
       <c r="G485" s="1"/>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" s="10" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>615</v>
@@ -17758,7 +17728,7 @@
         <v>4607111039293</v>
       </c>
       <c r="F486" s="5" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G486" s="1"/>
     </row>
@@ -17806,13 +17776,13 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="D489" s="4">
         <v>4301071094</v>
@@ -17821,19 +17791,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="D490" s="4">
         <v>4301071093</v>
@@ -17842,19 +17812,19 @@
         <v>4620207490709</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="G490" s="1"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D491" s="4">
         <v>4301132190</v>
@@ -17863,19 +17833,19 @@
         <v>4607111036537</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G491" s="1"/>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D492" s="4">
         <v>4301132188</v>
@@ -17884,19 +17854,19 @@
         <v>4607111036605</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G492" s="1"/>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D493" s="4">
         <v>4301071090</v>
@@ -17905,19 +17875,19 @@
         <v>4620207490075</v>
       </c>
       <c r="F493" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G493" s="1"/>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D494" s="4">
         <v>4301071091</v>
@@ -17926,13 +17896,13 @@
         <v>4620207490044</v>
       </c>
       <c r="F494" s="5" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G494" s="1"/>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>659</v>
@@ -17953,13 +17923,13 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D496" s="4">
         <v>4301135574</v>
@@ -17968,19 +17938,19 @@
         <v>4607111033659</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G496" s="1"/>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D497" s="4">
         <v>4301131047</v>
@@ -17989,19 +17959,19 @@
         <v>4607111034120</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G497" s="1"/>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="B498" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D498" s="4">
         <v>4301131046</v>
@@ -18010,19 +17980,19 @@
         <v>4607111034137</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G498" s="1"/>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D499" s="4">
         <v>4301135914</v>
@@ -18031,19 +18001,19 @@
         <v>4620207491621</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G499" s="1"/>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D500" s="4">
         <v>4301135760</v>
@@ -18052,13 +18022,13 @@
         <v>4620207491010</v>
       </c>
       <c r="F500" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G500" s="1"/>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>180</v>
@@ -18079,7 +18049,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>164</v>
@@ -18100,7 +18070,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>607</v>
@@ -18121,7 +18091,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>611</v>
@@ -18142,7 +18112,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>615</v>
@@ -18157,13 +18127,13 @@
         <v>4607111039293</v>
       </c>
       <c r="F505" s="5" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G505" s="1"/>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>619</v>
@@ -18184,7 +18154,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>645</v>
@@ -18205,7 +18175,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>642</v>
@@ -18226,13 +18196,13 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D509" s="4">
         <v>4301135946</v>
@@ -18241,19 +18211,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D510" s="4">
         <v>4301135753</v>
@@ -18262,40 +18232,40 @@
         <v>4620207490914</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G510" s="1"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>690</v>
+        <v>1060</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>691</v>
+        <v>1061</v>
       </c>
       <c r="D511" s="4">
-        <v>4301135570</v>
+        <v>4301135940</v>
       </c>
       <c r="E511" s="3">
-        <v>4607111035806</v>
+        <v>4620207491614</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>692</v>
+        <v>1062</v>
       </c>
       <c r="G511" s="1"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C512" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D512" s="4">
         <v>4301132179</v>
@@ -18304,19 +18274,19 @@
         <v>4607111035691</v>
       </c>
       <c r="F512" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G512" s="1"/>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="D513" s="4">
         <v>4301071063</v>
@@ -18325,13 +18295,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="G513" s="1"/>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>491</v>
@@ -18352,13 +18322,13 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18367,19 +18337,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18388,19 +18358,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="D517" s="4">
         <v>4301135834</v>
@@ -18409,19 +18379,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="C518" s="3" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="D518" s="4">
         <v>4301135873</v>
@@ -18430,19 +18400,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="C519" s="3" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="D519" s="4">
         <v>4301135850</v>
@@ -18451,19 +18421,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C520" s="3" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="D520" s="4">
         <v>4301190117</v>
@@ -18472,19 +18442,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C521" s="3" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="D521" s="4">
         <v>4301190115</v>
@@ -18493,19 +18463,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C522" s="3" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="D522" s="4">
         <v>4301135865</v>
@@ -18514,19 +18484,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="C523" s="3" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="D523" s="4">
         <v>4301190116</v>
@@ -18535,19 +18505,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18556,19 +18526,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G524" s="1"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="C525" s="3" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="D525" s="4">
         <v>4301071112</v>
@@ -18577,13 +18547,13 @@
         <v>4620207491256</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G525" s="1"/>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="17" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B526" s="18" t="s">
         <v>611</v>
@@ -18602,12 +18572,12 @@
       </c>
       <c r="G526" s="21"/>
       <c r="H526" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="17" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B527" s="18" t="s">
         <v>106</v>
@@ -18626,12 +18596,12 @@
       </c>
       <c r="G527" s="21"/>
       <c r="H527" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="17" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B528" s="18" t="s">
         <v>619</v>
@@ -18650,12 +18620,12 @@
       </c>
       <c r="G528" s="21"/>
       <c r="H528" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="17" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B529" s="18" t="s">
         <v>607</v>
@@ -18674,12 +18644,12 @@
       </c>
       <c r="G529" s="21"/>
       <c r="H529" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="17" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B530" s="18" t="s">
         <v>288</v>
@@ -18698,18 +18668,18 @@
       </c>
       <c r="G530" s="21"/>
       <c r="H530" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="17" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D531" s="4">
         <v>4301071117</v>
@@ -18718,18 +18688,18 @@
         <v>4620207491737</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="G531" s="1">
         <v>180</v>
       </c>
       <c r="H531" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="17" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B532" s="3" t="s">
         <v>297</v>
@@ -18748,12 +18718,12 @@
       </c>
       <c r="G532" s="21"/>
       <c r="H532" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="17" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B533" s="18" t="s">
         <v>313</v>
@@ -18772,12 +18742,12 @@
       </c>
       <c r="G533" s="21"/>
       <c r="H533" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="17" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B534" s="18" t="s">
         <v>545</v>
@@ -18796,18 +18766,18 @@
       </c>
       <c r="G534" s="21"/>
       <c r="H534" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="17" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="D535" s="4">
         <v>4301135760</v>
@@ -18816,16 +18786,16 @@
         <v>4620207491010</v>
       </c>
       <c r="F535" s="5" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="17" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B536" s="3" t="s">
         <v>110</v>
@@ -18844,12 +18814,12 @@
       </c>
       <c r="G536" s="21"/>
       <c r="H536" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="17" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B537" s="18" t="s">
         <v>615</v>
@@ -18868,12 +18838,12 @@
       </c>
       <c r="G537" s="21"/>
       <c r="H537" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="17" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B538" s="18" t="s">
         <v>642</v>
@@ -18892,12 +18862,12 @@
       </c>
       <c r="G538" s="21"/>
       <c r="H538" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="17" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B539" s="3" t="s">
         <v>645</v>
@@ -18916,18 +18886,18 @@
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="17" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D540" s="4">
         <v>4301135914</v>
@@ -18936,16 +18906,16 @@
         <v>4620207491621</v>
       </c>
       <c r="F540" s="5" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="G540" s="21"/>
       <c r="H540" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="17" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>377</v>
@@ -18964,18 +18934,18 @@
       </c>
       <c r="G541" s="21"/>
       <c r="H541" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="17" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D542" s="4">
         <v>4301137046</v>
@@ -18984,18 +18954,18 @@
         <v>4620207492093</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="G542" s="1">
         <v>180</v>
       </c>
       <c r="H542" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="17" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B543" s="18" t="s">
         <v>590</v>
@@ -19014,18 +18984,18 @@
       </c>
       <c r="G543" s="21"/>
       <c r="H543" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="17" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B544" s="18" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C544" s="18" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D544" s="19">
         <v>4301132079</v>
@@ -19038,12 +19008,12 @@
       </c>
       <c r="G544" s="21"/>
       <c r="H544" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="17" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B545" s="18" t="s">
         <v>159</v>
@@ -19062,12 +19032,12 @@
       </c>
       <c r="G545" s="21"/>
       <c r="H545" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="17" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>294</v>
@@ -19086,18 +19056,18 @@
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="17" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="D547" s="4">
         <v>4301071109</v>
@@ -19106,22 +19076,22 @@
         <v>4607111035929</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="17" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D548" s="4">
         <v>4301135946</v>
@@ -19130,22 +19100,22 @@
         <v>4620207491553</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="17" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B549" s="18" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C549" s="18" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D549" s="19">
         <v>4301132186</v>
@@ -19154,16 +19124,16 @@
         <v>4607111036520</v>
       </c>
       <c r="F549" s="20" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G549" s="21"/>
       <c r="H549" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="17" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B550" s="18" t="s">
         <v>603</v>
@@ -19182,18 +19152,18 @@
       </c>
       <c r="G550" s="21"/>
       <c r="H550" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="17" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C551" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D551" s="4">
         <v>4301131047</v>
@@ -19202,22 +19172,22 @@
         <v>4607111034120</v>
       </c>
       <c r="F551" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G551" s="21"/>
       <c r="H551" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="17" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B552" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C552" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D552" s="4">
         <v>4301135763</v>
@@ -19226,16 +19196,16 @@
         <v>4620207491027</v>
       </c>
       <c r="F552" s="5" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="17" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B553" s="18" t="s">
         <v>549</v>
@@ -19254,18 +19224,18 @@
       </c>
       <c r="G553" s="21"/>
       <c r="H553" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="17" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B554" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C554" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D554" s="19">
         <v>4301135402</v>
@@ -19274,22 +19244,22 @@
         <v>4640242181493</v>
       </c>
       <c r="F554" s="20" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G554" s="21"/>
       <c r="H554" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="17" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C555" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D555" s="4">
         <v>4301131046</v>
@@ -19298,22 +19268,22 @@
         <v>4607111034137</v>
       </c>
       <c r="F555" s="5" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G555" s="21"/>
       <c r="H555" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="17" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B556" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C556" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D556" s="4">
         <v>4301136079</v>
@@ -19322,22 +19292,22 @@
         <v>4607025784319</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G556" s="21"/>
       <c r="H556" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="17" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D557" s="4">
         <v>4301135753</v>
@@ -19346,22 +19316,22 @@
         <v>4620207490914</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="17" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D558" s="4">
         <v>4301135778</v>
@@ -19370,22 +19340,22 @@
         <v>4620207490853</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="16" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="17" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C559" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D559" s="4">
         <v>4301132179</v>
@@ -19394,22 +19364,22 @@
         <v>4607111035691</v>
       </c>
       <c r="F559" s="5" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G559" s="21"/>
       <c r="H559" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" s="17" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C560" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D560" s="4">
         <v>4301132190</v>
@@ -19418,16 +19388,16 @@
         <v>4607111036537</v>
       </c>
       <c r="F560" s="5" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G560" s="21"/>
       <c r="H560" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="17" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B561" s="18" t="s">
         <v>370</v>
@@ -19446,60 +19416,60 @@
       </c>
       <c r="G561" s="21"/>
       <c r="H561" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" s="17" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
       <c r="D562" s="4">
-        <v>4301135571</v>
+        <v>4301135984</v>
       </c>
       <c r="E562" s="3">
-        <v>4607111035028</v>
+        <v>4620207491874</v>
       </c>
       <c r="F562" s="5" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="G562" s="21"/>
       <c r="H562" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" s="17" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>912</v>
+        <v>1055</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>913</v>
+        <v>1056</v>
       </c>
       <c r="D563" s="4">
-        <v>4301135768</v>
+        <v>4301135990</v>
       </c>
       <c r="E563" s="3">
-        <v>4620207491034</v>
+        <v>4620207491881</v>
       </c>
       <c r="F563" s="5" t="s">
-        <v>911</v>
+        <v>1057</v>
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
     </row>
     <row r="564" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A564" s="17" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B564" s="18" t="s">
         <v>482</v>
@@ -19518,12 +19488,12 @@
       </c>
       <c r="G564" s="21"/>
       <c r="H564" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="17" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B565" s="18" t="s">
         <v>363</v>
@@ -19542,18 +19512,18 @@
       </c>
       <c r="G565" s="21"/>
       <c r="H565" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="10" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C566" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D566" s="4">
         <v>4301070990</v>
@@ -19562,22 +19532,22 @@
         <v>4607111038494</v>
       </c>
       <c r="F566" s="5" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G566" s="1"/>
       <c r="H566" s="16" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="17" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B567" s="18" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C567" s="18" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D567" s="19">
         <v>4301070990</v>
@@ -19586,22 +19556,22 @@
         <v>4607111038494</v>
       </c>
       <c r="F567" s="20" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G567" s="21"/>
       <c r="H567" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="17" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D568" s="4">
         <v>4301071107</v>
@@ -19610,22 +19580,22 @@
         <v>4607111035905</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" s="17" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D569" s="4">
         <v>4301135824</v>
@@ -19634,16 +19604,16 @@
         <v>4607111039095</v>
       </c>
       <c r="F569" s="5" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" s="17" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B570" s="18" t="s">
         <v>180</v>
@@ -19662,18 +19632,18 @@
       </c>
       <c r="G570" s="21"/>
       <c r="H570" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="17" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C571" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D571" s="4">
         <v>4301135607</v>
@@ -19682,16 +19652,16 @@
         <v>4607111039613</v>
       </c>
       <c r="F571" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G571" s="21"/>
       <c r="H571" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="17" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B572" s="18" t="s">
         <v>124</v>
@@ -19710,18 +19680,18 @@
       </c>
       <c r="G572" s="21"/>
       <c r="H572" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="17" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D573" s="4">
         <v>4301135574</v>
@@ -19730,16 +19700,16 @@
         <v>4607111033659</v>
       </c>
       <c r="F573" s="5" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G573" s="21"/>
       <c r="H573" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="17" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B574" s="18" t="s">
         <v>659</v>
@@ -19758,12 +19728,12 @@
       </c>
       <c r="G574" s="21"/>
       <c r="H574" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="17" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B575" s="18" t="s">
         <v>676</v>
@@ -19782,12 +19752,12 @@
       </c>
       <c r="G575" s="21"/>
       <c r="H575" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" s="17" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B576" s="18" t="s">
         <v>176</v>
@@ -19806,12 +19776,12 @@
       </c>
       <c r="G576" s="21"/>
       <c r="H576" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" s="17" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>164</v>
@@ -19830,12 +19800,12 @@
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" s="17" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B578" s="18" t="s">
         <v>599</v>
@@ -19854,18 +19824,18 @@
       </c>
       <c r="G578" s="21"/>
       <c r="H578" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="579" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A579" s="17" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B579" s="18" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C579" s="18" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D579" s="19">
         <v>4301070959</v>
@@ -19874,22 +19844,22 @@
         <v>4607111038616</v>
       </c>
       <c r="F579" s="20" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G579" s="21"/>
       <c r="H579" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="580" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A580" s="17" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B580" s="18" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C580" s="18" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D580" s="19">
         <v>4301070962</v>
@@ -19898,16 +19868,16 @@
         <v>4607111038609</v>
       </c>
       <c r="F580" s="20" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G580" s="21"/>
       <c r="H580" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="17" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B581" s="18" t="s">
         <v>249</v>
@@ -19926,42 +19896,42 @@
       </c>
       <c r="G581" s="21"/>
       <c r="H581" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" s="17" t="s">
-        <v>836</v>
-      </c>
-      <c r="B582" s="18" t="s">
-        <v>690</v>
-      </c>
-      <c r="C582" s="18" t="s">
-        <v>691</v>
-      </c>
-      <c r="D582" s="19">
-        <v>4301135570</v>
-      </c>
-      <c r="E582" s="18">
-        <v>4607111035806</v>
-      </c>
-      <c r="F582" s="20" t="s">
-        <v>692</v>
+        <v>834</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D582" s="4">
+        <v>4301135940</v>
+      </c>
+      <c r="E582" s="3">
+        <v>4620207491614</v>
+      </c>
+      <c r="F582" s="5" t="s">
+        <v>1062</v>
       </c>
       <c r="G582" s="21"/>
       <c r="H582" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" s="17" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B583" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C583" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D583" s="19">
         <v>4301071032</v>
@@ -19970,16 +19940,16 @@
         <v>4607111038999</v>
       </c>
       <c r="F583" s="20" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G583" s="21"/>
       <c r="H583" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" s="17" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B584" s="18" t="s">
         <v>663</v>
@@ -19998,12 +19968,12 @@
       </c>
       <c r="G584" s="21"/>
       <c r="H584" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" s="17" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B585" s="18" t="s">
         <v>478</v>
@@ -20022,12 +19992,12 @@
       </c>
       <c r="G585" s="21"/>
       <c r="H585" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" s="17" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B586" s="18" t="s">
         <v>581</v>
@@ -20046,12 +20016,12 @@
       </c>
       <c r="G586" s="21"/>
       <c r="H586" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" s="17" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B587" s="18" t="s">
         <v>335</v>
@@ -20070,18 +20040,18 @@
       </c>
       <c r="G587" s="21"/>
       <c r="H587" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="D588" s="4">
         <v>4301135848</v>
@@ -20090,19 +20060,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F588" s="5" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="G588" s="1"/>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="D589" s="4">
         <v>4301135848</v>
@@ -20111,19 +20081,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F589" s="5" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="G589" s="1"/>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="D590" s="4">
         <v>4301190118</v>
@@ -20132,19 +20102,19 @@
         <v>4620207491461</v>
       </c>
       <c r="F590" s="5" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="G590" s="1"/>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C591" s="3" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="D591" s="4">
         <v>4301190118</v>
@@ -20153,7 +20123,7 @@
         <v>4620207491461</v>
       </c>
       <c r="F591" s="5" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="G591" s="1"/>
     </row>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A766BD-F410-4255-B6DC-E3598635FC09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3252E7EB-9314-48F7-9607-98AB91410271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,16 +23,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$591</definedName>
     <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$526</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3463,7 +3457,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Лист1"/>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1EBF99-0B3E-4A9A-A541-55EA502D705A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECCDF97-3FC6-4FED-9C50-4B3819C5A31C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2795,12 +2795,6 @@
     <t>Снеки «Круггетсы сочные» Фикс.вес 0,2 ТМ «Горячая штучка»</t>
   </si>
   <si>
-    <t>SU003884</t>
-  </si>
-  <si>
-    <t>P004966</t>
-  </si>
-  <si>
     <t>Снеки «Готовые чебупели сочные с мясом» Фикс.вес 0,24 ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -3231,6 +3225,12 @@
   </si>
   <si>
     <t>Пельмени «Домашние со сливочным маслом» 0,7 сфера ТМ «Зареченские продукты»</t>
+  </si>
+  <si>
+    <t>SU004210</t>
+  </si>
+  <si>
+    <t>P005476</t>
   </si>
 </sst>
 </file>
@@ -6742,10 +6742,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D11" s="4">
         <v>4301135914</v>
@@ -6769,10 +6769,10 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D12" s="4">
         <v>4301135914</v>
@@ -6796,10 +6796,10 @@
         <v>185</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D13" s="4">
         <v>4301135914</v>
@@ -6823,10 +6823,10 @@
         <v>913</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D14" s="4">
         <v>4301135914</v>
@@ -6841,13 +6841,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D15" s="4">
         <v>4301135914</v>
@@ -6865,10 +6865,10 @@
         <v>215</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D16" s="4">
         <v>4301135990</v>
@@ -6877,7 +6877,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G16" s="1" t="e">
         <f>VLOOKUP(E16,[1]Лист1!$D:$M,10,0)</f>
@@ -6892,10 +6892,10 @@
         <v>411</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D17" s="4">
         <v>4301135990</v>
@@ -6904,7 +6904,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G17" s="1" t="e">
         <f>VLOOKUP(E17,[1]Лист1!$D:$M,10,0)</f>
@@ -6919,10 +6919,10 @@
         <v>417</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D18" s="4">
         <v>4301135990</v>
@@ -6931,7 +6931,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G18" s="1" t="e">
         <f>VLOOKUP(E18,[1]Лист1!$D:$M,10,0)</f>
@@ -6946,10 +6946,10 @@
         <v>186</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D19" s="4">
         <v>4301135990</v>
@@ -6958,7 +6958,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G19" s="1" t="e">
         <f>VLOOKUP(E19,[1]Лист1!$D:$M,10,0)</f>
@@ -6970,13 +6970,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D20" s="4">
         <v>4301135990</v>
@@ -6985,19 +6985,19 @@
         <v>4620207491881</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D21" s="4">
         <v>4301135990</v>
@@ -7006,7 +7006,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -7015,19 +7015,19 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D22" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D22" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E22" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G22" s="1" t="e">
         <f>VLOOKUP(E22,[1]Лист1!$D:$M,10,0)</f>
@@ -7042,19 +7042,19 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D23" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D23" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E23" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G23" s="1" t="e">
         <f>VLOOKUP(E23,[1]Лист1!$D:$M,10,0)</f>
@@ -7069,19 +7069,19 @@
         <v>187</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D24" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D24" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E24" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G24" s="1" t="e">
         <f>VLOOKUP(E24,[1]Лист1!$D:$M,10,0)</f>
@@ -7093,43 +7093,43 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D25" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D25" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E25" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D26" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D26" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E26" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -7342,10 +7342,10 @@
         <v>188</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D35" s="4">
         <v>4301136101</v>
@@ -7354,7 +7354,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -7363,10 +7363,10 @@
         <v>164</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D36" s="4">
         <v>4301136101</v>
@@ -7375,7 +7375,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -7384,10 +7384,10 @@
         <v>165</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D37" s="4">
         <v>4301136101</v>
@@ -7396,7 +7396,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G37" s="1"/>
     </row>
@@ -8414,10 +8414,10 @@
         <v>192</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D80" s="4">
         <v>4301135753</v>
@@ -8426,14 +8426,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G80" s="1" t="e">
         <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8441,10 +8441,10 @@
         <v>681</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D81" s="4">
         <v>4301135753</v>
@@ -8453,14 +8453,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G81" s="1" t="e">
         <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8468,10 +8468,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D82" s="4">
         <v>4301135753</v>
@@ -8480,14 +8480,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G82" s="1" t="e">
         <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8514,7 +8514,7 @@
         <v>#N/A</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8541,7 +8541,7 @@
         <v>#N/A</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8568,7 +8568,7 @@
         <v>#N/A</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8595,12 +8595,12 @@
         <v>#N/A</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>915</v>
@@ -8642,7 +8642,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>915</v>
@@ -8810,10 +8810,10 @@
         <v>196</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D96" s="4">
         <v>4301137046</v>
@@ -8822,7 +8822,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G96" s="1">
         <v>180</v>
@@ -8833,10 +8833,10 @@
         <v>225</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D97" s="4">
         <v>4301137046</v>
@@ -8845,7 +8845,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G97" s="1">
         <v>180</v>
@@ -8856,10 +8856,10 @@
         <v>339</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D98" s="4">
         <v>4301137046</v>
@@ -8868,7 +8868,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G98" s="1">
         <v>180</v>
@@ -8879,10 +8879,10 @@
         <v>367</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D99" s="4">
         <v>4301137046</v>
@@ -8891,7 +8891,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G99" s="1">
         <v>180</v>
@@ -8902,10 +8902,10 @@
         <v>76</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D100" s="4">
         <v>4301137046</v>
@@ -8914,7 +8914,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G100" s="1">
         <v>180</v>
@@ -8925,10 +8925,10 @@
         <v>539</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D101" s="4">
         <v>4301137046</v>
@@ -8937,7 +8937,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G101" s="1">
         <v>180</v>
@@ -8948,10 +8948,10 @@
         <v>575</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D102" s="4">
         <v>4301137046</v>
@@ -8960,7 +8960,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G102" s="1">
         <v>180</v>
@@ -8968,13 +8968,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D103" s="4">
         <v>4301137046</v>
@@ -8983,7 +8983,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G103" s="1">
         <v>180</v>
@@ -8994,10 +8994,10 @@
         <v>574</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D104" s="4">
         <v>4301137046</v>
@@ -9006,7 +9006,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G104" s="1">
         <v>180</v>
@@ -9178,7 +9178,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>742</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>721</v>
@@ -9685,10 +9685,10 @@
         <v>331</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D133" s="4">
         <v>4301135940</v>
@@ -9697,7 +9697,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G133" s="1"/>
     </row>
@@ -9706,10 +9706,10 @@
         <v>338</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D134" s="4">
         <v>4301135940</v>
@@ -9718,7 +9718,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G134" s="1"/>
     </row>
@@ -9727,10 +9727,10 @@
         <v>412</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D135" s="4">
         <v>4301135940</v>
@@ -9739,7 +9739,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G135" s="1"/>
     </row>
@@ -9748,10 +9748,10 @@
         <v>421</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D136" s="4">
         <v>4301135940</v>
@@ -9760,7 +9760,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G136" s="1"/>
     </row>
@@ -9769,10 +9769,10 @@
         <v>687</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D137" s="4">
         <v>4301135940</v>
@@ -9781,7 +9781,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G137" s="1"/>
     </row>
@@ -9790,10 +9790,10 @@
         <v>201</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D138" s="4">
         <v>4301135940</v>
@@ -9802,7 +9802,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G138" s="1"/>
     </row>
@@ -11200,10 +11200,10 @@
         <v>109</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11212,7 +11212,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11224,10 +11224,10 @@
         <v>88</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D198" s="4">
         <v>4301071109</v>
@@ -11236,7 +11236,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11248,10 +11248,10 @@
         <v>150</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11260,7 +11260,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11272,10 +11272,10 @@
         <v>755</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11284,7 +11284,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11296,10 +11296,10 @@
         <v>151</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D201" s="4">
         <v>4301071107</v>
@@ -11308,7 +11308,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G201" s="1">
         <f>VLOOKUP(E201,[1]Лист1!$D:$M,10,0)</f>
@@ -11482,7 +11482,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>110</v>
@@ -11530,10 +11530,10 @@
         <v>111</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11542,13 +11542,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -11556,10 +11556,10 @@
         <v>90</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D212" s="4">
         <v>4301071117</v>
@@ -11568,13 +11568,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G212" s="1">
         <v>180</v>
       </c>
       <c r="H212" s="16" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -11876,10 +11876,10 @@
         <v>183</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D225" s="4">
         <v>4301135946</v>
@@ -11888,7 +11888,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G225" s="1"/>
     </row>
@@ -11897,10 +11897,10 @@
         <v>112</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D226" s="4">
         <v>4301135946</v>
@@ -11909,7 +11909,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G226" s="1"/>
     </row>
@@ -11918,10 +11918,10 @@
         <v>758</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D227" s="4">
         <v>4301135946</v>
@@ -11930,7 +11930,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G227" s="1"/>
     </row>
@@ -11939,10 +11939,10 @@
         <v>92</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D228" s="4">
         <v>4301135946</v>
@@ -11951,7 +11951,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G228" s="1"/>
     </row>
@@ -13207,10 +13207,10 @@
         <v>402</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D281" s="4">
         <v>4301135984</v>
@@ -13228,10 +13228,10 @@
         <v>322</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D282" s="4">
         <v>4301135984</v>
@@ -13249,10 +13249,10 @@
         <v>871</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D283" s="4">
         <v>4301135984</v>
@@ -13267,13 +13267,13 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D284" s="4">
         <v>4301135984</v>
@@ -13288,13 +13288,13 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D285" s="4">
         <v>4301135984</v>
@@ -13312,10 +13312,10 @@
         <v>321</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D286" s="4">
         <v>4301135984</v>
@@ -14555,7 +14555,7 @@
         <v>510</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D339" s="4">
         <v>4301071141</v>
@@ -14564,7 +14564,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G339" s="1"/>
     </row>
@@ -14576,7 +14576,7 @@
         <v>510</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D340" s="4">
         <v>4301071141</v>
@@ -14585,7 +14585,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F340" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G340" s="1"/>
     </row>
@@ -14597,7 +14597,7 @@
         <v>510</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D341" s="4">
         <v>4301071141</v>
@@ -14606,7 +14606,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G341" s="1"/>
     </row>
@@ -14618,7 +14618,7 @@
         <v>510</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D342" s="4">
         <v>4301071141</v>
@@ -14627,7 +14627,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F342" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G342" s="1"/>
     </row>
@@ -14975,10 +14975,10 @@
         <v>566</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="D359" s="4">
         <v>4301135824</v>
@@ -14987,7 +14987,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G359" s="1"/>
     </row>
@@ -14996,10 +14996,10 @@
         <v>748</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="D360" s="4">
         <v>4301135824</v>
@@ -15008,7 +15008,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -15017,10 +15017,10 @@
         <v>540</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="D361" s="4">
         <v>4301135824</v>
@@ -15029,7 +15029,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G361" s="1"/>
     </row>
@@ -16172,10 +16172,10 @@
         <v>757</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D416" s="4">
         <v>4301135591</v>
@@ -16184,7 +16184,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16195,10 +16195,10 @@
         <v>851</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D417" s="4">
         <v>4301135591</v>
@@ -16207,7 +16207,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16218,10 +16218,10 @@
         <v>688</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D418" s="4">
         <v>4301135591</v>
@@ -16230,7 +16230,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G418" s="1">
         <v>180</v>
@@ -16811,10 +16811,10 @@
         <v>867</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16834,10 +16834,10 @@
         <v>873</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16857,10 +16857,10 @@
         <v>874</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16880,10 +16880,10 @@
         <v>858</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D448" s="4">
         <v>4301135826</v>
@@ -17284,19 +17284,19 @@
         <v>632</v>
       </c>
       <c r="B466" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D466" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E466" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F466" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C466" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D466" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E466" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F466" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="16" t="s">
@@ -17332,10 +17332,10 @@
         <v>903</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D468" s="4">
         <v>4301135990</v>
@@ -17344,7 +17344,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G468" s="1"/>
     </row>
@@ -17434,13 +17434,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="C473" s="3" t="s">
         <v>926</v>
-      </c>
-      <c r="B473" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="C473" s="3" t="s">
-        <v>928</v>
       </c>
       <c r="D473" s="4">
         <v>4301135753</v>
@@ -17449,13 +17449,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G473" s="1"/>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>845</v>
@@ -17476,7 +17476,7 @@
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>842</v>
@@ -17497,13 +17497,13 @@
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17512,19 +17512,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G476" s="1"/>
     </row>
     <row r="477" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="C477" s="3" t="s">
         <v>934</v>
-      </c>
-      <c r="B477" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="C477" s="3" t="s">
-        <v>936</v>
       </c>
       <c r="D477" s="4">
         <v>4301071075</v>
@@ -17533,7 +17533,7 @@
         <v>4620207491102</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G477" s="1"/>
     </row>
@@ -17563,10 +17563,10 @@
         <v>727</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D479" s="4">
         <v>4301135946</v>
@@ -17575,19 +17575,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D480" s="4">
         <v>4301135753</v>
@@ -17596,7 +17596,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G480" s="1"/>
     </row>
@@ -17689,10 +17689,10 @@
         <v>686</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D485" s="4">
         <v>4301135940</v>
@@ -17701,7 +17701,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G485" s="1"/>
     </row>
@@ -17770,13 +17770,13 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="C489" s="3" t="s">
         <v>940</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="C489" s="3" t="s">
-        <v>942</v>
       </c>
       <c r="D489" s="4">
         <v>4301071094</v>
@@ -17785,19 +17785,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C490" s="3" t="s">
         <v>944</v>
-      </c>
-      <c r="B490" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="C490" s="3" t="s">
-        <v>946</v>
       </c>
       <c r="D490" s="4">
         <v>4301071093</v>
@@ -17806,13 +17806,13 @@
         <v>4620207490709</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G490" s="1"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>721</v>
@@ -17833,7 +17833,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>742</v>
@@ -17854,7 +17854,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>733</v>
@@ -17875,7 +17875,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>739</v>
@@ -17896,7 +17896,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>655</v>
@@ -17917,7 +17917,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>709</v>
@@ -17938,7 +17938,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>764</v>
@@ -17959,7 +17959,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>862</v>
@@ -17980,13 +17980,13 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D499" s="4">
         <v>4301135914</v>
@@ -18001,28 +18001,28 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B500" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D500" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E500" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F500" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C500" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D500" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E500" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F500" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G500" s="1"/>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>179</v>
@@ -18043,13 +18043,13 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D502" s="4">
         <v>4301136101</v>
@@ -18058,13 +18058,13 @@
         <v>4620207491652</v>
       </c>
       <c r="F502" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G502" s="1"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>603</v>
@@ -18085,7 +18085,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>607</v>
@@ -18106,7 +18106,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>611</v>
@@ -18127,7 +18127,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>615</v>
@@ -18148,7 +18148,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>641</v>
@@ -18169,7 +18169,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>638</v>
@@ -18190,13 +18190,13 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D509" s="4">
         <v>4301135946</v>
@@ -18205,19 +18205,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D510" s="4">
         <v>4301135753</v>
@@ -18226,19 +18226,19 @@
         <v>4620207490914</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G510" s="1"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D511" s="4">
         <v>4301135940</v>
@@ -18247,13 +18247,13 @@
         <v>4620207491614</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G511" s="1"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>852</v>
@@ -18274,13 +18274,13 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D513" s="4">
         <v>4301071063</v>
@@ -18289,13 +18289,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G513" s="1"/>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>490</v>
@@ -18316,13 +18316,13 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18331,19 +18331,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18352,19 +18352,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D517" s="4">
         <v>4301135834</v>
@@ -18373,19 +18373,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="C518" s="3" t="s">
         <v>991</v>
-      </c>
-      <c r="B518" s="3" t="s">
-        <v>992</v>
-      </c>
-      <c r="C518" s="3" t="s">
-        <v>993</v>
       </c>
       <c r="D518" s="4">
         <v>4301135873</v>
@@ -18394,19 +18394,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="C519" s="3" t="s">
         <v>999</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>1001</v>
       </c>
       <c r="D519" s="4">
         <v>4301135850</v>
@@ -18415,19 +18415,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C520" s="3" t="s">
         <v>1003</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C520" s="3" t="s">
-        <v>1005</v>
       </c>
       <c r="D520" s="4">
         <v>4301190117</v>
@@ -18436,19 +18436,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C521" s="3" t="s">
         <v>1007</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="D521" s="4">
         <v>4301190115</v>
@@ -18457,19 +18457,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C522" s="3" t="s">
         <v>1011</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>1013</v>
       </c>
       <c r="D522" s="4">
         <v>4301135865</v>
@@ -18478,19 +18478,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B523" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C523" s="3" t="s">
         <v>1016</v>
-      </c>
-      <c r="B523" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>1018</v>
       </c>
       <c r="D523" s="4">
         <v>4301190116</v>
@@ -18499,19 +18499,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18520,19 +18520,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G524" s="1"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B525" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C525" s="3" t="s">
         <v>1020</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C525" s="3" t="s">
-        <v>1022</v>
       </c>
       <c r="D525" s="4">
         <v>4301071112</v>
@@ -18541,7 +18541,7 @@
         <v>4620207491256</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G525" s="1"/>
     </row>
@@ -18670,10 +18670,10 @@
         <v>780</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D531" s="4">
         <v>4301071117</v>
@@ -18682,7 +18682,7 @@
         <v>4620207491737</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G531" s="1">
         <v>180</v>
@@ -18768,19 +18768,19 @@
         <v>784</v>
       </c>
       <c r="B535" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D535" s="4">
+        <v>4301135920</v>
+      </c>
+      <c r="E535" s="3">
+        <v>4620207491577</v>
+      </c>
+      <c r="F535" s="5" t="s">
         <v>918</v>
-      </c>
-      <c r="C535" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="D535" s="4">
-        <v>4301135760</v>
-      </c>
-      <c r="E535" s="3">
-        <v>4620207491010</v>
-      </c>
-      <c r="F535" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="16" t="s">
@@ -18888,10 +18888,10 @@
         <v>789</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D540" s="4">
         <v>4301135914</v>
@@ -18936,10 +18936,10 @@
         <v>791</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D542" s="4">
         <v>4301137046</v>
@@ -18948,7 +18948,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G542" s="1">
         <v>180</v>
@@ -19058,10 +19058,10 @@
         <v>796</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D547" s="4">
         <v>4301071109</v>
@@ -19070,7 +19070,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
@@ -19082,10 +19082,10 @@
         <v>797</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D548" s="4">
         <v>4301135946</v>
@@ -19094,7 +19094,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -19298,10 +19298,10 @@
         <v>806</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D557" s="4">
         <v>4301135753</v>
@@ -19310,7 +19310,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="16" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
@@ -19418,10 +19418,10 @@
         <v>811</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D562" s="4">
         <v>4301135984</v>
@@ -19442,10 +19442,10 @@
         <v>812</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D563" s="4">
         <v>4301135990</v>
@@ -19454,7 +19454,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F563" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="16" t="s">
@@ -19562,10 +19562,10 @@
         <v>817</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D568" s="4">
         <v>4301071107</v>
@@ -19574,7 +19574,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19586,10 +19586,10 @@
         <v>818</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="D569" s="4">
         <v>4301135824</v>
@@ -19598,7 +19598,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F569" s="5" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
@@ -19778,10 +19778,10 @@
         <v>825</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D577" s="4">
         <v>4301136101</v>
@@ -19790,7 +19790,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F577" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
@@ -19898,10 +19898,10 @@
         <v>830</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C582" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D582" s="4">
         <v>4301135940</v>
@@ -19910,7 +19910,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F582" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G582" s="21"/>
       <c r="H582" s="22" t="s">
@@ -20039,13 +20039,13 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D588" s="4">
         <v>4301135848</v>
@@ -20054,19 +20054,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F588" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G588" s="1"/>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C589" s="3" t="s">
         <v>1029</v>
-      </c>
-      <c r="B589" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C589" s="3" t="s">
-        <v>1031</v>
       </c>
       <c r="D589" s="4">
         <v>4301135848</v>
@@ -20075,19 +20075,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F589" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G589" s="1"/>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="D590" s="4">
         <v>4301190118</v>
@@ -20096,19 +20096,19 @@
         <v>4620207491461</v>
       </c>
       <c r="F590" s="5" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G590" s="1"/>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C591" s="3" t="s">
         <v>1033</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C591" s="3" t="s">
-        <v>1035</v>
       </c>
       <c r="D591" s="4">
         <v>4301190118</v>
@@ -20117,7 +20117,7 @@
         <v>4620207491461</v>
       </c>
       <c r="F591" s="5" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G591" s="1"/>
     </row>
